--- a/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
+++ b/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
@@ -16,12 +16,12 @@
     <sheet name="福島県" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'青森県'!$A$3:$S$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'岩手県'!$A$3:$S$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'宮城県'!$A$3:$S$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'秋田県'!$A$3:$S$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'山形県'!$A$3:$S$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'福島県'!$A$3:$S$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'青森県'!$A$3:$T$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'岩手県'!$A$3:$T$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'宮城県'!$A$3:$T$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'秋田県'!$A$3:$T$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'山形県'!$A$3:$T$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'福島県'!$A$3:$T$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -574,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1000,26 +1003,50 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>■ 調査の方法と限界</t>
+          <t>■ 国交省一覧との照合（T列）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>【重要】検索回数に上限（1セッション200回）があるため、県によっては一部の市町村・計画を調べきれていません。「調査状況」列が「未調査」「交通のみ調査」の行は空欄・？になっていますが、計画がないという意味ではありません。</t>
+          <t>国土交通省「地域公共交通計画の作成状況一覧」（令和8年5月末時点）と照合。掲載＝計画作成済み、期間満了＝一覧で灰色（計画期間が満了）。一覧には計画期間の記載がないため、終期は各計画書で確認。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>【当方未把握】＝一覧には計画があるが本調査で計画書を特定できていない／【当方は計画あり】＝本調査では計画を把握したが一覧に未掲載（旧法計画・最近の策定・名称違いの可能性）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>■ 調査の方法と限界</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>【重要】検索回数に上限（1セッション200回）があるため、県によっては一部の市町村・計画を調べきれていません。「調査状況」列が「未調査」「交通のみ調査」の行は空欄・？になっていますが、計画がないという意味ではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
           <t>2026年9月30日時点でWeb検索して調べました。自治体サイトやPDFを直接開けない環境だったため、期間は検索結果の本文・要約から取っています。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>計画リンクはエビデンスとして検索結果に出たURLを載せています。営業に行く前に、リンク先の計画書で計画期間を確かめてください。特に「推定」「不明」の行は必ず確認してください。</t>
         </is>
@@ -1036,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1058,6 +1085,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1170,6 +1198,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -1258,6 +1291,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -1346,6 +1384,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -1434,6 +1477,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T6" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -1520,6 +1568,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -1593,9 +1646,14 @@
           <t>交通：R5.6策定（パブコメR5.4.17〜5.16）。期間は検索結果で未確認のため5年と仮定した推定値（要確認）。R6.3に五所川原市地域公共交通推進計画（R6〜R10、確認済 https://www.city.goshogawara.lg.jp/jouhou/keikaku/files/koutuu_suisin.pdf）。H28.3網形成計画・H30.3再編実施計画あり。環境：環境基本計画は検索で見当たらず。代替として五所川原市地球温暖化対策実行計画（区域施策編）が存在する模様（https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/planR2_gaiyouban.pdf の可能性）。事務事業編相当は環境保全率先行動計画（H21〜H25）。</t>
         </is>
       </c>
-      <c r="S8" s="17" t="inlineStr">
+      <c r="S8" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -1671,9 +1729,14 @@
           <t>交通：計画期間R5〜R9（5か年、検索結果で確認）。概要版 https://www.city.towada.lg.jp/kurashi/koutsu/files/gaiyouban.pdf 。策定支援業務仕様書 https://www.city.towada.lg.jp/kurashi/koutsu/files/shiyousyo.pdf あり（日付不明、現行計画策定時のものの可能性が高い。次期計画分かは要確認）。R9終了のため次期計画はR8〜R9に着手見込み。環境：環境基本計画は検索で見当たらず。R7.3に十和田市地球温暖化対策実行計画（区域施策編）策定（https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/keikakugaiyouban.pdf）。</t>
         </is>
       </c>
-      <c r="S9" s="17" t="inlineStr">
+      <c r="S9" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -1762,6 +1825,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -1835,9 +1903,14 @@
           <t>交通：下北地域公共交通総合連携協議会（むつ市・大間町・東通村・風間浦村・佐井村）がR7.3策定、2025〜2029。URLは素案PDF（パブコメR7.2.17〜3.3）。前計画はH30.3の下北地域公共交通網形成計画。市単独ではむつ市公共交通再編関連資料（2026）https://www.city.mutsu.lg.jp/kurashi/koutsu/koutsu_sisaku/files/mutsu_kokyokotsusaihen_2026.pdf あり（地域公共交通計画ではなく再編計画の可能性）。環境：環境基本計画は検索で見当たらず。第4期むつ市地球温暖化対策推進実行計画（事務事業編）R7.6策定（https://www.city.mutsu.lg.jp/kurashi/kankyo/kankyo/files/ondankakeikaku4.pdf）。</t>
         </is>
       </c>
-      <c r="S11" s="17" t="inlineStr">
+      <c r="S11" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：下北地域）</t>
         </is>
       </c>
     </row>
@@ -1911,9 +1984,14 @@
           <t>交通：地域公共交通計画は検索で確認できず。つがる市地域公共交通会議（H20.9設置）https://www.city.tsugaru.aomori.jp/soshiki/somu/tiikisousei/kikakusinnkou/kokyokotu/6434.html 。環境：第2次計画のページは確認、期間不明。区域施策編は西つがる3市町（つがる市・鰺ヶ沢町・深浦町）共同で策定（R6.3パブコメ https://www.town.fukaura.lg.jp/fixed_docs/2024032100017/）。</t>
         </is>
       </c>
-      <c r="S12" s="17" t="inlineStr">
+      <c r="S12" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2002,6 +2080,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -2075,9 +2158,14 @@
           <t>交通：町HPに計画掲載、令和3年度策定と検索結果に記載（期間は未確認、5年計画と仮定しR4〜R8推定）。R8終了なら次期改定の動きに注意。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S14" s="17" t="inlineStr">
+      <c r="S14" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2153,9 +2241,14 @@
           <t>交通：策定支援業務プロポーザル2022-10（https://www.town.imabetsu.lg.jp/news/gyousei/2022-1017-1745-1.html）、計画公表ページ2023-08-28。期間は検索結果で未確認（R5〜R9推定）。JR津軽線蟹田〜三厩は2027年4月廃止・バス/乗合タクシー転換予定（NPO今別外ヶ浜交通）で計画見直しの可能性あり。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S15" s="17" t="inlineStr">
+      <c r="S15" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2221,9 +2314,14 @@
           <t>交通：村名検索・村HP内検索で地域公共交通計画は見当たらず（公共交通ページ https://www.vill.yomogita.lg.jp/kurashi/kotsu/ のみ）。青森市計画は市単独。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S16" s="17" t="inlineStr">
+      <c r="S16" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2299,9 +2397,14 @@
           <t>交通計画は2024年2月27日パブコメ実施（URLは同パブコメページ、期間は5年と推定）。JR津軽線蟹田〜三厩の代行・転換が絡む。環境基本計画は確認できず（今回検索でも見当たらず）、代替として地球温暖化対策実行計画（区域施策編）令和8年3月策定: https://www.town.sotogahama.lg.jp/gyosei/keikaku/files/01_soto_kuikisesaku_plan.pdf 環境基本計画は検索で確認できず（計画なしの確証なし）。</t>
         </is>
       </c>
-      <c r="S17" s="17" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2377,9 +2480,14 @@
           <t>交通：旧メモ「単独計画は確認できず」は誤り。町HPで2024年3月策定を確認（パブコメ http://www.town.ajigasawa.lg.jp/gyosei_jyoho/publiccomment/kokyokotukeikaku.html）。期間は未確認で5年と仮定しR6〜R10推定。五所川原圏域定住自立圏構成町。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S18" s="17" t="inlineStr">
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2455,9 +2563,14 @@
           <t>交通：計画書表紙「令和6年4月」。前計画は深浦町地域公共交通網形成計画（2020年3月策定）。期間は未確認で5年と仮定しR6〜R10推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S19" s="17" t="inlineStr">
+      <c r="S19" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2523,9 +2636,14 @@
           <t>交通：村HP内検索で地域公共交通計画は見当たらず（コミュニティバスのみ https://www.nishimeya.jp/kurashi_tetsuzuki/kokyokotsu/300.html）。弘前市地域公共交通計画（R6.3）は市単独とみられる。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境：村HP内検索で環境基本計画は見当たらず（再生可能エネルギー振興策 https://www.nishimeya.jp/sonseijoho/seisaku_keikaku/5/7/228.html、災害廃棄物処理計画R8.1はあり）。計画なしの可能性が高いが確証なく未確認。</t>
         </is>
       </c>
-      <c r="S20" s="17" t="inlineStr">
+      <c r="S20" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2591,9 +2709,14 @@
           <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン・総合計画のみ）。弘前圏域8市町村の弘南鉄道維持活性化基本方針（2020）あり。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S21" s="17" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2669,9 +2792,14 @@
           <t>町HP「大鰐町地域公共交通計画策定について」ページに計画PDF（ファイル名R5.5.pdf）掲載→R5.5策定と見られ、5年計画ならR5〜R9（期間は未確認・推定）。過去に計画案策定支援業務の公募型プロポーザル実施: http://www.town.owani.lg.jp/news/index.cfm/detail.1.12187.html （日付未確認）。弘南鉄道大鰐線は運行休止/廃止方向で交通再編の動きあり。環境基本計画・温対計画は検索で見当たらず。</t>
         </is>
       </c>
-      <c r="S22" s="17" t="inlineStr">
+      <c r="S22" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -2737,9 +2865,14 @@
           <t>交通：村HP内検索で地域公共交通計画は見当たらず。弘南鉄道弘南線・大鰐線 維持活性化支援計画（5市町村、2021年1月）に参加 http://www.vill.inakadate.lg.jp/docs/2021022200016/。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S23" s="17" t="inlineStr">
+      <c r="S23" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2805,9 +2938,14 @@
           <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン案R7.2に公共交通の記述あり https://www.town.itayanagi.aomori.jp/administration/salary/files/toshimasu.pdf）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S24" s="17" t="inlineStr">
+      <c r="S24" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2873,9 +3011,14 @@
           <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（各種計画ページ https://www.town.tsuruta.lg.jp/syoukai/syoukai-kakusyu/index.html に該当表示なし、要目視確認）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S25" s="17" t="inlineStr">
+      <c r="S25" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -2951,9 +3094,14 @@
           <t>交通：計画書表紙「令和5年4月」、計画ページ https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 。ファイル名にr6とあり令和6年に改訂の可能性。期間は未確認で5年と仮定しR5〜R9推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
         </is>
       </c>
-      <c r="S26" s="17" t="inlineStr">
+      <c r="S26" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -3019,9 +3167,14 @@
           <t>交通・環境とも町単独計画は検索で確認できず（町HP「まちの計画」 https://www.town.noheji.aomori.jp/life/chosei/machidukuri/machi-keikaku は存在するが内容未確認、町サイトは取得不可）。地域間幹線系統確保維持費補助金交付要綱あり https://www.town.noheji.aomori.jp/reiki_int/reiki_honbun/c041RG00000724.html 。改定作業の情報なし。</t>
         </is>
       </c>
-      <c r="S27" s="17" t="inlineStr">
+      <c r="S27" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -3095,9 +3248,14 @@
           <t>網形成計画（策定支援プロポ: http://www.town.shichinohe.lg.jp/jigyo/nyuusatsu/post-65.html）。期間未確認で既に期限切れの可能性、後継の地域公共交通計画は未確認（H21に地域公共交通会議設置・総合連携計画策定の経緯あり）。環境基本計画は確認できず、関連として地域省エネルギー重点ビジョン（H22）あり（計画なしは弱い根拠）。 環境基本計画は検索で確認できず（計画なしの確証なし）。</t>
         </is>
       </c>
-      <c r="S28" s="17" t="inlineStr">
+      <c r="S28" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
         </is>
       </c>
     </row>
@@ -3163,9 +3321,14 @@
           <t>交通計画は未確認だが、2026年8月31日に「交通まちづくりワークショップ」開催告知（町バス利用者・学生・保護者・事業者対象）: https://www.town.rokunohe.aomori.jp/docs/2026083100015 。地域公共交通計画策定に向けた作業と推定（計画名・プロポは未確認）。環境基本計画・温対計画は検索で見当たらず。</t>
         </is>
       </c>
-      <c r="S29" s="17" t="inlineStr">
+      <c r="S29" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -3231,9 +3394,14 @@
           <t>町単独の地域公共交通計画は確認できず。下北地域公共交通計画（2025年3月策定、下北地域公共交通総合連携協議会）の対象はむつ市・大間町・東通村・風間浦村・佐井村の5市町村で横浜町は含まれない（むつ市資料 https://www.city.mutsu.lg.jp/government/katsudou/kyoudou/files/04kotsu.pdf で確認）。下北半島都市圏広域立地適正化方針（R5.8）には含まれる。町HPに2026-04-10付PDFあり内容未確認 https://www.town.yokohama.lg.jp/index.cfm/6,9299,c,html/9299/20260410-143501.pdf 。環境基本計画・区域施策編も検索で見当たらず（横浜市との再エネ連携協定はあり）。</t>
         </is>
       </c>
-      <c r="S30" s="17" t="inlineStr">
+      <c r="S30" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -3299,9 +3467,14 @@
           <t>東北町地域公共交通会議あり（会議録 https://www.town.tohoku.lg.jp/chousei/info/info_yakuba_03-54.html ）。地域公共交通計画の有無は検索で確認できず（東北運輸局の計画一覧PDF https://wwwtb.mlit.go.jp/tohoku/content/000338501.pdf がヒットしたが中身未確認）。環境基本計画も見当たらず、関連は「小川原湖環境再生」計画（地域再生計画、汚水処理）程度。第2期まち・ひと・しごと創生推進計画はR8.4〜R13.3。</t>
         </is>
       </c>
-      <c r="S31" s="17" t="inlineStr">
+      <c r="S31" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -3375,9 +3548,14 @@
           <t>R7.3策定（素案住民意見聴取後）。計画ページ https://www.rokkasho.jp/index.cfm/11,19571,31,177,html 。R7.6に計画に基づく再編・見直し検討及び実証運行支援業務の公募型プロポーザル実施 https://www.rokkasho.jp/index.cfm/14,19918,31,177,html 。環境基本計画は検索で見当たらず（関連: 水環境保全計画、地域新エネルギービジョン、バイオマスタウン構想）。</t>
         </is>
       </c>
-      <c r="S32" s="17" t="inlineStr">
+      <c r="S32" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -3453,9 +3631,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は町名検索・ゼロカーボン検索とも該当なし（地域再生計画等のみヒット）。区域施策編も未確認。</t>
         </is>
       </c>
-      <c r="S33" s="17" t="inlineStr">
+      <c r="S33" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -3531,9 +3714,14 @@
           <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S34" s="17" t="inlineStr">
+      <c r="S34" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：下北地域）</t>
         </is>
       </c>
     </row>
@@ -3609,9 +3797,14 @@
           <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画は検索でヒットせず（原発モニタリング・風力アセス関連のみ）。</t>
         </is>
       </c>
-      <c r="S35" s="17" t="inlineStr">
+      <c r="S35" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：下北地域）</t>
         </is>
       </c>
     </row>
@@ -3687,9 +3880,14 @@
           <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S36" s="17" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：下北地域）</t>
         </is>
       </c>
     </row>
@@ -3765,9 +3963,14 @@
           <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S37" s="17" t="inlineStr">
+      <c r="S37" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：下北地域）</t>
         </is>
       </c>
     </row>
@@ -3843,9 +4046,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・地球温暖化対策実行計画とも検索でヒットせず（地域再生計画・風力アセスのみ）。</t>
         </is>
       </c>
-      <c r="S38" s="17" t="inlineStr">
+      <c r="S38" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -3921,9 +4129,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は検索でヒットせず。代替として五戸町地球温暖化対策実行計画（区域施策編・地域気候変動適応計画兼ねる、R7.3策定、環境省地域脱炭素実現支援事業で作成）あり：https://www.town.gonohe.aomori.jp/chosei/tikyuondankahonpen.pdf （概要版 https://www.town.gonohe.aomori.jp/chosei/tikyuondankagaiyouban.pdf ）。期間は検索結果で確認できず。環境省策定状況 https://www.env.go.jp/policy/local_keikaku/sakutei2/02/02442.html</t>
         </is>
       </c>
-      <c r="S39" s="17" t="inlineStr">
+      <c r="S39" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T39" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -3999,9 +4212,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S40" s="17" t="inlineStr">
+      <c r="S40" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T40" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -4077,9 +4295,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。青森県三戸郡南部町。環境基本計画・温暖化対策実行計画とも検索でヒットせず（地域再生計画のみ）。</t>
         </is>
       </c>
-      <c r="S41" s="17" t="inlineStr">
+      <c r="S41" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T41" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -4155,9 +4378,14 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画・ゼロカーボン関連とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S42" s="17" t="inlineStr">
+      <c r="S42" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T42" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
         </is>
       </c>
     </row>
@@ -4233,15 +4461,20 @@
           <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
         </is>
       </c>
-      <c r="S43" s="17" t="inlineStr">
+      <c r="S43" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
         </is>
       </c>
+      <c r="T43" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：八戸圏域）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S43"/>
-  <conditionalFormatting sqref="A4:S43">
+  <autoFilter ref="A3:T43"/>
+  <conditionalFormatting sqref="A4:T43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
@@ -4308,7 +4541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4330,6 +4563,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4442,6 +4676,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -4530,6 +4769,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：盛岡市・滝沢市・矢巾町）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -4618,6 +4862,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -4706,6 +4955,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -4794,6 +5048,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -4882,6 +5141,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -4968,6 +5232,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -5054,6 +5323,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -5142,6 +5416,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -5220,6 +5499,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -5308,6 +5592,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -5384,6 +5673,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -5472,6 +5766,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -5560,6 +5859,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -5648,6 +5952,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：盛岡市・滝沢市・矢巾町）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -5734,6 +6043,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
@@ -5797,9 +6111,14 @@
           <t>交通・環境とも町サイト検索で計画を確認できず（公共交通マップのみ https://www.town.kuzumaki.iwate.jp/docs/2015102200249/ ）。県の地域公共交通計画でカバーされる可能性。</t>
         </is>
       </c>
-      <c r="S19" s="17" t="inlineStr">
+      <c r="S19" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -5880,6 +6199,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -5962,6 +6286,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -6040,6 +6369,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：盛岡市・滝沢市・矢巾町）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -6116,6 +6450,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -6194,6 +6533,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -6272,6 +6616,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -6358,6 +6707,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -6436,6 +6790,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -6512,6 +6871,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -6590,6 +6954,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -6674,6 +7043,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -6737,9 +7111,14 @@
           <t>交通：村独自の地域公共交通計画は確認できず（村営バス無料運行 https://www.vill.fudai.iwate.jp/lifescene/koutsu.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。</t>
         </is>
       </c>
-      <c r="S31" s="17" t="inlineStr">
+      <c r="S31" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）【当方未把握】</t>
         </is>
       </c>
     </row>
@@ -6805,9 +7184,14 @@
           <t>交通：地域公共交通計画は確認できず。R8.4からコミュニティバス（円子線・大野線）運行、デマンド交通導入を検討中（R7.3議会一般質問）。環境：確認できず。</t>
         </is>
       </c>
-      <c r="S32" s="17" t="inlineStr">
+      <c r="S32" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -6873,9 +7257,14 @@
           <t>交通：村独自の計画は確認できず（村営バス https://www.vill.noda.iwate.jp/soshiki/miraizukurisuishinka/miraizukurisuishinhan/doro_kotsu/642.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。</t>
         </is>
       </c>
-      <c r="S33" s="17" t="inlineStr">
+      <c r="S33" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）【当方未把握】</t>
         </is>
       </c>
     </row>
@@ -6954,6 +7343,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
@@ -7032,6 +7426,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -7095,15 +7494,20 @@
           <t>交通：地域公共交通計画は確認できず（デマンド交通いくべ号、R8.4運賃改定案パブコメ https://www.town.ichinohe.iwate.jp/soshikikarasagasu/seisakukikakuka/kokyokotsu/6744.html ）。環境：確認できず。</t>
         </is>
       </c>
-      <c r="S36" s="17" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
         </is>
       </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S36"/>
-  <conditionalFormatting sqref="A4:S36">
+  <autoFilter ref="A3:T36"/>
+  <conditionalFormatting sqref="A4:T36">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
@@ -7177,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7199,6 +7603,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7311,6 +7716,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -7399,6 +7809,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -7487,6 +7902,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -7560,9 +7980,14 @@
           <t>交通：市の地域公共交通計画は検索（市サイト内含む）で見つからず（計画なしの可能性、要確認）。環境：第3次計画R7〜R16、素案パブコメ https://www.city.shiogama.miyagi.jp/soshiki/18/49050.html を経て策定（ページ更新R7.4.18）。参考：循環型社会形成推進地域計画 R5.4〜R10.3。</t>
         </is>
       </c>
-      <c r="S6" s="17" t="inlineStr">
+      <c r="S6" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -7638,9 +8063,14 @@
           <t>交通：第2次はH30.2策定・R3.6.28二次改定、目標年次R8（県の市町村計画一覧 https://www.pref.miyagi.jp/documents/7752/02_r8_sityousonkeikaku.pdf の検索要約より）。同資料で第3次気仙沼市総合交通計画を策定中と記載あり→着手済と判断（要確認）。法定地域公共交通計画としての位置付けは未確認。R8.7にAIデマンド交通導入業務プロポーザル https://www.kesennuma.miyagi.jp/sec/s023/020/010/010/20260706170359.html 。環境：市公式サイト内検索で環境基本計画ヒットせず（計画なしの可能性、要確認）。WebFetchは市サイトblocked。 地球温暖化対策実行計画（区域施策編）のパブコメ実績・気仙沼市持続可能なまち推進計画（R7.7）あり https://www.kesennuma.miyagi.jp/li/life/020/080/070/index.html 。</t>
         </is>
       </c>
-      <c r="S7" s="17" t="inlineStr">
+      <c r="S7" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -7729,6 +8159,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -7815,6 +8250,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -7895,6 +8335,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：阿武隈急行線地域）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -7977,6 +8422,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -8065,6 +8515,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -8153,6 +8608,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -8237,6 +8697,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -8325,6 +8790,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T15" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -8413,6 +8883,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -8486,9 +8961,14 @@
           <t>交通：R7.3策定（R6年度）、t_urlはR7.3協議会資料の計画（案）。都市・地域総合交通戦略 https://www.tomiya-city.miyagi.jp/shisei/keikaku/keikaku/nek5ga2.html 。環境：単独の環境基本計画は検索で確認できず（計画なしの可能性、市HP計画一覧 https://www.tomiya-city.miyagi.jp/shisei/keikaku/ 要確認）。温暖化対策実行計画は存在。第2次富谷市総合計画をR8年度開始で策定。</t>
         </is>
       </c>
-      <c r="S17" s="17" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -8579,6 +9059,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
@@ -8642,9 +9127,14 @@
           <t>交通：町営バス3路線を運行（https://town.shichikashuku.miyagi.jp/life/bus.html）が、地域公共交通計画は町の計画一覧（https://town.shichikashuku.miyagi.jp/town/plan/）の検索結果に見当たらず。環境：環境基本計画は確認できず（計画なしと推定）、代替として再生可能エネルギー発電基本計画あり。広域の仙南地域計画も未確認。</t>
         </is>
       </c>
-      <c r="S19" s="17" t="inlineStr">
+      <c r="S19" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -8727,6 +9217,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T20" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -8790,9 +9285,14 @@
           <t>交通：村田町地域公共交通会議（道路運送法）設置要綱 https://www.town.murata.miyagi.jp/cyosei/on-line/reiki_int/reiki_honbun/c215RG00000781.html 、町民バス等運行 https://www.town.murata.miyagi.jp/kurashi/kostu/bus/index.html 。法定の地域公共交通計画は検索で確認できず（未策定の可能性）。環境：環境基本計画は町HP検索で見当たらず（計画なしと推定）。広域の仙南地域計画も未確認。</t>
         </is>
       </c>
-      <c r="S21" s="17" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -8881,6 +9381,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：阿武隈急行線地域）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -8957,6 +9462,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -9035,6 +9545,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：阿武隈急行線地域）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -9121,6 +9636,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -9199,6 +9719,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -9262,9 +9787,14 @@
           <t>交通・環境とも町独自計画は検索で確認できず（町サイトの検索インデックスが薄く、存在しない確証はない＝要確認）。宮城県地域公共交通計画（R8〜R14）が町域を含む https://www.pref.miyagi.jp/soshiki/soukou/20240520.html 。</t>
         </is>
       </c>
-      <c r="S27" s="17" t="inlineStr">
+      <c r="S27" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了【当方未把握】</t>
         </is>
       </c>
     </row>
@@ -9330,9 +9860,14 @@
           <t>交通：町独自の地域公共交通計画は検索で確認できず。町民バス「ぐるりんこ」についてR7.7にアンケート調査を実施し、運行計画見直しに活用予定 https://www.shichigahama.com/benricho/oshirase/sanka3-100-12175.html 。R8.4.1ダイヤ改正。計画策定に発展する可能性あり（要確認・有望）。宮城県地域公共交通計画（R8〜R14）が町域を含む。環境：環境基本計画は町サイト検索で見当たらず。</t>
         </is>
       </c>
-      <c r="S28" s="17" t="inlineStr">
+      <c r="S28" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -9411,6 +9946,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -9499,6 +10039,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -9562,9 +10107,14 @@
           <t>交通：町単独・黒川地域共同の地域公共交通計画は検索で確認できず（町民バス運行のみの可能性）。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：町独自の環境基本計画は検索で確認できず。</t>
         </is>
       </c>
-      <c r="S31" s="17" t="inlineStr">
+      <c r="S31" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -9630,9 +10180,14 @@
           <t>交通：村単独・黒川地域共同の地域公共交通計画は検索で確認できず。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：環境基本計画は確認できず。代替として第5次大衡村地球温暖化対策実行計画（事務事業編、R5〜R12）あり。</t>
         </is>
       </c>
-      <c r="S32" s="17" t="inlineStr">
+      <c r="S32" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -9698,9 +10253,14 @@
           <t>交通：町単独計画は確認できず。大崎定住自立圏（大崎市・色麻・加美・涌谷・美里）で大崎圏域公共交通検討研究会を開催し圏域交通を検討 https://www.pref.miyagi.jp/site/tiikisinnkou/teizyu.html 。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：環境基本計画は検索で確認できず。</t>
         </is>
       </c>
-      <c r="S33" s="17" t="inlineStr">
+      <c r="S33" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -9776,9 +10336,14 @@
           <t>交通：町の地域公共交通計画は未策定とみられ、第三次加美町総合計画策定の経緯資料に「地域公共交通計画」の策定が言及されている（策定作業中の可能性、要確認）https://www.town.kami.miyagi.jp/material/files/group/6/2-keii.pdf 。住民バスはR7.4.1から新体系で運行。大崎定住自立圏で圏域公共交通検討研究会あり。環境：H19.3初版、R5.3改定版策定（10年間）。地球温暖化対策実行計画（区域施策編・事務事業編）R7.1策定 https://www.town.kami.miyagi.jp/material/files/group/60/gaiyou2.pdf</t>
         </is>
       </c>
-      <c r="S34" s="17" t="inlineStr">
+      <c r="S34" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -9859,6 +10424,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -9922,9 +10492,14 @@
           <t>交通：地域公共交通計画は町サイト検索で確認できず。美里町地域公共交通会議は活動中（R8.2.13会議録あり）https://www.town.misato.miyagi.jp/16bus/ 。大崎定住自立圏の圏域公共交通検討研究会に参加。環境：環境基本計画は確認できず、代替として美里町再生可能エネルギー導入推進計画（R4.4）https://www.town.misato.miyagi.jp/08kankyo/pdf/saiseikanou.pdf 。</t>
         </is>
       </c>
-      <c r="S36" s="17" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10580,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -10091,10 +10671,15 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S38"/>
-  <conditionalFormatting sqref="A4:S38">
+  <autoFilter ref="A3:T38"/>
+  <conditionalFormatting sqref="A4:T38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
@@ -10167,7 +10752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10189,6 +10774,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10301,6 +10887,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -10389,6 +10980,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -10475,6 +11071,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -10563,6 +11164,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -10651,6 +11257,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -10729,6 +11340,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -10807,6 +11423,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -10895,6 +11516,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -10983,6 +11609,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -11071,6 +11702,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -11159,6 +11795,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -11247,6 +11888,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -11325,6 +11971,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -11403,6 +12054,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -11489,6 +12145,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -11552,9 +12213,14 @@
           <t>交通：村単独の地域公共交通計画は確認できず。以前は北秋田市・上小阿仁村の地域公共交通網形成計画（H29〜H34）が検索要約に出たが未確証。現行の北秋田市地域公共交通計画（R5〜R9、R5.3策定 https://www.city.kitaakita.akita.jp/uploads/public/news_0000015700_00/koukyoukoutsukeikaku.pdf ）の計画区域に上小阿仁村が含まれるかは未確認（要確認、含まれればt_end=9）。環境：環境基本計画・温対計画とも村HP検索で確認できず（計画なしの可能性大）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。</t>
         </is>
       </c>
-      <c r="S18" s="17" t="inlineStr">
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -11643,6 +12309,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -11719,6 +12390,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -11782,9 +12458,14 @@
           <t>交通：八峰町単独の地域公共交通計画は町HP検索で確認できず。R2年度に住民アンケート、R3.10.1〜R4.9.30巡回バス試行運行 http://www.town.happou.akita.jp/docs/2021091400034/ 。能代山本地域の広域計画も確認できず（R6.10秋北バス能代山本路線再編で町の巡回バス・乗合タクシー拡充）https://www.sakigake.jp/news/article/20241006AK0019/ 。環境：環境基本計画は確認できず（町HP要約に地球温暖化防止対策実行計画・省エネビジョンの言及のみ、詳細不明）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。</t>
         </is>
       </c>
-      <c r="S21" s="17" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -11865,6 +12546,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：南秋）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -11943,6 +12629,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：南秋）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -12021,6 +12712,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -12099,6 +12795,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：南秋）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -12177,6 +12878,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -12255,6 +12961,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -12333,10 +13044,15 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S28"/>
-  <conditionalFormatting sqref="A4:S28">
+  <autoFilter ref="A3:T28"/>
+  <conditionalFormatting sqref="A4:T28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
@@ -12401,7 +13117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12423,6 +13139,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12535,6 +13252,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -12623,6 +13345,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -12709,6 +13436,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -12797,6 +13529,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -12883,6 +13620,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -12969,6 +13711,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T8" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -13053,6 +13800,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T9" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -13139,6 +13891,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -13225,6 +13982,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T11" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -13311,6 +14073,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：フラワー長井線沿線）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -13397,6 +14164,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n">
@@ -13481,6 +14253,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -13567,6 +14344,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T15" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -13643,6 +14425,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：フラワー長井線沿線）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -13719,6 +14506,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T17" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -13795,6 +14587,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T18" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
@@ -13877,6 +14674,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n">
@@ -13955,6 +14757,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -14041,6 +14848,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T21" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
@@ -14127,6 +14939,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -14203,6 +15020,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -14279,6 +15101,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -14355,6 +15182,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -14431,6 +15263,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -14507,6 +15344,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n">
@@ -14583,6 +15425,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
@@ -14659,6 +15506,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -14735,6 +15587,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -14819,6 +15676,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -14895,6 +15757,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：フラワー長井線沿線）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -14971,6 +15838,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -15047,6 +15919,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：フラワー長井線沿線）／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
@@ -15123,6 +16000,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T35" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -15199,6 +16081,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
@@ -15283,6 +16170,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -15367,10 +16259,15 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S38"/>
-  <conditionalFormatting sqref="A4:S38">
+  <autoFilter ref="A3:T38"/>
+  <conditionalFormatting sqref="A4:T38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
@@ -15453,7 +16350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15475,6 +16372,7 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15587,6 +16485,11 @@
           <t>調査状況</t>
         </is>
       </c>
+      <c r="T3" s="10" t="inlineStr">
+        <is>
+          <t>国交省一覧(R8.5末)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -15675,6 +16578,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域・阿武隈急行線地域）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -15763,6 +16671,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -15851,6 +16764,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -15939,6 +16857,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -16027,6 +16950,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -16111,6 +17039,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -16193,6 +17126,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -16256,9 +17194,14 @@
           <t>交通・環境とも検索で確認できず（市サイト内検索でも該当ページ出ず、南相馬市の結果に埋もれる）。公共交通情報 https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/seikatsu/1/1679.html 。参考：福島県地域公共交通計画（R6.3策定）https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf</t>
         </is>
       </c>
-      <c r="S11" s="17" t="inlineStr">
+      <c r="S11" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -16347,6 +17290,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -16420,9 +17368,14 @@
           <t>交通：R4〜R8、R6.6一部改訂。R8.3協議会で「第2次田村市地域公共交通計画策定業務」の審査委員会設置を協議→次期計画策定着手（資料 https://www.city.tamura.lg.jp/soshiki/1/assets/%E8%B3%87%E6%96%99%E4%B8%80%E5%BC%8F%EF%BC%88R7%E7%AC%AC1%E5%9B%9E%EF%BC%89.pdf ほか）。環境：環境基本計画は検索で確認できず（一般廃棄物処理計画等のみヒット）。</t>
         </is>
       </c>
-      <c r="S13" s="17" t="inlineStr">
+      <c r="S13" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
         </is>
       </c>
     </row>
@@ -16511,6 +17464,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -16597,6 +17555,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：阿武隈急行線地域）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n">
@@ -16679,6 +17642,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
@@ -16742,9 +17710,14 @@
           <t>地域公共交通計画は町HP内検索・一般検索とも確認できず（都市計画マスタープランR6年度策定、公共交通は環境係所管）。環境基本計画も見当たらず、代替として地球温暖化対策実行計画 区域施策編（地域まるごと省エネ計画、R6.2改正）・事務事業編（第4期、R4.3策定）あり: https://www.town.koori.fukushima.jp/soshiki/kankyo/1/3/9286.html 。都市計画マスタープランはR6年度策定。環境基本計画の「計画なし」は検索未ヒットに基づく推定。</t>
         </is>
       </c>
-      <c r="S17" s="17" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -16810,9 +17783,14 @@
           <t>地域公共交通計画は町HP内検索でも確認できず。「地域公共交通あり方協議会」設置、国見まちなかタクシー・ももたんパス（タクシー助成実証、https://www.town.kunimi.fukushima.jp/soshiki/4/16576.html）等を実施。広報くにみR3.4号特集、町資料「これからの公共交通のカタチ」（https://www.town.kunimi.fukushima.jp/uploaded/attachment/6659.pdf）。環境基本計画は検索で確認できず。代替として地球温暖化対策実行計画をR6.1.9公表（住民防災課所管）。第6次総合計画（KuniMirai2030）あり。</t>
         </is>
       </c>
-      <c r="S18" s="17" t="inlineStr">
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -16878,9 +17856,14 @@
           <t>地域公共交通計画は検索で確認できず。川俣町地域公共交通会議（H20.3設置、https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/kawamatakoukyokotsu.html）がH21.3に地域公共交通総合連携計画を策定（デマンド型乗合タクシー導入、国交省資料）—旧法計画で現行計画は未確認。環境基本計画も検索で確認できず（各種計画一覧 https://www.town.kawamata.lg.jp/site/chosei-shisetsu/list74.html 要確認）。循環型社会形成推進地域計画（R3〜R7）あり。</t>
         </is>
       </c>
-      <c r="S19" s="17" t="inlineStr">
+      <c r="S19" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T19" s="17" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）【当方未把握】</t>
         </is>
       </c>
     </row>
@@ -16956,9 +17939,14 @@
           <t>地域公共交通計画は素案パブコメR4.1.28〜2.25実施（結果 https://www.vill.otama.fukushima.jp/file/contents/527/25641/koukyoukoutuu_kekka.pdf）→R3年度末策定、期間は5年と推定（R8度末終了なら次期計画作業の可能性、ただし検索で確認できず）。デマンド型乗合タクシー（AI配車）・通勤通学バス運行。環境基本計画は検索で確認できず（各種計画一覧に見当たらず、第5次総合振興計画・立地適正化計画R6.8等のみ）。</t>
         </is>
       </c>
-      <c r="S20" s="17" t="inlineStr">
+      <c r="S20" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -17024,9 +18012,14 @@
           <t>地域公共交通計画は町HP内検索でも確認できず（都市計画マスタープラン、鏡石駅周辺将来まちづくりビジョンR7.3のみ）。環境基本計画も検索で確認できず。各種まちづくり計画一覧: https://www.town.kagamiishi.fukushima.jp/kurashi/chousei/008285.html</t>
         </is>
       </c>
-      <c r="S21" s="17" t="inlineStr">
+      <c r="S21" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17092,9 +18085,14 @@
           <t>地域公共交通計画・環境基本計画とも検索で確認できず（村HPはほぼ検索インデックスなし）。小規模村で計画なしの可能性。</t>
         </is>
       </c>
-      <c r="S22" s="17" t="inlineStr">
+      <c r="S22" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17160,9 +18158,14 @@
           <t>町単独の地域公共交通計画・環境基本計画は検索で確認できず。会津線沿線（会津若松市・下郷町・南会津町）で会津線活性化連携協議会が地域公共交通総合連携計画を策定（旧法）、会津鉄道の鉄道事業再構築実施計画はR7.4〜R17.3。会津地域の広域公共交通計画（2026〜2031、6市町村）の記載が検索要約にあるが対象市町村・名称は要確認。過疎地域持続的発展計画（R3〜R7）あり。</t>
         </is>
       </c>
-      <c r="S23" s="17" t="inlineStr">
+      <c r="S23" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17228,9 +18231,14 @@
           <t>地域公共交通計画・環境基本計画とも検索で確認できず。小規模村で計画なしの可能性（南会津地域4町村の共同交通計画も確認できず）。</t>
         </is>
       </c>
-      <c r="S24" s="17" t="inlineStr">
+      <c r="S24" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17296,9 +18304,14 @@
           <t>地域公共交通計画は町HP内検索でも確認できず（只見駅周回バス、雪んこタクシー等運行）。環境基本計画も検索で確認できず（ユネスコエコパーク関連の取組はあり）。</t>
         </is>
       </c>
-      <c r="S25" s="17" t="inlineStr">
+      <c r="S25" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17387,6 +18400,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
@@ -17450,9 +18468,14 @@
           <t>村単独の地域公共交通計画は検索で確認できず（会津圏域計画の対象外）。再検索でも確認できず（国交省事例:喜多方～裏磐梯バス・桧原湖周遊バス https://www.mlit.go.jp/sogoseisaku/transport/pdf/021_kitashiobara.pdf ）。 【環境】環境基本計画は検索で確認できず。代替として『北塩原村地域まるごと脱炭素計画』（区域施策編＋地域気候変動適応計画を兼ねる） https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3387.pdf 、事務事業編あり。ゼロカーボンシティ宣言済。</t>
         </is>
       </c>
-      <c r="S27" s="17" t="inlineStr">
+      <c r="S27" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>掲載【当方未把握】</t>
         </is>
       </c>
     </row>
@@ -17518,9 +18541,14 @@
           <t>町単独の地域公共交通計画は町HPで確認できず（町民バス・デマンドバス運行、会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。代替として『西会津町地域まるごと省エネ計画（区域施策編）』R3.3策定、事務事業編H30.2策定 https://www.town.nishiaizu.fukushima.jp/soshiki/3/10204.html 。</t>
         </is>
       </c>
-      <c r="S28" s="17" t="inlineStr">
+      <c r="S28" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17586,9 +18614,14 @@
           <t>町単独の地域公共交通計画は確認できず（AIオンデマンド交通導入 https://www.town.bandai.fukushima.jp/site/kurashi-kankyo/bandai-koukyo-koutuuondemand.html ）。総合計画見直し中(R7審議会)。 【環境】環境基本計画は検索で確認できず。代替として『磐梯町地球温暖化対策実行計画（区域施策編・事務事業編）』令和7年9月策定 https://www.town.bandai.fukushima.jp/uploaded/attachment/7725.pdf 。ゼロカーボン宣言・ネイチャーポジティブ宣言済。</t>
         </is>
       </c>
-      <c r="S29" s="17" t="inlineStr">
+      <c r="S29" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17654,9 +18687,14 @@
           <t>町単独の地域公共交通計画は町HP・再検索でも確認できず。立地適正化計画策定の動きあり https://www.town.inawashiro.fukushima.jp/cb/hpc/Article-199-15693.html 。 【環境】町HP『環境計画・構想』に環境基本計画は見当たらず。第3次地球温暖化対策実行計画(R3.3策定、最終R6年度) https://www.town.inawashiro.fukushima.jp/cb/hpc/Article-128-18213.html （次期未確認）、再エネ推進計画(2021〜2040) https://www.town.inawashiro.fukushima.jp/cb/hpc/Article-8-18273.html 。</t>
         </is>
       </c>
-      <c r="S30" s="17" t="inlineStr">
+      <c r="S30" s="18" t="inlineStr">
         <is>
           <t>環境のみ調査</t>
+        </is>
+      </c>
+      <c r="T30" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -17737,6 +18775,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -17810,9 +18853,14 @@
           <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.yugawa.fukushima.jp/site/gyousei-top/various-plans.html ）。</t>
         </is>
       </c>
-      <c r="S32" s="17" t="inlineStr">
+      <c r="S32" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
         </is>
       </c>
     </row>
@@ -17888,9 +18936,14 @@
           <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず。役場地球温暖化対策実行計画(R4.1改訂) https://www.town.yanaizu.fukushima.jp/docs/2022120500022/file_contents/ondankakeikaku.pdf 、R4.12ゼロカーボンシティ宣言。</t>
         </is>
       </c>
-      <c r="S33" s="17" t="inlineStr">
+      <c r="S33" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
         </is>
       </c>
     </row>
@@ -17956,9 +19009,14 @@
           <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。三島町ゼロカーボンビジョン(2022.5) https://www.town.mishima.fukushima.jp/uploaded/attachment/1087.pdf 、第2次実行計画（事務事業編）R6.3策定・2024〜2030 http://www.town.mishima.fukushima.jp/soshiki/chiiki-seisaku/4267.html 。</t>
         </is>
       </c>
-      <c r="S34" s="17" t="inlineStr">
+      <c r="S34" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -18024,9 +19082,14 @@
           <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。自然環境等と再エネ発電事業等との調和に関する条例制定(パブコメ) https://www.town.kaneyama.fukushima.jp/soshiki/54/pabukomesizennkannkyou.html 。R7.9議会でゼロカーボン表明検討の質疑。</t>
         </is>
       </c>
-      <c r="S35" s="17" t="inlineStr">
+      <c r="S35" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -18092,9 +19155,14 @@
           <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.showa.fukushima.jp/procedure/1096/ ）。</t>
         </is>
       </c>
-      <c r="S36" s="17" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>未調査</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>未掲載</t>
         </is>
       </c>
     </row>
@@ -18170,9 +19238,14 @@
           <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 別途、町単独の『会津美里町地域公共交通計画（案）』(令和8年、町地域公共交通会議資料) https://www.town.aizumisato.fukushima.jp/material/files/group/3/keikakuann.pdf が作成中＝着手済（期間未確認）。 【環境】環境基本計画は検索で確認できず。地球温暖化対策実行計画（事務事業編R4〜R6） https://www.town.aizumisato.fukushima.jp/gyosei/gyoseijoho/8/7/2/3496.html 、再エネ導入目標等策定支援業務プロポーザル https://www.town.aizumisato.fukushima.jp/soshiki/1009/3/10/5800.html 、ゼロカーボン宣言済。</t>
         </is>
       </c>
-      <c r="S37" s="17" t="inlineStr">
+      <c r="S37" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：会津圏域）</t>
         </is>
       </c>
     </row>
@@ -18261,6 +19334,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
@@ -18334,9 +19412,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。コミュニティバス「ふれあい号」3路線運行。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。村HP「各種計画の一覧」https://www.vill.izumizaki.fukushima.jp/page/page001839.html で要確認。</t>
         </is>
       </c>
-      <c r="S39" s="17" t="inlineStr">
+      <c r="S39" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -18412,9 +19495,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。しらかわ地域定住自立圏構成村。環境基本計画・温暖化対策実行計画とも検索で確認できず。</t>
         </is>
       </c>
-      <c r="S40" s="17" t="inlineStr">
+      <c r="S40" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T40" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -18493,6 +19581,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T41" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
@@ -18579,6 +19672,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
@@ -18652,9 +19750,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。町は「地域の公共交通網整備に向けた基本調査研究」を公表（https://www.town.yamatsuri.fukushima.jp/sp/page/page000235.html）。環境基本計画は町HPドメイン検索でも確認できず（総合計画・太陽光条例等のみ）。第7次総合計画R8〜R12策定。</t>
         </is>
       </c>
-      <c r="S43" s="17" t="inlineStr">
+      <c r="S43" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T43" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -18735,6 +19838,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T44" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
@@ -18808,9 +19916,14 @@
           <t>交通計画はR5.2.21協議会で策定、デマンド交通導入を位置付け。R9年度末で満了→R8〜R9に次期計画検討が見込まれる。R7年度協議会会議録が村HP（上記協議会ページ）に公開、次期計画への言及は未確認。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。（バイオマスヴィレッジ構想・公害対策条例のみ確認）</t>
         </is>
       </c>
-      <c r="S45" s="17" t="inlineStr">
+      <c r="S45" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T45" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -18886,9 +19999,14 @@
           <t>H29.3策定の石川町地域公共交通網形成計画の後継計画（2023〜2028年度）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。第2次石川町地球温暖化防止実行計画（事務事業編、2023〜2028年度）https://www.town.ishikawa.fukushima.jp/admin/ishikawa/info/005930.html のみ確認。</t>
         </is>
       </c>
-      <c r="S46" s="17" t="inlineStr">
+      <c r="S46" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T46" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -18964,9 +20082,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。住宅用太陽光補助等のみ確認。</t>
         </is>
       </c>
-      <c r="S47" s="17" t="inlineStr">
+      <c r="S47" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T47" s="17" t="inlineStr">
+        <is>
+          <t>掲載／期間満了</t>
         </is>
       </c>
     </row>
@@ -19042,9 +20165,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。平田村地球温暖化対策実施計画が情報公開ページ（https://www.vill.hirata.fukushima.jp/soshiki/2/174.html）に掲載、一般廃棄物処理基本計画（R4.4, R7.4変更）あり。</t>
         </is>
       </c>
-      <c r="S48" s="17" t="inlineStr">
+      <c r="S48" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T48" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -19125,6 +20253,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T49" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n">
@@ -19198,9 +20331,14 @@
           <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。町HP「各種計画」ページ（https://www.town.furudono.fukushima.jp/chouseijyouhou/torikumikeikaku/keikaku/760）に記載ある可能性は低いが未確認。</t>
         </is>
       </c>
-      <c r="S50" s="17" t="inlineStr">
+      <c r="S50" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -19281,6 +20419,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T51" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n">
@@ -19359,6 +20502,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T52" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
@@ -19447,6 +20595,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T53" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n">
@@ -19525,6 +20678,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T54" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
@@ -19603,6 +20761,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T55" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n">
@@ -19676,9 +20839,14 @@
           <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。村HPで脱炭素ビジョン策定業務および「地球温暖化対策実行計画(区域施策編)策定業務委託」の公募型プロポーザル実施の記載あり(時期未確認、https://www.kawauchimura.jp/)。</t>
         </is>
       </c>
-      <c r="S56" s="17" t="inlineStr">
+      <c r="S56" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T56" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
         </is>
       </c>
     </row>
@@ -19759,6 +20927,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T57" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n">
@@ -19832,9 +21005,14 @@
           <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。双葉町再生可能エネルギー活用・推進計画(H28.3)あり(https://www.town.fukushima-futaba.lg.jp/secure/7318/201603_renewable-energy-promotion-plan.pdf)。</t>
         </is>
       </c>
-      <c r="S58" s="17" t="inlineStr">
+      <c r="S58" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T58" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
         </is>
       </c>
     </row>
@@ -19915,6 +21093,11 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T59" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n">
@@ -19988,9 +21171,14 @@
           <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず(村HP計画一覧 https://www.katsurao.org/life/3/17/52/ 参照)。第五次葛尾村振興計画(2023)、スマートコミュニティ事業あり。</t>
         </is>
       </c>
-      <c r="S60" s="17" t="inlineStr">
+      <c r="S60" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T60" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
         </is>
       </c>
     </row>
@@ -20066,9 +21254,14 @@
           <t>交通：町単独の地域公共交通計画は検索で確認できず、県全域の福島県地域公共交通計画(R6〜R12)が該当。環境：環境基本計画は検索で確認できず。新地町環境未来都市計画(H24.5策定、R7.1・R7.7・R8.7改定、https://future-city.go.jp/pdf/torikumi_city/shinchi_plan.pdf)、地球温暖化対策実行計画(事務事業編)(https://www.shinchi-town.jp/uploaded/attachment/7983.pdf)あり。</t>
         </is>
       </c>
-      <c r="S61" s="17" t="inlineStr">
+      <c r="S61" s="18" t="inlineStr">
         <is>
           <t>交通のみ調査</t>
+        </is>
+      </c>
+      <c r="T61" s="17" t="inlineStr">
+        <is>
+          <t>未掲載【当方は計画あり】</t>
         </is>
       </c>
     </row>
@@ -20149,10 +21342,15 @@
           <t>調査済</t>
         </is>
       </c>
+      <c r="T62" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S62"/>
-  <conditionalFormatting sqref="A4:S62">
+  <autoFilter ref="A3:T62"/>
+  <conditionalFormatting sqref="A4:T62">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>

--- a/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
+++ b/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
@@ -1602,15 +1602,15 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>R5〜R9</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>9</v>
+          <t>R5〜R10</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -1643,7 +1643,7 @@
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.6策定（パブコメR5.4.17〜5.16）。期間は検索結果で未確認のため5年と仮定した推定値（要確認）。R6.3に五所川原市地域公共交通推進計画（R6〜R10、確認済 https://www.city.goshogawara.lg.jp/jouhou/keikaku/files/koutuu_suisin.pdf）。H28.3網形成計画・H30.3再編実施計画あり。環境：環境基本計画は検索で見当たらず。代替として五所川原市地球温暖化対策実行計画（区域施策編）が存在する模様（https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/planR2_gaiyouban.pdf の可能性）。事務事業編相当は環境保全率先行動計画（H21〜H25）。</t>
+          <t>交通：R5.6策定（パブコメR5.4.17〜5.16）。期間は検索結果で未確認のため5年と仮定した推定値（要確認）。R6.3に五所川原市地域公共交通推進計画（R6〜R10、確認済 https://www.city.goshogawara.lg.jp/jouhou/keikaku/files/koutuu_suisin.pdf）。H28.3網形成計画・H30.3再編実施計画あり。環境：環境基本計画は検索で見当たらず。代替として五所川原市地球温暖化対策実行計画（区域施策編）が存在する模様（https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/planR2_gaiyouban.pdf の可能性）。事務事業編相当は環境保全率先行動計画（H21〜H25）。 【ファクトチェック 2026-10-01: 誤り】確認期間: R5〜R10（令和5年6月策定、令和10年度までの取組を定める）／次期: 確認できず（次期計画の策定支援業務・パブコメは見当たらず。概要版が gaiyouR7.1/R7.6/R8.1 と更新されており、R8.1時点で計画の変更あり）／根拠: https://www.city.goshogawara.lg.jp/kurashi/machi/files/suishinnkeikaku-gaiyou.ver.pdf</t>
         </is>
       </c>
       <c r="S8" s="18" t="inlineStr">
@@ -1726,7 +1726,7 @@
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：計画期間R5〜R9（5か年、検索結果で確認）。概要版 https://www.city.towada.lg.jp/kurashi/koutsu/files/gaiyouban.pdf 。策定支援業務仕様書 https://www.city.towada.lg.jp/kurashi/koutsu/files/shiyousyo.pdf あり（日付不明、現行計画策定時のものの可能性が高い。次期計画分かは要確認）。R9終了のため次期計画はR8〜R9に着手見込み。環境：環境基本計画は検索で見当たらず。R7.3に十和田市地球温暖化対策実行計画（区域施策編）策定（https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/keikakugaiyouban.pdf）。</t>
+          <t>交通：計画期間R5〜R9（5か年、検索結果で確認）。概要版 https://www.city.towada.lg.jp/kurashi/koutsu/files/gaiyouban.pdf 。策定支援業務仕様書 https://www.city.towada.lg.jp/kurashi/koutsu/files/shiyousyo.pdf あり（日付不明、現行計画策定時のものの可能性が高い。次期計画分かは要確認）。R9終了のため次期計画はR8〜R9に着手見込み。環境：環境基本計画は検索で見当たらず。R7.3に十和田市地球温暖化対策実行計画（区域施策編）策定（https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/keikakugaiyouban.pdf）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（2023〜2027年度）／次期: 確認できず（市サイト内検索で次期計画の策定支援プロポーザル・協議会審議は見当たらず。前回はR4年度にプロポーザル https://www.city.towada.lg.jp/kurashi/koutsuu/koutsuukeikaku.ht／根拠: https://www.city.towada.lg.jp/kurashi/koutsuu/files/keikaku.pdf</t>
         </is>
       </c>
       <c r="S9" s="18" t="inlineStr">
@@ -2238,7 +2238,7 @@
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>交通：策定支援業務プロポーザル2022-10（https://www.town.imabetsu.lg.jp/news/gyousei/2022-1017-1745-1.html）、計画公表ページ2023-08-28。期間は検索結果で未確認（R5〜R9推定）。JR津軽線蟹田〜三厩は2027年4月廃止・バス/乗合タクシー転換予定（NPO今別外ヶ浜交通）で計画見直しの可能性あり。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：策定支援業務プロポーザル2022-10（https://www.town.imabetsu.lg.jp/news/gyousei/2022-1017-1745-1.html）、計画公表ページ2023-08-28。期間は検索結果で未確認（R5〜R9推定）。JR津軽線蟹田〜三厩は2027年4月廃止・バス/乗合タクシー転換予定（NPO今別外ヶ浜交通）で計画見直しの可能性あり。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（5年間）／次期: 確認できず（次期計画の策定業務・アンケートは見当たらず。ただしJR津軽線蟹田以北について、代行バス・わんタク・町営バス等を統合した自動車交通を令和9年4月1日から運行予定（広報今別733号 https://www.town.imabetsu／根拠: https://www.town.imabetsu.lg.jp/gyousei/koukai/2023-0828-1639-1.html</t>
         </is>
       </c>
       <c r="S15" s="18" t="inlineStr">
@@ -2789,7 +2789,7 @@
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>町HP「大鰐町地域公共交通計画策定について」ページに計画PDF（ファイル名R5.5.pdf）掲載→R5.5策定と見られ、5年計画ならR5〜R9（期間は未確認・推定）。過去に計画案策定支援業務の公募型プロポーザル実施: http://www.town.owani.lg.jp/news/index.cfm/detail.1.12187.html （日付未確認）。弘南鉄道大鰐線は運行休止/廃止方向で交通再編の動きあり。環境基本計画・温対計画は検索で見当たらず。</t>
+          <t>町HP「大鰐町地域公共交通計画策定について」ページに計画PDF（ファイル名R5.5.pdf）掲載→R5.5策定と見られ、5年計画ならR5〜R9（期間は未確認・推定）。過去に計画案策定支援業務の公募型プロポーザル実施: http://www.town.owani.lg.jp/news/index.cfm/detail.1.12187.html （日付未確認）。弘南鉄道大鰐線は運行休止/廃止方向で交通再編の動きあり。環境基本計画・温対計画は検索で見当たらず。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず（関連: 弘南鉄道大鰐線は2028年3月末で運行休止と発表され、代替交通は県主催の検討会議で調整中 https://trafficnews.jp/post/592513）／根拠: http://www.town.owani.lg.jp/aboutowani/plan/kokyo-kotsu.html</t>
         </is>
       </c>
       <c r="S22" s="18" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="Q26" s="11" t="n"/>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>交通：計画書表紙「令和5年4月」、計画ページ https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 。ファイル名にr6とあり令和6年に改訂の可能性。期間は未確認で5年と仮定しR5〜R9推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：計画書表紙「令和5年4月」、計画ページ https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 。ファイル名にr6とあり令和6年に改訂の可能性。期間は未確認で5年と仮定しR5〜R9推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（町のプロポーザル一覧に交通計画関連は見当たらず）／根拠: https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html</t>
         </is>
       </c>
       <c r="S26" s="18" t="inlineStr">
@@ -5178,12 +5178,12 @@
           <t>H30〜R9</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="16" t="n">
         <v>9</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>確認済</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：網形成計画（H30〜）をR6.3に地域公共交通計画として策定、計画期間は2018〜2027年度（R9終期）、2028年度以降に見直し予定。計画ページ https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html 。次期計画の委託等は未確認。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：10年計画（R10以降に見直しとの記載あり）、正確な期間未確認。区域施策編改訂支援業務プロポーザルあり https://www.city.kuji.iwate.jp/assets/fukushi/siyousyo_ondankapropo.pdf 。</t>
+          <t>交通：網形成計画（H30〜）をR6.3に地域公共交通計画として策定、計画期間は2018〜2027年度（R9終期）、2028年度以降に見直し予定。計画ページ https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html 。次期計画の委託等は未確認。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：10年計画（R10以降に見直しとの記載あり）、正確な期間未確認。区域施策編改訂支援業務プロポーザルあり https://www.city.kuji.iwate.jp/assets/fukushi/siyousyo_ondankapropo.pdf 。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず／根拠: https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -8105,17 +8105,17 @@
           <t>R5〜R9（推定）</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="13" t="n">
         <v>9</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>着手済</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3策定（前身の網形成計画はH29.6）、計画ページ https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html 。期間は検索で確認できず5年と仮定しR9終期を推定→R9終期なら次期策定はR8〜R9着手見込み（有望・要確認）。環境：第3次計画と第3次温暖化対策実行計画をH31.4.23掲載、期間不明（10年ならR10頃終期）。広域：宮城県地域公共交通計画R8〜R14あり（県計画、検索要約より）。佐賀県白石町・千葉県白井市とは別。</t>
+          <t>交通：R5.3策定（前身の網形成計画はH29.6）、計画ページ https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html 。期間は検索で確認できず5年と仮定しR9終期を推定→R9終期なら次期策定はR8〜R9着手見込み（有望・要確認）。環境：第3次計画と第3次温暖化対策実行計画をH31.4.23掲載、期間不明（10年ならR10頃終期）。広域：宮城県地域公共交通計画R8〜R14あり（県計画、検索要約より）。佐賀県白石町・千葉県白井市とは別。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度〜令和9年度の5年間、R5.3策定）／次期: 着手済の可能性高：「白石市地域公共交通計画策定調査に係る公募型プロポーザル」（2026-07-14更新、募集終了）が市サイト まちづくり推進課/入札・契約情報に掲載（https://www.city.shiroishi.miyagi.jp/／根拠: https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html</t>
         </is>
       </c>
       <c r="S8" s="15" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3.28策定、R9終期。次期計画の策定業務・プロポーザルは検索で未確認。R8.8.25にR8年度名取市地域公共交通活性化推進協議会開催 https://www.city.natori.miyagi.jp/page/45227.html （次期計画の議題か要確認・有望）。計画ページ https://www.city.natori.miyagi.jp/page/4327.html 。環境：第二次計画の期間は検索で確認できず（R2開始10年ならR11終期と推定）。</t>
+          <t>交通：R5.3.28策定、R9終期。次期計画の策定業務・プロポーザルは検索で未確認。R8.8.25にR8年度名取市地域公共交通活性化推進協議会開催 https://www.city.natori.miyagi.jp/page/45227.html （次期計画の議題か要確認・有望）。計画ページ https://www.city.natori.miyagi.jp/page/4327.html 。環境：第二次計画の期間は検索で確認できず（R2開始10年ならR11終期と推定）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度の5ヶ年、R5.3.28策定）／次期: 確認できず（令和8年度協議会 R8.8.25開催の議題は『計画の取組状況について』のみ／https://www.city.natori.miyagi.jp/page/45227.html）／根拠: https://www.city.natori.miyagi.jp/page/4327.html</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="P4" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>着手済</t>
         </is>
       </c>
       <c r="Q4" s="14" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>交通：前計画（第3次公共交通政策ビジョン R3〜R7）の後継として第4次ビジョン（地域公共交通計画）R8.3策定。関連ページ https://www.city.akita.lg.jp/kurashi/kotsu/1007422/1028662.html 。環境：H30〜R9の10年計画、R4〜R5に中間見直し（パブコメR4.12〜R5.1）。R9終期のため次期計画はR8〜R9に策定見込みだが、着手（審議会・委託等）は検索で未確認（有望）。計画ページ https://www.city.akita.lg.jp/shisei/hoshin-keikaku/1009930/1006108.html</t>
+          <t>交通：前計画（第3次公共交通政策ビジョン R3〜R7）の後継として第4次ビジョン（地域公共交通計画）R8.3策定。関連ページ https://www.city.akita.lg.jp/kurashi/kotsu/1007422/1028662.html 。環境：H30〜R9の10年計画、R4〜R5に中間見直し（パブコメR4.12〜R5.1）。R9終期のため次期計画はR8〜R9に策定見込みだが、着手（審議会・委託等）は検索で未確認（有望）。計画ページ https://www.city.akita.lg.jp/shisei/hoshin-keikaku/1009930/1006108.html 【ファクトチェック 2026-10-01: 正しい】確認期間: H30〜R9（平成30年度〜令和9年度の10年間、R5.3中間見直し）／次期: 着手済：第45回秋田市環境審議会（令和8年3月24日）議題「秋田市環境基本計画の改定について」（資料1あり）https://www.city.akita.lg.jp/kurashi/recycle/1016631/1006116.html／根拠: https://www.city.akita.lg.jp/_res/projects/default_project/_page_/001/006/108/r2-1nenhoukoku.pdf</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>交通：R6.3策定（前計画は能代市地域公共交通網形成計画 H31.3策定）。市単独計画で能代山本広域の共同計画は確認できず。終期は検索で確認できず。環境：H30〜R9の10年計画、R5.3中間見直し（PDF https://www.city.noshiro.lg.jp/up/files/www/sangyo/kankyo/keikaku/keikaku_minaoshi_2nd.pdf ）。R9終期のため第3次計画はR8〜R9策定見込み、着手は未確認（有望）。環境基本計画懇談会の資料あり https://www.city.noshiro.lg.jp/up/files/www/sangyo/kankyo/keikaku/kondankai/1st/shiryo2_jokyo-kongo.pdf （開催時期未確認）。 R8.6に市民意識調査実施（https://www.city.noshiro.lg.jp/city/koho/ishiki-chosa/27883 、総合計画向けで環境計画専用ではない）。</t>
+          <t>交通：R6.3策定（前計画は能代市地域公共交通網形成計画 H31.3策定）。市単独計画で能代山本広域の共同計画は確認できず。終期は検索で確認できず。環境：H30〜R9の10年計画、R5.3中間見直し（PDF https://www.city.noshiro.lg.jp/up/files/www/sangyo/kankyo/keikaku/keikaku_minaoshi_2nd.pdf ）。R9終期のため第3次計画はR8〜R9策定見込み、着手は未確認（有望）。環境基本計画懇談会の資料あり https://www.city.noshiro.lg.jp/up/files/www/sangyo/kankyo/keikaku/kondankai/1st/shiryo2_jokyo-kongo.pdf （開催時期未確認）。 R8.6に市民意識調査実施（https://www.city.noshiro.lg.jp/city/koho/ishiki-chosa/27883 、総合計画向けで環境計画専用ではない）。 【ファクトチェック 2026-10-01: 正しい】確認期間: H30〜R9（平成30年度〜令和9年度の10年間、R5.3中間見直し）／次期: 確認できず／根拠: https://www.city.noshiro.lg.jp/sangyo/kankyo/keikaku/22091</t>
         </is>
       </c>
       <c r="S5" s="15" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>交通：H30.3策定の網形成計画（H30〜R9）をR6年度に地域公共交通計画へ名称変更・改定（R6.5『大館市地域公共交通網形成計画見直し業務』入札 https://nsearch.jp/nyusatsu_ankens/664c662d6a90d97d72380dee ）、R7.3/R7.8改定版PDFあり。R9(2027)終期のため次期計画策定はR8〜R9に着手見込みだが、策定業務プロポーザル等は検索で未確認（有望）。環境：第3次はR3.3パブコメを経て策定、期間は第2次(H23〜R2)の10年サイクルから推定。 R7.8改定版には『概ね10年後に見直し』との記載あり（計画期間はH30〜R9）。関連：大館市地域公共交通利便増進実施計画 https://www.mlit.go.jp/sogoseisaku/transport/content/001911965.pdf</t>
+          <t>交通：H30.3策定の網形成計画（H30〜R9）をR6年度に地域公共交通計画へ名称変更・改定（R6.5『大館市地域公共交通網形成計画見直し業務』入札 https://nsearch.jp/nyusatsu_ankens/664c662d6a90d97d72380dee ）、R7.3/R7.8改定版PDFあり。R9(2027)終期のため次期計画策定はR8〜R9に着手見込みだが、策定業務プロポーザル等は検索で未確認（有望）。環境：第3次はR3.3パブコメを経て策定、期間は第2次(H23〜R2)の10年サイクルから推定。 R7.8改定版には『概ね10年後に見直し』との記載あり（計画期間はH30〜R9）。関連：大館市地域公共交通利便増進実施計画 https://www.mlit.go.jp/sogoseisaku/transport/content/001911965.pdf 【ファクトチェック 2026-10-01: 正しい】確認期間: H30〜R9（2018年度～2027年度）／次期: 確認できず（R7に利便増進実施計画（2025～2027年度）を策定済。次期計画の策定業務・協議会審議は未確認）／根拠: https://www.city.odate.lg.jp/uploads/public/pages_0000011901_00/R07.8%E6%9C%88%E6%94%B9%E6%AD%A3.%E5%A4%A7%E9%A4%A8%E5%B8%82%E5%9C%B0%E5%9F%9F%E5%85%AC%E5%85%B1%E4%BA%A4%E8%A8%88%E7%94%BB_.pdf</t>
         </is>
       </c>
       <c r="S7" s="15" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>交通：R7.6改訂版（秋北バス一部路線廃止・八幡平地区再編 R7.10.1対応）。計画期間は検索結果で未確認だが、R4年度協議会で策定審議（資料 https://www.city.kazuno.lg.jp/material/files/group/8/shiryou3_R4_3.pdf ）→R5年度始期の5年計画（R5〜R9）と推定、要確認。協議会 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html 。環境：エネルギービジョン（R4.2）が第3次環境基本計画と終期を整合、R13年3月まで（=R12年度末）https://www.city.kazuno.lg.jp/material/files/group/14/energyvision.pdf 。e_urlは市の環境ページ（計画直リンク未取得）。</t>
+          <t>交通：R7.6改訂版（秋北バス一部路線廃止・八幡平地区再編 R7.10.1対応）。計画期間は検索結果で未確認だが、R4年度協議会で策定審議（資料 https://www.city.kazuno.lg.jp/material/files/group/8/shiryou3_R4_3.pdf ）→R5年度始期の5年計画（R5〜R9）と推定、要確認。協議会 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html 。環境：エネルギービジョン（R4.2）が第3次環境基本計画と終期を整合、R13年3月まで（=R12年度末）https://www.city.kazuno.lg.jp/material/files/group/14/energyvision.pdf 。e_urlは市の環境ページ（計画直リンク未取得）。 【ファクトチェック 2026-10-01: 確認できず】確認期間: R5〜R9（要約のみ）／次期: 確認できず／根拠: https://realtime-nippon.com/archives/052094230123001/</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -11857,15 +11857,15 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>H30〜R9</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="n">
-        <v>9</v>
+          <t>〜R8（H28またはH29〜R8の10年間）</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P14" s="13" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3（公表2024.3.29頃）策定、R5〜R9（網形成計画H30〜R4の後継）。市単独計画（上小阿仁村との共同計画は確認できず）。利便増進実施計画もあり https://www.city.kitaakita.akita.jp/news/p12935 。R9終期のため次期計画はR8〜R9に着手見込み、現時点で策定業務は未確認。R8年度県北地域部会資料あり https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会県北地域部会_会議概要.pdf 。環境：H30.4.1始期・R3改正（10年間ならR9終期、推定・要確認）。区域施策編も策定中/策定済（ゼロカーボン宣言R6.2.15）。</t>
+          <t>交通：R5.3（公表2024.3.29頃）策定、R5〜R9（網形成計画H30〜R4の後継）。市単独計画（上小阿仁村との共同計画は確認できず）。利便増進実施計画もあり https://www.city.kitaakita.akita.jp/news/p12935 。R9終期のため次期計画はR8〜R9に着手見込み、現時点で策定業務は未確認。R8年度県北地域部会資料あり https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会県北地域部会_会議概要.pdf 。環境：H30.4.1始期・R3改正（10年間ならR9終期、推定・要確認）。区域施策編も策定中/策定済（ゼロカーボン宣言R6.2.15）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず／根拠: https://www.city.kitaakita.akita.jp/news/p15700 【ファクトチェック 2026-10-01: 誤り】確認期間: 〜R8（「平成28年度から令和8年度までの10年間」と要約。10年間ならH29〜R8の可能性）／次期: 確認できず（終期R8＝今年度のため次期計画策定が進行中の可能性が高いが、策定業務公告・審議会・アンケートは検索で見つからず）／根拠: https://www.city.kitaakita.akita.jp/archive/p13109</t>
         </is>
       </c>
       <c r="S14" s="15" t="inlineStr">
@@ -12538,7 +12538,7 @@
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>交通：南秋地域公共交通活性化協議会（五城目・八郎潟・大潟）が策定、R5〜R9でR9終期→次期はR8〜R9に着手見込み（着手情報は未確認）。計画案PDF https://www.town.gojome.akita.jp/up/files/town/machikeikaku/koutuukeikaku.pdf 。別途、町単独の五城目町地域公共交通計画（R4〜R8、R4.5策定）https://www.town.gojome.akita.jp/town/sosikiannai/machi/matiduku/1734 もあり、R8終期（次期は未確認）。環境：環境基本計画は確認できず。地球温暖化対策実行計画（事務事業編）のみ確認。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。</t>
+          <t>交通：南秋地域公共交通活性化協議会（五城目・八郎潟・大潟）が策定、R5〜R9でR9終期→次期はR8〜R9に着手見込み（着手情報は未確認）。計画案PDF https://www.town.gojome.akita.jp/up/files/town/machikeikaku/koutuukeikaku.pdf 。別途、町単独の五城目町地域公共交通計画（R4〜R8、R4.5策定）https://www.town.gojome.akita.jp/town/sosikiannai/machi/matiduku/1734 もあり、R8終期（次期は未確認）。環境：環境基本計画は確認できず。地球温暖化対策実行計画（事務事業編）のみ確認。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度、5年間）／次期: 確認できず（協議会での次期計画審議・策定業務の公告は検索で見つからず）／根拠: https://www.town.gojome.akita.jp/kurashi/koukyoukoutsu/2085</t>
         </is>
       </c>
       <c r="S22" s="15" t="inlineStr">
@@ -12621,7 +12621,7 @@
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>交通：南秋地域公共交通計画はR5.6策定（東北運輸局資料で確認）。井川町は含まれない。計画期間R5〜R9（五城目町サイトで確認、計画案PDF https://www.town.gojome.akita.jp/up/files/town/machikeikaku/koutuukeikaku.pdf ）。東北運輸局資料 https://wwwtb.mlit.go.jp/tohoku/content/000305851.pdf 。環境：町独自の環境基本計画は検索で見当たらず。【県計画】秋田県地域公共交通計画はR4〜R8（R4.3策定、R8＝今年度終期）。R8.6.23の令和8年度第1回秋田県地域公共交通活性化協議会で県計画の策定（次期計画）を議論 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf</t>
+          <t>交通：南秋地域公共交通計画はR5.6策定（東北運輸局資料で確認）。井川町は含まれない。計画期間R5〜R9（五城目町サイトで確認、計画案PDF https://www.town.gojome.akita.jp/up/files/town/machikeikaku/koutuukeikaku.pdf ）。東北運輸局資料 https://wwwtb.mlit.go.jp/tohoku/content/000305851.pdf 。環境：町独自の環境基本計画は検索で見当たらず。【県計画】秋田県地域公共交通計画はR4〜R8（R4.3策定、R8＝今年度終期）。R8.6.23の令和8年度第1回秋田県地域公共交通活性化協議会で県計画の策定（次期計画）を議論 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度、5年間）／次期: 確認できず（協議会での次期計画審議・策定業務の公告は検索で見つからず）／根拠: https://www.town.gojome.akita.jp/kurashi/koukyoukoutsu/2085</t>
         </is>
       </c>
       <c r="S23" s="15" t="inlineStr">
@@ -12787,7 +12787,7 @@
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>交通：八郎潟町と同じ南秋地域公共交通計画（R5.6策定）。期間R5〜R9（五城目町サイトで確認）。環境：村独自の環境基本計画は検索で見当たらず。大潟村は環境省の脱炭素先行地域（メガソーラー・地域エネルギー会社等） https://www.env.go.jp/content/900512579.pdf 。第3次大潟村振興計画に「自然にやさしい環境の創造」あり。</t>
+          <t>交通：八郎潟町と同じ南秋地域公共交通計画（R5.6策定）。期間R5〜R9（五城目町サイトで確認）。環境：村独自の環境基本計画は検索で見当たらず。大潟村は環境省の脱炭素先行地域（メガソーラー・地域エネルギー会社等） https://www.env.go.jp/content/900512579.pdf 。第3次大潟村振興計画に「自然にやさしい環境の創造」あり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度、5年間）／次期: 確認できず（協議会での次期計画審議・策定業務の公告は検索で見つからず）／根拠: https://www.town.gojome.akita.jp/kurashi/koukyoukoutsu/2085</t>
         </is>
       </c>
       <c r="S25" s="15" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>環境：H30〜R9（2027）の10年計画で終期R9。次期（第3次）策定の着手は未確認（R8〜R9に着手見込み・営業対象）。交通：市単独計画は見当たらず（市営バス・乗合タクシー運行）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。</t>
+          <t>環境：H30〜R9（2027）の10年計画で終期R9。次期（第3次）策定の着手は未確認（R8〜R9に着手見込み・営業対象）。交通：市単独計画は見当たらず（市営バス・乗合タクシー運行）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 【ファクトチェック 2026-10-01: 正しい】確認期間: H30〜R9（平成30年度〜平成39年度）／次期: 確認できず（市サイト内で第3次計画・アンケート等の情報見当たらず）／根拠: https://www.city.murayama.lg.jp/kurashi/shizen/kankyohozen/kankyoukihon.files/kankyou-2.pdf</t>
         </is>
       </c>
       <c r="S11" s="15" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>環境：H30.3策定（第1次H23.3、見直し版あり）。第6次総合発展計画（H30〜R9の10年）と同期間とみられR9終期（計画書本文での期間記載は未確認）。次期計画着手は未確認・営業候補。交通：町単独の法定計画は見当たらず（旧・地域公共交通総合連携計画H22.3、H30活性化協議会設置）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。</t>
+          <t>環境：H30.3策定（第1次H23.3、見直し版あり）。第6次総合発展計画（H30〜R9の10年）と同期間とみられR9終期（計画書本文での期間記載は未確認）。次期計画着手は未確認・営業候補。交通：町単独の法定計画は見当たらず（旧・地域公共交通総合連携計画H22.3、H30活性化協議会設置）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 【ファクトチェック 2026-10-01: 正しい】確認期間: H30〜R9（2018〜2027年度）／次期: 確認できず（第3次計画の情報なし）／根拠: https://www.town.asahi.yamagata.jp/portal/soshikinogoannai/somuka/bosaigakari/3_1/3/2438.html</t>
         </is>
       </c>
       <c r="S21" s="15" t="inlineStr">
@@ -16519,11 +16519,11 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>R5〜R9</t>
+          <t>R5〜R12（県計画に準拠）</t>
         </is>
       </c>
       <c r="H4" s="13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="R4" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3策定、最終年度2027(R9)。R7.2.26に計画改定資料あり（一部改定）https://www.city.fukushima.fukushima.jp/material/files/group/62/20250226koutuukeikakukaitei1-3.pdf 。R7.10.3協議会で県北圏域地域公共交通利便増進実施計画の変更協議。R9終期のため次期計画策定はR8〜R9に着手見込み。環境：R7(2025)終期、2026年度からの第4次計画策定を環境審議会で審議開始（R7.6.23報道資料 https://www.city.fukushima.fukushima.jp/material/files/group/3/press2025-06-23-3.pdf）。第4次の策定完了は未確認。</t>
+          <t>交通：R5.3策定、最終年度2027(R9)。R7.2.26に計画改定資料あり（一部改定）https://www.city.fukushima.fukushima.jp/material/files/group/62/20250226koutuukeikakukaitei1-3.pdf 。R7.10.3協議会で県北圏域地域公共交通利便増進実施計画の変更協議。R9終期のため次期計画策定はR8〜R9に着手見込み。環境：R7(2025)終期、2026年度からの第4次計画策定を環境審議会で審議開始（R7.6.23報道資料 https://www.city.fukushima.fukushima.jp/material/files/group/3/press2025-06-23-3.pdf）。第4次の策定完了は未確認。 【ファクトチェック 2026-10-01: 誤り】確認期間: R5〜R12（2023〜2030年度、8年間）／次期: 該当なし（終期R12のため次期計画は当面なし）／根拠: https://www.city.fukushima.fukushima.jp/material/files/group/62/40koutuukeikaku-honnpenn1.pdf</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3策定、計画期間「概ね5年間」（R9終期は推定）。R7.1.20第15回いわき都市圏総合都市交通推進協議会で計画改定を協議（一部改定）。次期計画策定の着手は検索で確認できず（R9終期のため要注視）。概要版 https://www.city.iwaki.lg.jp/www/contents/1679296597893/simple/gaiyouban.pdf 。環境：第三次R3〜R12（R3.3策定）、R6〜R7で中間の一部改定を実施、改定版の期間R8〜R12（概要gaiyo.pdf）。</t>
+          <t>交通：R5.3策定、計画期間「概ね5年間」（R9終期は推定）。R7.1.20第15回いわき都市圏総合都市交通推進協議会で計画改定を協議（一部改定）。次期計画策定の着手は検索で確認できず（R9終期のため要注視）。概要版 https://www.city.iwaki.lg.jp/www/contents/1679296597893/simple/gaiyouban.pdf 。環境：第三次R3〜R12（R3.3策定）、R6〜R7で中間の一部改定を実施、改定版の期間R8〜R12（概要gaiyo.pdf）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年3月〜令和10年3月、概ね5年間）／次期: 確認できず（次期計画策定業務・協議会での審議情報は見当たらず）／根拠: https://www.city.iwaki.lg.jp/www/contents/1679296597893/index.html</t>
         </is>
       </c>
       <c r="S7" s="15" t="inlineStr">
@@ -19913,7 +19913,7 @@
       <c r="Q45" s="11" t="n"/>
       <c r="R45" s="11" t="inlineStr">
         <is>
-          <t>交通計画はR5.2.21協議会で策定、デマンド交通導入を位置付け。R9年度末で満了→R8〜R9に次期計画検討が見込まれる。R7年度協議会会議録が村HP（上記協議会ページ）に公開、次期計画への言及は未確認。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。（バイオマスヴィレッジ構想・公害対策条例のみ確認）</t>
+          <t>交通計画はR5.2.21協議会で策定、デマンド交通導入を位置付け。R9年度末で満了→R8〜R9に次期計画検討が見込まれる。R7年度協議会会議録が村HP（上記協議会ページ）に公開、次期計画への言及は未確認。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。（バイオマスヴィレッジ構想・公害対策条例のみ確認） 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（R7年度第1回協議会資料は公開されているが次期計画の記載は確認できず）／根拠: https://www.vill.samegawa.fukushima.jp/sp/page/page002592.html</t>
         </is>
       </c>
       <c r="S45" s="18" t="inlineStr">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="R53" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：広野町環境基本計画をR7.3策定(計画期間R7〜R17の11年間、R12に必要に応じ見直し)(PDF https://www.town.hirono.fukushima.jp/_res/projects/default_project/_page_/001/005/075/kankyokihonkeikaku.pdf)。他に地球温暖化対策実行計画(事務事業編・区域施策編、R5〜R12)、ゼロカーボンビジョンあり。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：広野町環境基本計画をR7.3策定(計画期間R7〜R17の11年間、R12に必要に応じ見直し)(PDF https://www.town.hirono.fukushima.jp/_res/projects/default_project/_page_/001/005/075/kankyokihonkeikaku.pdf)。他に地球温暖化対策実行計画(事務事業編・区域施策編、R5〜R12)、ゼロカーボンビジョンあり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S53" s="15" t="inlineStr">
@@ -20670,7 +20670,7 @@
       <c r="Q54" s="11" t="n"/>
       <c r="R54" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替として楢葉町ゼロカーボンビジョン(R5.3策定、区域施策編＋地域気候変動適応計画を兼ねる)(https://www.town.naraha.lg.jp/life/cat309/cat331/008538.html)。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替として楢葉町ゼロカーボンビジョン(R5.3策定、区域施策編＋地域気候変動適応計画を兼ねる)(https://www.town.naraha.lg.jp/life/cat309/cat331/008538.html)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S54" s="15" t="inlineStr">
@@ -20753,7 +20753,7 @@
       <c r="Q55" s="11" t="n"/>
       <c r="R55" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず（復興推進計画のみ）。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず（復興推進計画のみ）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S55" s="15" t="inlineStr">
@@ -20836,7 +20836,7 @@
       <c r="Q56" s="11" t="n"/>
       <c r="R56" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。村HPで脱炭素ビジョン策定業務および「地球温暖化対策実行計画(区域施策編)策定業務委託」の公募型プロポーザル実施の記載あり(時期未確認、https://www.kawauchimura.jp/)。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。村HPで脱炭素ビジョン策定業務および「地球温暖化対策実行計画(区域施策編)策定業務委託」の公募型プロポーザル実施の記載あり(時期未確認、https://www.kawauchimura.jp/)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S56" s="18" t="inlineStr">
@@ -20919,7 +20919,7 @@
       <c r="Q57" s="11" t="n"/>
       <c r="R57" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替として大熊町ゼロカーボンビジョン(R3.2策定、区域施策編に位置付け、R3〜R32、Ver.3 R5.3 https://www.town.okuma.fukushima.jp/uploaded/attachment/8103.pdf)、ゼロカーボン推進ロードマップあり(https://www.town.okuma.fukushima.jp/site/zerocarbon/24388.html)。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替として大熊町ゼロカーボンビジョン(R3.2策定、区域施策編に位置付け、R3〜R32、Ver.3 R5.3 https://www.town.okuma.fukushima.jp/uploaded/attachment/8103.pdf)、ゼロカーボン推進ロードマップあり(https://www.town.okuma.fukushima.jp/site/zerocarbon/24388.html)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S57" s="15" t="inlineStr">
@@ -21002,7 +21002,7 @@
       <c r="Q58" s="11" t="n"/>
       <c r="R58" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。双葉町再生可能エネルギー活用・推進計画(H28.3)あり(https://www.town.fukushima-futaba.lg.jp/secure/7318/201603_renewable-energy-promotion-plan.pdf)。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。双葉町再生可能エネルギー活用・推進計画(H28.3)あり(https://www.town.fukushima-futaba.lg.jp/secure/7318/201603_renewable-energy-promotion-plan.pdf)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S58" s="18" t="inlineStr">
@@ -21085,7 +21085,7 @@
       <c r="Q59" s="11" t="n"/>
       <c r="R59" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず（復興計画・里山再生等のみ）。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず（復興計画・里山再生等のみ）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S59" s="15" t="inlineStr">
@@ -21168,7 +21168,7 @@
       <c r="Q60" s="11" t="n"/>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず(村HP計画一覧 https://www.katsurao.org/life/3/17/52/ 参照)。第五次葛尾村振興計画(2023)、スマートコミュニティ事業あり。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず(村HP計画一覧 https://www.katsurao.org/life/3/17/52/ 参照)。第五次葛尾村振興計画(2023)、スマートコミュニティ事業あり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S60" s="18" t="inlineStr">
@@ -21334,7 +21334,7 @@
       <c r="Q62" s="11" t="n"/>
       <c r="R62" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替としてゼロカーボンビレッジいいたて実行計画(R6.3策定、区域施策編目標年2030)(https://www.vill.iitate.fukushima.jp/life/5/20/126/)、同事務事業編(R7〜R12)あり。</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。代替としてゼロカーボンビレッジいいたて実行計画(R6.3策定、区域施策編目標年2030)(https://www.vill.iitate.fukushima.jp/life/5/20/126/)、同事務事業編(R7〜R12)あり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
         </is>
       </c>
       <c r="S62" s="15" t="inlineStr">

--- a/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
+++ b/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
@@ -16,6 +16,8 @@
     <sheet name="福島県" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="TGT_MIN">'集計・設定'!$C$4</definedName>
+    <definedName name="TGT_MAX">'集計・設定'!$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'青森県'!$A$3:$T$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'岩手県'!$A$3:$T$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'宮城県'!$A$3:$T$38</definedName>
@@ -186,7 +188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -212,6 +214,27 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0063BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F4B183"/>
         </patternFill>
       </fill>
     </dxf>
@@ -616,7 +639,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>R8年度で終わる計画は作成中のため対象外（下限9）。数字を変えると全シートの判定が再計算されます。</t>
+          <t>▼プルダウンで選ぶと全シートの判定（◎）と終期セルの色が切り替わります。例：R10年度に終わる計画も見る→上限を10に／R10だけ見る→下限・上限とも10に。</t>
         </is>
       </c>
     </row>
@@ -629,6 +652,11 @@
       <c r="C5" s="4" t="n">
         <v>9</v>
       </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>R8年度で終わる計画は作成中のため対象外（初期値は下限9・上限9）。終期セルの色：緑＝対象年度、橙＝上限の翌年度（次の営業候補）。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1053,6 +1081,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C4 C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"7,8,9,10,11,12,13,14,15"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1096,10 +1129,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -1218,11 +1250,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -1311,11 +1343,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1404,11 +1436,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1497,11 +1529,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1588,11 +1620,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -1671,11 +1703,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1754,11 +1786,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -1845,11 +1877,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1928,11 +1960,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="n"/>
@@ -2009,11 +2041,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -2100,11 +2132,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -2183,11 +2215,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2200,12 +2232,12 @@
           <t>R5〜R9</t>
         </is>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="13" t="n">
         <v>9</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
@@ -2266,11 +2298,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="n"/>
@@ -2339,11 +2371,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -2422,11 +2454,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -2505,11 +2537,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2588,11 +2620,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -2661,11 +2693,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -2734,11 +2766,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -2817,11 +2849,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -2890,11 +2922,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -2963,11 +2995,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -3036,11 +3068,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -3053,12 +3085,12 @@
           <t>R5〜R9</t>
         </is>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="13" t="n">
         <v>9</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr">
@@ -3119,11 +3151,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -3192,11 +3224,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -3273,11 +3305,11 @@
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;='集計・設定'!$C$4,H29&lt;='集計・設定'!$C$5),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;='集計・設定'!$C$4,N29&lt;='集計・設定'!$C$5),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -3346,11 +3378,11 @@
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;='集計・設定'!$C$4,H30&lt;='集計・設定'!$C$5),IF(J30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;=TGT_MIN,H30&lt;=TGT_MAX),IF(J30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;='集計・設定'!$C$4,N30&lt;='集計・設定'!$C$5),IF(P30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;=TGT_MIN,N30&lt;=TGT_MAX),IF(P30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -3419,11 +3451,11 @@
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;='集計・設定'!$C$4,H31&lt;='集計・設定'!$C$5),IF(J31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;=TGT_MIN,H31&lt;=TGT_MAX),IF(J31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;='集計・設定'!$C$4,N31&lt;='集計・設定'!$C$5),IF(P31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -3492,11 +3524,11 @@
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;='集計・設定'!$C$4,H32&lt;='集計・設定'!$C$5),IF(J32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;=TGT_MIN,H32&lt;=TGT_MAX),IF(J32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;='集計・設定'!$C$4,N32&lt;='集計・設定'!$C$5),IF(P32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;=TGT_MIN,N32&lt;=TGT_MAX),IF(P32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -3573,11 +3605,11 @@
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;='集計・設定'!$C$4,H33&lt;='集計・設定'!$C$5),IF(J33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;=TGT_MIN,H33&lt;=TGT_MAX),IF(J33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;='集計・設定'!$C$4,N33&lt;='集計・設定'!$C$5),IF(P33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3656,11 +3688,11 @@
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;='集計・設定'!$C$4,H34&lt;='集計・設定'!$C$5),IF(J34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;=TGT_MIN,H34&lt;=TGT_MAX),IF(J34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;='集計・設定'!$C$4,N34&lt;='集計・設定'!$C$5),IF(P34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;=TGT_MIN,N34&lt;=TGT_MAX),IF(P34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -3739,11 +3771,11 @@
         <v/>
       </c>
       <c r="D35" s="13">
-        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;='集計・設定'!$C$4,H35&lt;='集計・設定'!$C$5),IF(J35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;=TGT_MIN,H35&lt;=TGT_MAX),IF(J35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;='集計・設定'!$C$4,N35&lt;='集計・設定'!$C$5),IF(P35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;=TGT_MIN,N35&lt;=TGT_MAX),IF(P35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3822,11 +3854,11 @@
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;='集計・設定'!$C$4,H36&lt;='集計・設定'!$C$5),IF(J36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;=TGT_MIN,H36&lt;=TGT_MAX),IF(J36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;='集計・設定'!$C$4,N36&lt;='集計・設定'!$C$5),IF(P36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;=TGT_MIN,N36&lt;=TGT_MAX),IF(P36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -3905,11 +3937,11 @@
         <v/>
       </c>
       <c r="D37" s="13">
-        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;='集計・設定'!$C$4,H37&lt;='集計・設定'!$C$5),IF(J37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;=TGT_MIN,H37&lt;=TGT_MAX),IF(J37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;='集計・設定'!$C$4,N37&lt;='集計・設定'!$C$5),IF(P37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;=TGT_MIN,N37&lt;=TGT_MAX),IF(P37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3988,11 +4020,11 @@
         <v/>
       </c>
       <c r="D38" s="13">
-        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;='集計・設定'!$C$4,H38&lt;='集計・設定'!$C$5),IF(J38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;=TGT_MIN,H38&lt;=TGT_MAX),IF(J38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;='集計・設定'!$C$4,N38&lt;='集計・設定'!$C$5),IF(P38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;=TGT_MIN,N38&lt;=TGT_MAX),IF(P38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -4071,11 +4103,11 @@
         <v/>
       </c>
       <c r="D39" s="13">
-        <f>IF(J39="計画なし","－",IF(J39="策定済","✕",IF(H39="","？",IF(AND(H39&gt;='集計・設定'!$C$4,H39&lt;='集計・設定'!$C$5),IF(J39="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J39="計画なし","－",IF(J39="策定済","✕",IF(H39="","？",IF(AND(H39&gt;=TGT_MIN,H39&lt;=TGT_MAX),IF(J39="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E39" s="13">
-        <f>IF(P39="計画なし","－",IF(P39="策定済","✕",IF(N39="","？",IF(AND(N39&gt;='集計・設定'!$C$4,N39&lt;='集計・設定'!$C$5),IF(P39="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P39="計画なし","－",IF(P39="策定済","✕",IF(N39="","？",IF(AND(N39&gt;=TGT_MIN,N39&lt;=TGT_MAX),IF(P39="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -4154,11 +4186,11 @@
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>IF(J40="計画なし","－",IF(J40="策定済","✕",IF(H40="","？",IF(AND(H40&gt;='集計・設定'!$C$4,H40&lt;='集計・設定'!$C$5),IF(J40="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J40="計画なし","－",IF(J40="策定済","✕",IF(H40="","？",IF(AND(H40&gt;=TGT_MIN,H40&lt;=TGT_MAX),IF(J40="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>IF(P40="計画なし","－",IF(P40="策定済","✕",IF(N40="","？",IF(AND(N40&gt;='集計・設定'!$C$4,N40&lt;='集計・設定'!$C$5),IF(P40="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P40="計画なし","－",IF(P40="策定済","✕",IF(N40="","？",IF(AND(N40&gt;=TGT_MIN,N40&lt;=TGT_MAX),IF(P40="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -4237,11 +4269,11 @@
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>IF(J41="計画なし","－",IF(J41="策定済","✕",IF(H41="","？",IF(AND(H41&gt;='集計・設定'!$C$4,H41&lt;='集計・設定'!$C$5),IF(J41="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J41="計画なし","－",IF(J41="策定済","✕",IF(H41="","？",IF(AND(H41&gt;=TGT_MIN,H41&lt;=TGT_MAX),IF(J41="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>IF(P41="計画なし","－",IF(P41="策定済","✕",IF(N41="","？",IF(AND(N41&gt;='集計・設定'!$C$4,N41&lt;='集計・設定'!$C$5),IF(P41="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P41="計画なし","－",IF(P41="策定済","✕",IF(N41="","？",IF(AND(N41&gt;=TGT_MIN,N41&lt;=TGT_MAX),IF(P41="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -4320,11 +4352,11 @@
         <v/>
       </c>
       <c r="D42" s="13">
-        <f>IF(J42="計画なし","－",IF(J42="策定済","✕",IF(H42="","？",IF(AND(H42&gt;='集計・設定'!$C$4,H42&lt;='集計・設定'!$C$5),IF(J42="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J42="計画なし","－",IF(J42="策定済","✕",IF(H42="","？",IF(AND(H42&gt;=TGT_MIN,H42&lt;=TGT_MAX),IF(J42="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E42" s="13">
-        <f>IF(P42="計画なし","－",IF(P42="策定済","✕",IF(N42="","？",IF(AND(N42&gt;='集計・設定'!$C$4,N42&lt;='集計・設定'!$C$5),IF(P42="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P42="計画なし","－",IF(P42="策定済","✕",IF(N42="","？",IF(AND(N42&gt;=TGT_MIN,N42&lt;=TGT_MAX),IF(P42="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -4403,11 +4435,11 @@
         <v/>
       </c>
       <c r="D43" s="13">
-        <f>IF(J43="計画なし","－",IF(J43="策定済","✕",IF(H43="","？",IF(AND(H43&gt;='集計・設定'!$C$4,H43&lt;='集計・設定'!$C$5),IF(J43="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J43="計画なし","－",IF(J43="策定済","✕",IF(H43="","？",IF(AND(H43&gt;=TGT_MIN,H43&lt;=TGT_MAX),IF(J43="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E43" s="13">
-        <f>IF(P43="計画なし","－",IF(P43="策定済","✕",IF(N43="","？",IF(AND(N43&gt;='集計・設定'!$C$4,N43&lt;='集計・設定'!$C$5),IF(P43="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P43="計画なし","－",IF(P43="策定済","✕",IF(N43="","？",IF(AND(N43&gt;=TGT_MIN,N43&lt;=TGT_MAX),IF(P43="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -4475,17 +4507,33 @@
   </sheetData>
   <autoFilter ref="A3:T43"/>
   <conditionalFormatting sqref="A4:T43">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H43">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N43">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -4574,10 +4622,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -4696,11 +4743,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -4789,11 +4836,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -4882,11 +4929,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -4975,11 +5022,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -5068,11 +5115,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -5161,11 +5208,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -5252,11 +5299,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -5343,11 +5390,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -5436,11 +5483,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -5519,11 +5566,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -5612,11 +5659,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -5693,11 +5740,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -5786,11 +5833,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -5879,11 +5926,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -5972,11 +6019,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -6063,11 +6110,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -6136,11 +6183,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -6219,11 +6266,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -6306,11 +6353,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -6389,11 +6436,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -6470,11 +6517,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -6553,11 +6600,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -6636,11 +6683,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -6727,11 +6774,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -6810,11 +6857,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -6891,11 +6938,11 @@
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;='集計・設定'!$C$4,H29&lt;='集計・設定'!$C$5),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;='集計・設定'!$C$4,N29&lt;='集計・設定'!$C$5),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -6974,11 +7021,11 @@
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;='集計・設定'!$C$4,H30&lt;='集計・設定'!$C$5),IF(J30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;=TGT_MIN,H30&lt;=TGT_MAX),IF(J30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;='集計・設定'!$C$4,N30&lt;='集計・設定'!$C$5),IF(P30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;=TGT_MIN,N30&lt;=TGT_MAX),IF(P30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -7063,11 +7110,11 @@
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;='集計・設定'!$C$4,H31&lt;='集計・設定'!$C$5),IF(J31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;=TGT_MIN,H31&lt;=TGT_MAX),IF(J31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;='集計・設定'!$C$4,N31&lt;='集計・設定'!$C$5),IF(P31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -7136,11 +7183,11 @@
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;='集計・設定'!$C$4,H32&lt;='集計・設定'!$C$5),IF(J32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;=TGT_MIN,H32&lt;=TGT_MAX),IF(J32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;='集計・設定'!$C$4,N32&lt;='集計・設定'!$C$5),IF(P32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;=TGT_MIN,N32&lt;=TGT_MAX),IF(P32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -7209,11 +7256,11 @@
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;='集計・設定'!$C$4,H33&lt;='集計・設定'!$C$5),IF(J33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;=TGT_MIN,H33&lt;=TGT_MAX),IF(J33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;='集計・設定'!$C$4,N33&lt;='集計・設定'!$C$5),IF(P33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -7282,11 +7329,11 @@
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;='集計・設定'!$C$4,H34&lt;='集計・設定'!$C$5),IF(J34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;=TGT_MIN,H34&lt;=TGT_MAX),IF(J34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;='集計・設定'!$C$4,N34&lt;='集計・設定'!$C$5),IF(P34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;=TGT_MIN,N34&lt;=TGT_MAX),IF(P34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -7363,11 +7410,11 @@
         <v/>
       </c>
       <c r="D35" s="13">
-        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;='集計・設定'!$C$4,H35&lt;='集計・設定'!$C$5),IF(J35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;=TGT_MIN,H35&lt;=TGT_MAX),IF(J35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;='集計・設定'!$C$4,N35&lt;='集計・設定'!$C$5),IF(P35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;=TGT_MIN,N35&lt;=TGT_MAX),IF(P35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -7446,11 +7493,11 @@
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;='集計・設定'!$C$4,H36&lt;='集計・設定'!$C$5),IF(J36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;=TGT_MIN,H36&lt;=TGT_MAX),IF(J36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;='集計・設定'!$C$4,N36&lt;='集計・設定'!$C$5),IF(P36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;=TGT_MIN,N36&lt;=TGT_MAX),IF(P36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F36" s="11" t="n"/>
@@ -7508,17 +7555,33 @@
   </sheetData>
   <autoFilter ref="A3:T36"/>
   <conditionalFormatting sqref="A4:T36">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H36">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N36">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -7614,10 +7677,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -7736,11 +7798,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -7829,11 +7891,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -7922,11 +7984,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="n"/>
@@ -8005,11 +8067,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -8088,11 +8150,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -8179,11 +8241,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -8270,11 +8332,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -8355,11 +8417,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -8442,11 +8504,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -8535,11 +8597,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -8628,11 +8690,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -8717,11 +8779,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -8810,11 +8872,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -8903,11 +8965,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -8986,11 +9048,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -9079,11 +9141,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -9152,11 +9214,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -9237,11 +9299,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -9310,11 +9372,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -9401,11 +9463,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -9482,11 +9544,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -9565,11 +9627,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -9656,11 +9718,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -9739,11 +9801,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -9812,11 +9874,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -9885,11 +9947,11 @@
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;='集計・設定'!$C$4,H29&lt;='集計・設定'!$C$5),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;='集計・設定'!$C$4,N29&lt;='集計・設定'!$C$5),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -9966,11 +10028,11 @@
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;='集計・設定'!$C$4,H30&lt;='集計・設定'!$C$5),IF(J30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;=TGT_MIN,H30&lt;=TGT_MAX),IF(J30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;='集計・設定'!$C$4,N30&lt;='集計・設定'!$C$5),IF(P30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;=TGT_MIN,N30&lt;=TGT_MAX),IF(P30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -10059,11 +10121,11 @@
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;='集計・設定'!$C$4,H31&lt;='集計・設定'!$C$5),IF(J31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;=TGT_MIN,H31&lt;=TGT_MAX),IF(J31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;='集計・設定'!$C$4,N31&lt;='集計・設定'!$C$5),IF(P31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -10132,11 +10194,11 @@
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;='集計・設定'!$C$4,H32&lt;='集計・設定'!$C$5),IF(J32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;=TGT_MIN,H32&lt;=TGT_MAX),IF(J32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;='集計・設定'!$C$4,N32&lt;='集計・設定'!$C$5),IF(P32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;=TGT_MIN,N32&lt;=TGT_MAX),IF(P32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -10205,11 +10267,11 @@
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;='集計・設定'!$C$4,H33&lt;='集計・設定'!$C$5),IF(J33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;=TGT_MIN,H33&lt;=TGT_MAX),IF(J33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;='集計・設定'!$C$4,N33&lt;='集計・設定'!$C$5),IF(P33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -10278,11 +10340,11 @@
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;='集計・設定'!$C$4,H34&lt;='集計・設定'!$C$5),IF(J34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;=TGT_MIN,H34&lt;=TGT_MAX),IF(J34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;='集計・設定'!$C$4,N34&lt;='集計・設定'!$C$5),IF(P34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;=TGT_MIN,N34&lt;=TGT_MAX),IF(P34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -10361,11 +10423,11 @@
         <v/>
       </c>
       <c r="D35" s="13">
-        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;='集計・設定'!$C$4,H35&lt;='集計・設定'!$C$5),IF(J35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;=TGT_MIN,H35&lt;=TGT_MAX),IF(J35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;='集計・設定'!$C$4,N35&lt;='集計・設定'!$C$5),IF(P35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;=TGT_MIN,N35&lt;=TGT_MAX),IF(P35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -10444,11 +10506,11 @@
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;='集計・設定'!$C$4,H36&lt;='集計・設定'!$C$5),IF(J36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;=TGT_MIN,H36&lt;=TGT_MAX),IF(J36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;='集計・設定'!$C$4,N36&lt;='集計・設定'!$C$5),IF(P36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;=TGT_MIN,N36&lt;=TGT_MAX),IF(P36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F36" s="11" t="n"/>
@@ -10517,11 +10579,11 @@
         <v/>
       </c>
       <c r="D37" s="13">
-        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;='集計・設定'!$C$4,H37&lt;='集計・設定'!$C$5),IF(J37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;=TGT_MIN,H37&lt;=TGT_MAX),IF(J37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;='集計・設定'!$C$4,N37&lt;='集計・設定'!$C$5),IF(P37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;=TGT_MIN,N37&lt;=TGT_MAX),IF(P37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -10600,11 +10662,11 @@
         <v/>
       </c>
       <c r="D38" s="13">
-        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;='集計・設定'!$C$4,H38&lt;='集計・設定'!$C$5),IF(J38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;=TGT_MIN,H38&lt;=TGT_MAX),IF(J38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;='集計・設定'!$C$4,N38&lt;='集計・設定'!$C$5),IF(P38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;=TGT_MIN,N38&lt;=TGT_MAX),IF(P38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -10680,17 +10742,33 @@
   </sheetData>
   <autoFilter ref="A3:T38"/>
   <conditionalFormatting sqref="A4:T38">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H38">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N38">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -10785,10 +10863,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -10907,11 +10984,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -11000,11 +11077,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -11091,11 +11168,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -11184,11 +11261,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -11277,11 +11354,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -11360,11 +11437,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -11443,11 +11520,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -11536,11 +11613,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -11629,11 +11706,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -11722,11 +11799,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -11815,11 +11892,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -11908,11 +11985,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -11991,11 +12068,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -12074,11 +12151,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -12165,11 +12242,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -12238,11 +12315,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -12329,11 +12406,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -12410,11 +12487,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -12483,11 +12560,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -12566,11 +12643,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -12649,11 +12726,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -12732,11 +12809,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -12815,11 +12892,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -12898,11 +12975,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -12981,11 +13058,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -13053,17 +13130,33 @@
   </sheetData>
   <autoFilter ref="A3:T28"/>
   <conditionalFormatting sqref="A4:T28">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H28">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N28">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -13150,10 +13243,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -13272,11 +13364,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -13365,11 +13457,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -13456,11 +13548,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -13549,11 +13641,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -13640,11 +13732,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -13731,11 +13823,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -13820,11 +13912,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -13911,11 +14003,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -14002,11 +14094,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -14093,11 +14185,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -14184,11 +14276,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -14273,11 +14365,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -14364,11 +14456,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -14445,11 +14537,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -14526,11 +14618,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -14607,11 +14699,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -14694,11 +14786,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -14777,11 +14869,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -14820,12 +14912,12 @@
           <t>H30〜R9</t>
         </is>
       </c>
-      <c r="N21" s="16" t="n">
+      <c r="N21" s="13" t="n">
         <v>9</v>
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
@@ -14868,11 +14960,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -14959,11 +15051,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -15040,11 +15132,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -15121,11 +15213,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -15202,11 +15294,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -15283,11 +15375,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -15364,11 +15456,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -15445,11 +15537,11 @@
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;='集計・設定'!$C$4,H29&lt;='集計・設定'!$C$5),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;='集計・設定'!$C$4,N29&lt;='集計・設定'!$C$5),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -15526,11 +15618,11 @@
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;='集計・設定'!$C$4,H30&lt;='集計・設定'!$C$5),IF(J30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;=TGT_MIN,H30&lt;=TGT_MAX),IF(J30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;='集計・設定'!$C$4,N30&lt;='集計・設定'!$C$5),IF(P30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;=TGT_MIN,N30&lt;=TGT_MAX),IF(P30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -15607,11 +15699,11 @@
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;='集計・設定'!$C$4,H31&lt;='集計・設定'!$C$5),IF(J31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;=TGT_MIN,H31&lt;=TGT_MAX),IF(J31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;='集計・設定'!$C$4,N31&lt;='集計・設定'!$C$5),IF(P31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -15696,11 +15788,11 @@
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;='集計・設定'!$C$4,H32&lt;='集計・設定'!$C$5),IF(J32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;=TGT_MIN,H32&lt;=TGT_MAX),IF(J32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;='集計・設定'!$C$4,N32&lt;='集計・設定'!$C$5),IF(P32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;=TGT_MIN,N32&lt;=TGT_MAX),IF(P32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -15777,11 +15869,11 @@
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;='集計・設定'!$C$4,H33&lt;='集計・設定'!$C$5),IF(J33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;=TGT_MIN,H33&lt;=TGT_MAX),IF(J33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;='集計・設定'!$C$4,N33&lt;='集計・設定'!$C$5),IF(P33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -15858,11 +15950,11 @@
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;='集計・設定'!$C$4,H34&lt;='集計・設定'!$C$5),IF(J34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;=TGT_MIN,H34&lt;=TGT_MAX),IF(J34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;='集計・設定'!$C$4,N34&lt;='集計・設定'!$C$5),IF(P34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;=TGT_MIN,N34&lt;=TGT_MAX),IF(P34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -15939,11 +16031,11 @@
         <v/>
       </c>
       <c r="D35" s="13">
-        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;='集計・設定'!$C$4,H35&lt;='集計・設定'!$C$5),IF(J35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;=TGT_MIN,H35&lt;=TGT_MAX),IF(J35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;='集計・設定'!$C$4,N35&lt;='集計・設定'!$C$5),IF(P35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;=TGT_MIN,N35&lt;=TGT_MAX),IF(P35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -16020,11 +16112,11 @@
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;='集計・設定'!$C$4,H36&lt;='集計・設定'!$C$5),IF(J36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;=TGT_MIN,H36&lt;=TGT_MAX),IF(J36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;='集計・設定'!$C$4,N36&lt;='集計・設定'!$C$5),IF(P36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;=TGT_MIN,N36&lt;=TGT_MAX),IF(P36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -16101,11 +16193,11 @@
         <v/>
       </c>
       <c r="D37" s="13">
-        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;='集計・設定'!$C$4,H37&lt;='集計・設定'!$C$5),IF(J37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;=TGT_MIN,H37&lt;=TGT_MAX),IF(J37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;='集計・設定'!$C$4,N37&lt;='集計・設定'!$C$5),IF(P37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;=TGT_MIN,N37&lt;=TGT_MAX),IF(P37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -16190,11 +16282,11 @@
         <v/>
       </c>
       <c r="D38" s="13">
-        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;='集計・設定'!$C$4,H38&lt;='集計・設定'!$C$5),IF(J38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;=TGT_MIN,H38&lt;=TGT_MAX),IF(J38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;='集計・設定'!$C$4,N38&lt;='集計・設定'!$C$5),IF(P38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;=TGT_MIN,N38&lt;=TGT_MAX),IF(P38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -16268,17 +16360,33 @@
   </sheetData>
   <autoFilter ref="A3:T38"/>
   <conditionalFormatting sqref="A4:T38">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H38">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N38">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -16383,10 +16491,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>営業判定：どちらかの計画の終期が対象年度（「集計・設定」シートで設定、初期値はR9のみ）→◎。次期計画に着手済→△。期間不明→？。</t>
-        </is>
+      <c r="A2" s="9">
+        <f>"営業判定の対象：終期 R"&amp;TGT_MIN&amp;"〜R"&amp;TGT_MAX&amp;"年度 →◎（着手済は△、期間不明は？）。終期セルの色：緑＝対象年度／橙＝その翌年度（次の候補）。対象年度は「集計・設定」シートのC4・C5のプルダウンで切替。"</f>
+        <v/>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -16505,11 +16612,11 @@
         <v/>
       </c>
       <c r="D4" s="13">
-        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;='集計・設定'!$C$4,H4&lt;='集計・設定'!$C$5),IF(J4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J4="計画なし","－",IF(J4="策定済","✕",IF(H4="","？",IF(AND(H4&gt;=TGT_MIN,H4&lt;=TGT_MAX),IF(J4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;='集計・設定'!$C$4,N4&lt;='集計・設定'!$C$5),IF(P4="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P4="計画なし","－",IF(P4="策定済","✕",IF(N4="","？",IF(AND(N4&gt;=TGT_MIN,N4&lt;=TGT_MAX),IF(P4="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -16598,11 +16705,11 @@
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;='集計・設定'!$C$4,H5&lt;='集計・設定'!$C$5),IF(J5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J5="計画なし","－",IF(J5="策定済","✕",IF(H5="","？",IF(AND(H5&gt;=TGT_MIN,H5&lt;=TGT_MAX),IF(J5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;='集計・設定'!$C$4,N5&lt;='集計・設定'!$C$5),IF(P5="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P5="計画なし","－",IF(P5="策定済","✕",IF(N5="","？",IF(AND(N5&gt;=TGT_MIN,N5&lt;=TGT_MAX),IF(P5="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -16691,11 +16798,11 @@
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;='集計・設定'!$C$4,H6&lt;='集計・設定'!$C$5),IF(J6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J6="計画なし","－",IF(J6="策定済","✕",IF(H6="","？",IF(AND(H6&gt;=TGT_MIN,H6&lt;=TGT_MAX),IF(J6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;='集計・設定'!$C$4,N6&lt;='集計・設定'!$C$5),IF(P6="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P6="計画なし","－",IF(P6="策定済","✕",IF(N6="","？",IF(AND(N6&gt;=TGT_MIN,N6&lt;=TGT_MAX),IF(P6="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -16784,11 +16891,11 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;='集計・設定'!$C$4,H7&lt;='集計・設定'!$C$5),IF(J7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J7="計画なし","－",IF(J7="策定済","✕",IF(H7="","？",IF(AND(H7&gt;=TGT_MIN,H7&lt;=TGT_MAX),IF(J7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;='集計・設定'!$C$4,N7&lt;='集計・設定'!$C$5),IF(P7="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P7="計画なし","－",IF(P7="策定済","✕",IF(N7="","？",IF(AND(N7&gt;=TGT_MIN,N7&lt;=TGT_MAX),IF(P7="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -16801,12 +16908,12 @@
           <t>R5〜R9</t>
         </is>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="13" t="n">
         <v>9</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -16877,11 +16984,11 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;='集計・設定'!$C$4,H8&lt;='集計・設定'!$C$5),IF(J8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J8="計画なし","－",IF(J8="策定済","✕",IF(H8="","？",IF(AND(H8&gt;=TGT_MIN,H8&lt;=TGT_MAX),IF(J8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;='集計・設定'!$C$4,N8&lt;='集計・設定'!$C$5),IF(P8="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P8="計画なし","－",IF(P8="策定済","✕",IF(N8="","？",IF(AND(N8&gt;=TGT_MIN,N8&lt;=TGT_MAX),IF(P8="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -16970,11 +17077,11 @@
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;='集計・設定'!$C$4,H9&lt;='集計・設定'!$C$5),IF(J9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J9="計画なし","－",IF(J9="策定済","✕",IF(H9="","？",IF(AND(H9&gt;=TGT_MIN,H9&lt;=TGT_MAX),IF(J9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;='集計・設定'!$C$4,N9&lt;='集計・設定'!$C$5),IF(P9="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P9="計画なし","－",IF(P9="策定済","✕",IF(N9="","？",IF(AND(N9&gt;=TGT_MIN,N9&lt;=TGT_MAX),IF(P9="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -17059,11 +17166,11 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;='集計・設定'!$C$4,H10&lt;='集計・設定'!$C$5),IF(J10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J10="計画なし","－",IF(J10="策定済","✕",IF(H10="","？",IF(AND(H10&gt;=TGT_MIN,H10&lt;=TGT_MAX),IF(J10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;='集計・設定'!$C$4,N10&lt;='集計・設定'!$C$5),IF(P10="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P10="計画なし","－",IF(P10="策定済","✕",IF(N10="","？",IF(AND(N10&gt;=TGT_MIN,N10&lt;=TGT_MAX),IF(P10="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -17146,11 +17253,11 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;='集計・設定'!$C$4,H11&lt;='集計・設定'!$C$5),IF(J11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J11="計画なし","－",IF(J11="策定済","✕",IF(H11="","？",IF(AND(H11&gt;=TGT_MIN,H11&lt;=TGT_MAX),IF(J11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;='集計・設定'!$C$4,N11&lt;='集計・設定'!$C$5),IF(P11="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P11="計画なし","－",IF(P11="策定済","✕",IF(N11="","？",IF(AND(N11&gt;=TGT_MIN,N11&lt;=TGT_MAX),IF(P11="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F11" s="11" t="n"/>
@@ -17219,11 +17326,11 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;='集計・設定'!$C$4,H12&lt;='集計・設定'!$C$5),IF(J12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J12="計画なし","－",IF(J12="策定済","✕",IF(H12="","？",IF(AND(H12&gt;=TGT_MIN,H12&lt;=TGT_MAX),IF(J12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;='集計・設定'!$C$4,N12&lt;='集計・設定'!$C$5),IF(P12="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P12="計画なし","－",IF(P12="策定済","✕",IF(N12="","？",IF(AND(N12&gt;=TGT_MIN,N12&lt;=TGT_MAX),IF(P12="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17310,11 +17417,11 @@
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;='集計・設定'!$C$4,H13&lt;='集計・設定'!$C$5),IF(J13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J13="計画なし","－",IF(J13="策定済","✕",IF(H13="","？",IF(AND(H13&gt;=TGT_MIN,H13&lt;=TGT_MAX),IF(J13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;='集計・設定'!$C$4,N13&lt;='集計・設定'!$C$5),IF(P13="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P13="計画なし","－",IF(P13="策定済","✕",IF(N13="","？",IF(AND(N13&gt;=TGT_MIN,N13&lt;=TGT_MAX),IF(P13="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -17393,11 +17500,11 @@
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;='集計・設定'!$C$4,H14&lt;='集計・設定'!$C$5),IF(J14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J14="計画なし","－",IF(J14="策定済","✕",IF(H14="","？",IF(AND(H14&gt;=TGT_MIN,H14&lt;=TGT_MAX),IF(J14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;='集計・設定'!$C$4,N14&lt;='集計・設定'!$C$5),IF(P14="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P14="計画なし","－",IF(P14="策定済","✕",IF(N14="","？",IF(AND(N14&gt;=TGT_MIN,N14&lt;=TGT_MAX),IF(P14="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -17484,11 +17591,11 @@
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;='集計・設定'!$C$4,H15&lt;='集計・設定'!$C$5),IF(J15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J15="計画なし","－",IF(J15="策定済","✕",IF(H15="","？",IF(AND(H15&gt;=TGT_MIN,H15&lt;=TGT_MAX),IF(J15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;='集計・設定'!$C$4,N15&lt;='集計・設定'!$C$5),IF(P15="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P15="計画なし","－",IF(P15="策定済","✕",IF(N15="","？",IF(AND(N15&gt;=TGT_MIN,N15&lt;=TGT_MAX),IF(P15="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -17575,11 +17682,11 @@
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;='集計・設定'!$C$4,H16&lt;='集計・設定'!$C$5),IF(J16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J16="計画なし","－",IF(J16="策定済","✕",IF(H16="","？",IF(AND(H16&gt;=TGT_MIN,H16&lt;=TGT_MAX),IF(J16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;='集計・設定'!$C$4,N16&lt;='集計・設定'!$C$5),IF(P16="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P16="計画なし","－",IF(P16="策定済","✕",IF(N16="","？",IF(AND(N16&gt;=TGT_MIN,N16&lt;=TGT_MAX),IF(P16="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -17662,11 +17769,11 @@
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;='集計・設定'!$C$4,H17&lt;='集計・設定'!$C$5),IF(J17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J17="計画なし","－",IF(J17="策定済","✕",IF(H17="","？",IF(AND(H17&gt;=TGT_MIN,H17&lt;=TGT_MAX),IF(J17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;='集計・設定'!$C$4,N17&lt;='集計・設定'!$C$5),IF(P17="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P17="計画なし","－",IF(P17="策定済","✕",IF(N17="","？",IF(AND(N17&gt;=TGT_MIN,N17&lt;=TGT_MAX),IF(P17="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -17735,11 +17842,11 @@
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;='集計・設定'!$C$4,H18&lt;='集計・設定'!$C$5),IF(J18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J18="計画なし","－",IF(J18="策定済","✕",IF(H18="","？",IF(AND(H18&gt;=TGT_MIN,H18&lt;=TGT_MAX),IF(J18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;='集計・設定'!$C$4,N18&lt;='集計・設定'!$C$5),IF(P18="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P18="計画なし","－",IF(P18="策定済","✕",IF(N18="","？",IF(AND(N18&gt;=TGT_MIN,N18&lt;=TGT_MAX),IF(P18="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -17808,11 +17915,11 @@
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;='集計・設定'!$C$4,H19&lt;='集計・設定'!$C$5),IF(J19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J19="計画なし","－",IF(J19="策定済","✕",IF(H19="","？",IF(AND(H19&gt;=TGT_MIN,H19&lt;=TGT_MAX),IF(J19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;='集計・設定'!$C$4,N19&lt;='集計・設定'!$C$5),IF(P19="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -17881,11 +17988,11 @@
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;='集計・設定'!$C$4,H20&lt;='集計・設定'!$C$5),IF(J20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J20="計画なし","－",IF(J20="策定済","✕",IF(H20="","？",IF(AND(H20&gt;=TGT_MIN,H20&lt;=TGT_MAX),IF(J20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;='集計・設定'!$C$4,N20&lt;='集計・設定'!$C$5),IF(P20="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P20="計画なし","－",IF(P20="策定済","✕",IF(N20="","？",IF(AND(N20&gt;=TGT_MIN,N20&lt;=TGT_MAX),IF(P20="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -17964,11 +18071,11 @@
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;='集計・設定'!$C$4,H21&lt;='集計・設定'!$C$5),IF(J21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J21="計画なし","－",IF(J21="策定済","✕",IF(H21="","？",IF(AND(H21&gt;=TGT_MIN,H21&lt;=TGT_MAX),IF(J21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;='集計・設定'!$C$4,N21&lt;='集計・設定'!$C$5),IF(P21="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P21="計画なし","－",IF(P21="策定済","✕",IF(N21="","？",IF(AND(N21&gt;=TGT_MIN,N21&lt;=TGT_MAX),IF(P21="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -18037,11 +18144,11 @@
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;='集計・設定'!$C$4,H22&lt;='集計・設定'!$C$5),IF(J22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J22="計画なし","－",IF(J22="策定済","✕",IF(H22="","？",IF(AND(H22&gt;=TGT_MIN,H22&lt;=TGT_MAX),IF(J22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;='集計・設定'!$C$4,N22&lt;='集計・設定'!$C$5),IF(P22="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P22="計画なし","－",IF(P22="策定済","✕",IF(N22="","？",IF(AND(N22&gt;=TGT_MIN,N22&lt;=TGT_MAX),IF(P22="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -18110,11 +18217,11 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;='集計・設定'!$C$4,H23&lt;='集計・設定'!$C$5),IF(J23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J23="計画なし","－",IF(J23="策定済","✕",IF(H23="","？",IF(AND(H23&gt;=TGT_MIN,H23&lt;=TGT_MAX),IF(J23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;='集計・設定'!$C$4,N23&lt;='集計・設定'!$C$5),IF(P23="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P23="計画なし","－",IF(P23="策定済","✕",IF(N23="","？",IF(AND(N23&gt;=TGT_MIN,N23&lt;=TGT_MAX),IF(P23="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -18183,11 +18290,11 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;='集計・設定'!$C$4,H24&lt;='集計・設定'!$C$5),IF(J24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J24="計画なし","－",IF(J24="策定済","✕",IF(H24="","？",IF(AND(H24&gt;=TGT_MIN,H24&lt;=TGT_MAX),IF(J24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;='集計・設定'!$C$4,N24&lt;='集計・設定'!$C$5),IF(P24="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P24="計画なし","－",IF(P24="策定済","✕",IF(N24="","？",IF(AND(N24&gt;=TGT_MIN,N24&lt;=TGT_MAX),IF(P24="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -18256,11 +18363,11 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;='集計・設定'!$C$4,H25&lt;='集計・設定'!$C$5),IF(J25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J25="計画なし","－",IF(J25="策定済","✕",IF(H25="","？",IF(AND(H25&gt;=TGT_MIN,H25&lt;=TGT_MAX),IF(J25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;='集計・設定'!$C$4,N25&lt;='集計・設定'!$C$5),IF(P25="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P25="計画なし","－",IF(P25="策定済","✕",IF(N25="","？",IF(AND(N25&gt;=TGT_MIN,N25&lt;=TGT_MAX),IF(P25="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -18329,11 +18436,11 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;='集計・設定'!$C$4,H26&lt;='集計・設定'!$C$5),IF(J26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J26="計画なし","－",IF(J26="策定済","✕",IF(H26="","？",IF(AND(H26&gt;=TGT_MIN,H26&lt;=TGT_MAX),IF(J26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;='集計・設定'!$C$4,N26&lt;='集計・設定'!$C$5),IF(P26="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P26="計画なし","－",IF(P26="策定済","✕",IF(N26="","？",IF(AND(N26&gt;=TGT_MIN,N26&lt;=TGT_MAX),IF(P26="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -18420,11 +18527,11 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;='集計・設定'!$C$4,H27&lt;='集計・設定'!$C$5),IF(J27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J27="計画なし","－",IF(J27="策定済","✕",IF(H27="","？",IF(AND(H27&gt;=TGT_MIN,H27&lt;=TGT_MAX),IF(J27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;='集計・設定'!$C$4,N27&lt;='集計・設定'!$C$5),IF(P27="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -18493,11 +18600,11 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;='集計・設定'!$C$4,H28&lt;='集計・設定'!$C$5),IF(J28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J28="計画なし","－",IF(J28="策定済","✕",IF(H28="","？",IF(AND(H28&gt;=TGT_MIN,H28&lt;=TGT_MAX),IF(J28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;='集計・設定'!$C$4,N28&lt;='集計・設定'!$C$5),IF(P28="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P28="計画なし","－",IF(P28="策定済","✕",IF(N28="","？",IF(AND(N28&gt;=TGT_MIN,N28&lt;=TGT_MAX),IF(P28="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -18566,11 +18673,11 @@
         <v/>
       </c>
       <c r="D29" s="13">
-        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;='集計・設定'!$C$4,H29&lt;='集計・設定'!$C$5),IF(J29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J29="計画なし","－",IF(J29="策定済","✕",IF(H29="","？",IF(AND(H29&gt;=TGT_MIN,H29&lt;=TGT_MAX),IF(J29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;='集計・設定'!$C$4,N29&lt;='集計・設定'!$C$5),IF(P29="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P29="計画なし","－",IF(P29="策定済","✕",IF(N29="","？",IF(AND(N29&gt;=TGT_MIN,N29&lt;=TGT_MAX),IF(P29="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -18639,11 +18746,11 @@
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;='集計・設定'!$C$4,H30&lt;='集計・設定'!$C$5),IF(J30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J30="計画なし","－",IF(J30="策定済","✕",IF(H30="","？",IF(AND(H30&gt;=TGT_MIN,H30&lt;=TGT_MAX),IF(J30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;='集計・設定'!$C$4,N30&lt;='集計・設定'!$C$5),IF(P30="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P30="計画なし","－",IF(P30="策定済","✕",IF(N30="","？",IF(AND(N30&gt;=TGT_MIN,N30&lt;=TGT_MAX),IF(P30="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -18712,11 +18819,11 @@
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;='集計・設定'!$C$4,H31&lt;='集計・設定'!$C$5),IF(J31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J31="計画なし","－",IF(J31="策定済","✕",IF(H31="","？",IF(AND(H31&gt;=TGT_MIN,H31&lt;=TGT_MAX),IF(J31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;='集計・設定'!$C$4,N31&lt;='集計・設定'!$C$5),IF(P31="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -18795,11 +18902,11 @@
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;='集計・設定'!$C$4,H32&lt;='集計・設定'!$C$5),IF(J32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J32="計画なし","－",IF(J32="策定済","✕",IF(H32="","？",IF(AND(H32&gt;=TGT_MIN,H32&lt;=TGT_MAX),IF(J32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;='集計・設定'!$C$4,N32&lt;='集計・設定'!$C$5),IF(P32="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P32="計画なし","－",IF(P32="策定済","✕",IF(N32="","？",IF(AND(N32&gt;=TGT_MIN,N32&lt;=TGT_MAX),IF(P32="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -18878,11 +18985,11 @@
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;='集計・設定'!$C$4,H33&lt;='集計・設定'!$C$5),IF(J33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J33="計画なし","－",IF(J33="策定済","✕",IF(H33="","？",IF(AND(H33&gt;=TGT_MIN,H33&lt;=TGT_MAX),IF(J33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;='集計・設定'!$C$4,N33&lt;='集計・設定'!$C$5),IF(P33="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -18961,11 +19068,11 @@
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;='集計・設定'!$C$4,H34&lt;='集計・設定'!$C$5),IF(J34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J34="計画なし","－",IF(J34="策定済","✕",IF(H34="","？",IF(AND(H34&gt;=TGT_MIN,H34&lt;=TGT_MAX),IF(J34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;='集計・設定'!$C$4,N34&lt;='集計・設定'!$C$5),IF(P34="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P34="計画なし","－",IF(P34="策定済","✕",IF(N34="","？",IF(AND(N34&gt;=TGT_MIN,N34&lt;=TGT_MAX),IF(P34="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -19034,11 +19141,11 @@
         <v/>
       </c>
       <c r="D35" s="13">
-        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;='集計・設定'!$C$4,H35&lt;='集計・設定'!$C$5),IF(J35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J35="計画なし","－",IF(J35="策定済","✕",IF(H35="","？",IF(AND(H35&gt;=TGT_MIN,H35&lt;=TGT_MAX),IF(J35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;='集計・設定'!$C$4,N35&lt;='集計・設定'!$C$5),IF(P35="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P35="計画なし","－",IF(P35="策定済","✕",IF(N35="","？",IF(AND(N35&gt;=TGT_MIN,N35&lt;=TGT_MAX),IF(P35="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F35" s="11" t="n"/>
@@ -19107,11 +19214,11 @@
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;='集計・設定'!$C$4,H36&lt;='集計・設定'!$C$5),IF(J36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J36="計画なし","－",IF(J36="策定済","✕",IF(H36="","？",IF(AND(H36&gt;=TGT_MIN,H36&lt;=TGT_MAX),IF(J36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;='集計・設定'!$C$4,N36&lt;='集計・設定'!$C$5),IF(P36="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P36="計画なし","－",IF(P36="策定済","✕",IF(N36="","？",IF(AND(N36&gt;=TGT_MIN,N36&lt;=TGT_MAX),IF(P36="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F36" s="11" t="n"/>
@@ -19180,11 +19287,11 @@
         <v/>
       </c>
       <c r="D37" s="13">
-        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;='集計・設定'!$C$4,H37&lt;='集計・設定'!$C$5),IF(J37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J37="計画なし","－",IF(J37="策定済","✕",IF(H37="","？",IF(AND(H37&gt;=TGT_MIN,H37&lt;=TGT_MAX),IF(J37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;='集計・設定'!$C$4,N37&lt;='集計・設定'!$C$5),IF(P37="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P37="計画なし","－",IF(P37="策定済","✕",IF(N37="","？",IF(AND(N37&gt;=TGT_MIN,N37&lt;=TGT_MAX),IF(P37="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -19263,11 +19370,11 @@
         <v/>
       </c>
       <c r="D38" s="13">
-        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;='集計・設定'!$C$4,H38&lt;='集計・設定'!$C$5),IF(J38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J38="計画なし","－",IF(J38="策定済","✕",IF(H38="","？",IF(AND(H38&gt;=TGT_MIN,H38&lt;=TGT_MAX),IF(J38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;='集計・設定'!$C$4,N38&lt;='集計・設定'!$C$5),IF(P38="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P38="計画なし","－",IF(P38="策定済","✕",IF(N38="","？",IF(AND(N38&gt;=TGT_MIN,N38&lt;=TGT_MAX),IF(P38="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -19354,11 +19461,11 @@
         <v/>
       </c>
       <c r="D39" s="13">
-        <f>IF(J39="計画なし","－",IF(J39="策定済","✕",IF(H39="","？",IF(AND(H39&gt;='集計・設定'!$C$4,H39&lt;='集計・設定'!$C$5),IF(J39="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J39="計画なし","－",IF(J39="策定済","✕",IF(H39="","？",IF(AND(H39&gt;=TGT_MIN,H39&lt;=TGT_MAX),IF(J39="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E39" s="13">
-        <f>IF(P39="計画なし","－",IF(P39="策定済","✕",IF(N39="","？",IF(AND(N39&gt;='集計・設定'!$C$4,N39&lt;='集計・設定'!$C$5),IF(P39="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P39="計画なし","－",IF(P39="策定済","✕",IF(N39="","？",IF(AND(N39&gt;=TGT_MIN,N39&lt;=TGT_MAX),IF(P39="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -19437,11 +19544,11 @@
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>IF(J40="計画なし","－",IF(J40="策定済","✕",IF(H40="","？",IF(AND(H40&gt;='集計・設定'!$C$4,H40&lt;='集計・設定'!$C$5),IF(J40="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J40="計画なし","－",IF(J40="策定済","✕",IF(H40="","？",IF(AND(H40&gt;=TGT_MIN,H40&lt;=TGT_MAX),IF(J40="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>IF(P40="計画なし","－",IF(P40="策定済","✕",IF(N40="","？",IF(AND(N40&gt;='集計・設定'!$C$4,N40&lt;='集計・設定'!$C$5),IF(P40="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P40="計画なし","－",IF(P40="策定済","✕",IF(N40="","？",IF(AND(N40&gt;=TGT_MIN,N40&lt;=TGT_MAX),IF(P40="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -19520,11 +19627,11 @@
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>IF(J41="計画なし","－",IF(J41="策定済","✕",IF(H41="","？",IF(AND(H41&gt;='集計・設定'!$C$4,H41&lt;='集計・設定'!$C$5),IF(J41="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J41="計画なし","－",IF(J41="策定済","✕",IF(H41="","？",IF(AND(H41&gt;=TGT_MIN,H41&lt;=TGT_MAX),IF(J41="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>IF(P41="計画なし","－",IF(P41="策定済","✕",IF(N41="","？",IF(AND(N41&gt;='集計・設定'!$C$4,N41&lt;='集計・設定'!$C$5),IF(P41="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P41="計画なし","－",IF(P41="策定済","✕",IF(N41="","？",IF(AND(N41&gt;=TGT_MIN,N41&lt;=TGT_MAX),IF(P41="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -19601,11 +19708,11 @@
         <v/>
       </c>
       <c r="D42" s="13">
-        <f>IF(J42="計画なし","－",IF(J42="策定済","✕",IF(H42="","？",IF(AND(H42&gt;='集計・設定'!$C$4,H42&lt;='集計・設定'!$C$5),IF(J42="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J42="計画なし","－",IF(J42="策定済","✕",IF(H42="","？",IF(AND(H42&gt;=TGT_MIN,H42&lt;=TGT_MAX),IF(J42="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E42" s="13">
-        <f>IF(P42="計画なし","－",IF(P42="策定済","✕",IF(N42="","？",IF(AND(N42&gt;='集計・設定'!$C$4,N42&lt;='集計・設定'!$C$5),IF(P42="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P42="計画なし","－",IF(P42="策定済","✕",IF(N42="","？",IF(AND(N42&gt;=TGT_MIN,N42&lt;=TGT_MAX),IF(P42="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -19692,11 +19799,11 @@
         <v/>
       </c>
       <c r="D43" s="13">
-        <f>IF(J43="計画なし","－",IF(J43="策定済","✕",IF(H43="","？",IF(AND(H43&gt;='集計・設定'!$C$4,H43&lt;='集計・設定'!$C$5),IF(J43="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J43="計画なし","－",IF(J43="策定済","✕",IF(H43="","？",IF(AND(H43&gt;=TGT_MIN,H43&lt;=TGT_MAX),IF(J43="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E43" s="13">
-        <f>IF(P43="計画なし","－",IF(P43="策定済","✕",IF(N43="","？",IF(AND(N43&gt;='集計・設定'!$C$4,N43&lt;='集計・設定'!$C$5),IF(P43="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P43="計画なし","－",IF(P43="策定済","✕",IF(N43="","？",IF(AND(N43&gt;=TGT_MIN,N43&lt;=TGT_MAX),IF(P43="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -19775,11 +19882,11 @@
         <v/>
       </c>
       <c r="D44" s="13">
-        <f>IF(J44="計画なし","－",IF(J44="策定済","✕",IF(H44="","？",IF(AND(H44&gt;='集計・設定'!$C$4,H44&lt;='集計・設定'!$C$5),IF(J44="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J44="計画なし","－",IF(J44="策定済","✕",IF(H44="","？",IF(AND(H44&gt;=TGT_MIN,H44&lt;=TGT_MAX),IF(J44="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E44" s="13">
-        <f>IF(P44="計画なし","－",IF(P44="策定済","✕",IF(N44="","？",IF(AND(N44&gt;='集計・設定'!$C$4,N44&lt;='集計・設定'!$C$5),IF(P44="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P44="計画なし","－",IF(P44="策定済","✕",IF(N44="","？",IF(AND(N44&gt;=TGT_MIN,N44&lt;=TGT_MAX),IF(P44="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -19858,11 +19965,11 @@
         <v/>
       </c>
       <c r="D45" s="13">
-        <f>IF(J45="計画なし","－",IF(J45="策定済","✕",IF(H45="","？",IF(AND(H45&gt;='集計・設定'!$C$4,H45&lt;='集計・設定'!$C$5),IF(J45="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J45="計画なし","－",IF(J45="策定済","✕",IF(H45="","？",IF(AND(H45&gt;=TGT_MIN,H45&lt;=TGT_MAX),IF(J45="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E45" s="13">
-        <f>IF(P45="計画なし","－",IF(P45="策定済","✕",IF(N45="","？",IF(AND(N45&gt;='集計・設定'!$C$4,N45&lt;='集計・設定'!$C$5),IF(P45="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P45="計画なし","－",IF(P45="策定済","✕",IF(N45="","？",IF(AND(N45&gt;=TGT_MIN,N45&lt;=TGT_MAX),IF(P45="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -19941,11 +20048,11 @@
         <v/>
       </c>
       <c r="D46" s="13">
-        <f>IF(J46="計画なし","－",IF(J46="策定済","✕",IF(H46="","？",IF(AND(H46&gt;='集計・設定'!$C$4,H46&lt;='集計・設定'!$C$5),IF(J46="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J46="計画なし","－",IF(J46="策定済","✕",IF(H46="","？",IF(AND(H46&gt;=TGT_MIN,H46&lt;=TGT_MAX),IF(J46="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E46" s="13">
-        <f>IF(P46="計画なし","－",IF(P46="策定済","✕",IF(N46="","？",IF(AND(N46&gt;='集計・設定'!$C$4,N46&lt;='集計・設定'!$C$5),IF(P46="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P46="計画なし","－",IF(P46="策定済","✕",IF(N46="","？",IF(AND(N46&gt;=TGT_MIN,N46&lt;=TGT_MAX),IF(P46="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -20024,11 +20131,11 @@
         <v/>
       </c>
       <c r="D47" s="13">
-        <f>IF(J47="計画なし","－",IF(J47="策定済","✕",IF(H47="","？",IF(AND(H47&gt;='集計・設定'!$C$4,H47&lt;='集計・設定'!$C$5),IF(J47="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J47="計画なし","－",IF(J47="策定済","✕",IF(H47="","？",IF(AND(H47&gt;=TGT_MIN,H47&lt;=TGT_MAX),IF(J47="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E47" s="13">
-        <f>IF(P47="計画なし","－",IF(P47="策定済","✕",IF(N47="","？",IF(AND(N47&gt;='集計・設定'!$C$4,N47&lt;='集計・設定'!$C$5),IF(P47="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P47="計画なし","－",IF(P47="策定済","✕",IF(N47="","？",IF(AND(N47&gt;=TGT_MIN,N47&lt;=TGT_MAX),IF(P47="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -20107,11 +20214,11 @@
         <v/>
       </c>
       <c r="D48" s="13">
-        <f>IF(J48="計画なし","－",IF(J48="策定済","✕",IF(H48="","？",IF(AND(H48&gt;='集計・設定'!$C$4,H48&lt;='集計・設定'!$C$5),IF(J48="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J48="計画なし","－",IF(J48="策定済","✕",IF(H48="","？",IF(AND(H48&gt;=TGT_MIN,H48&lt;=TGT_MAX),IF(J48="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E48" s="13">
-        <f>IF(P48="計画なし","－",IF(P48="策定済","✕",IF(N48="","？",IF(AND(N48&gt;='集計・設定'!$C$4,N48&lt;='集計・設定'!$C$5),IF(P48="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P48="計画なし","－",IF(P48="策定済","✕",IF(N48="","？",IF(AND(N48&gt;=TGT_MIN,N48&lt;=TGT_MAX),IF(P48="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -20190,11 +20297,11 @@
         <v/>
       </c>
       <c r="D49" s="13">
-        <f>IF(J49="計画なし","－",IF(J49="策定済","✕",IF(H49="","？",IF(AND(H49&gt;='集計・設定'!$C$4,H49&lt;='集計・設定'!$C$5),IF(J49="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J49="計画なし","－",IF(J49="策定済","✕",IF(H49="","？",IF(AND(H49&gt;=TGT_MIN,H49&lt;=TGT_MAX),IF(J49="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E49" s="13">
-        <f>IF(P49="計画なし","－",IF(P49="策定済","✕",IF(N49="","？",IF(AND(N49&gt;='集計・設定'!$C$4,N49&lt;='集計・設定'!$C$5),IF(P49="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P49="計画なし","－",IF(P49="策定済","✕",IF(N49="","？",IF(AND(N49&gt;=TGT_MIN,N49&lt;=TGT_MAX),IF(P49="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -20273,11 +20380,11 @@
         <v/>
       </c>
       <c r="D50" s="13">
-        <f>IF(J50="計画なし","－",IF(J50="策定済","✕",IF(H50="","？",IF(AND(H50&gt;='集計・設定'!$C$4,H50&lt;='集計・設定'!$C$5),IF(J50="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J50="計画なし","－",IF(J50="策定済","✕",IF(H50="","？",IF(AND(H50&gt;=TGT_MIN,H50&lt;=TGT_MAX),IF(J50="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E50" s="13">
-        <f>IF(P50="計画なし","－",IF(P50="策定済","✕",IF(N50="","？",IF(AND(N50&gt;='集計・設定'!$C$4,N50&lt;='集計・設定'!$C$5),IF(P50="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P50="計画なし","－",IF(P50="策定済","✕",IF(N50="","？",IF(AND(N50&gt;=TGT_MIN,N50&lt;=TGT_MAX),IF(P50="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -20356,11 +20463,11 @@
         <v/>
       </c>
       <c r="D51" s="13">
-        <f>IF(J51="計画なし","－",IF(J51="策定済","✕",IF(H51="","？",IF(AND(H51&gt;='集計・設定'!$C$4,H51&lt;='集計・設定'!$C$5),IF(J51="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J51="計画なし","－",IF(J51="策定済","✕",IF(H51="","？",IF(AND(H51&gt;=TGT_MIN,H51&lt;=TGT_MAX),IF(J51="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E51" s="13">
-        <f>IF(P51="計画なし","－",IF(P51="策定済","✕",IF(N51="","？",IF(AND(N51&gt;='集計・設定'!$C$4,N51&lt;='集計・設定'!$C$5),IF(P51="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P51="計画なし","－",IF(P51="策定済","✕",IF(N51="","？",IF(AND(N51&gt;=TGT_MIN,N51&lt;=TGT_MAX),IF(P51="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -20439,11 +20546,11 @@
         <v/>
       </c>
       <c r="D52" s="13">
-        <f>IF(J52="計画なし","－",IF(J52="策定済","✕",IF(H52="","？",IF(AND(H52&gt;='集計・設定'!$C$4,H52&lt;='集計・設定'!$C$5),IF(J52="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J52="計画なし","－",IF(J52="策定済","✕",IF(H52="","？",IF(AND(H52&gt;=TGT_MIN,H52&lt;=TGT_MAX),IF(J52="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E52" s="13">
-        <f>IF(P52="計画なし","－",IF(P52="策定済","✕",IF(N52="","？",IF(AND(N52&gt;='集計・設定'!$C$4,N52&lt;='集計・設定'!$C$5),IF(P52="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P52="計画なし","－",IF(P52="策定済","✕",IF(N52="","？",IF(AND(N52&gt;=TGT_MIN,N52&lt;=TGT_MAX),IF(P52="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F52" s="11" t="inlineStr">
@@ -20522,11 +20629,11 @@
         <v/>
       </c>
       <c r="D53" s="13">
-        <f>IF(J53="計画なし","－",IF(J53="策定済","✕",IF(H53="","？",IF(AND(H53&gt;='集計・設定'!$C$4,H53&lt;='集計・設定'!$C$5),IF(J53="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J53="計画なし","－",IF(J53="策定済","✕",IF(H53="","？",IF(AND(H53&gt;=TGT_MIN,H53&lt;=TGT_MAX),IF(J53="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E53" s="13">
-        <f>IF(P53="計画なし","－",IF(P53="策定済","✕",IF(N53="","？",IF(AND(N53&gt;='集計・設定'!$C$4,N53&lt;='集計・設定'!$C$5),IF(P53="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P53="計画なし","－",IF(P53="策定済","✕",IF(N53="","？",IF(AND(N53&gt;=TGT_MIN,N53&lt;=TGT_MAX),IF(P53="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -20615,11 +20722,11 @@
         <v/>
       </c>
       <c r="D54" s="13">
-        <f>IF(J54="計画なし","－",IF(J54="策定済","✕",IF(H54="","？",IF(AND(H54&gt;='集計・設定'!$C$4,H54&lt;='集計・設定'!$C$5),IF(J54="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J54="計画なし","－",IF(J54="策定済","✕",IF(H54="","？",IF(AND(H54&gt;=TGT_MIN,H54&lt;=TGT_MAX),IF(J54="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E54" s="13">
-        <f>IF(P54="計画なし","－",IF(P54="策定済","✕",IF(N54="","？",IF(AND(N54&gt;='集計・設定'!$C$4,N54&lt;='集計・設定'!$C$5),IF(P54="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P54="計画なし","－",IF(P54="策定済","✕",IF(N54="","？",IF(AND(N54&gt;=TGT_MIN,N54&lt;=TGT_MAX),IF(P54="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -20698,11 +20805,11 @@
         <v/>
       </c>
       <c r="D55" s="13">
-        <f>IF(J55="計画なし","－",IF(J55="策定済","✕",IF(H55="","？",IF(AND(H55&gt;='集計・設定'!$C$4,H55&lt;='集計・設定'!$C$5),IF(J55="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J55="計画なし","－",IF(J55="策定済","✕",IF(H55="","？",IF(AND(H55&gt;=TGT_MIN,H55&lt;=TGT_MAX),IF(J55="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E55" s="13">
-        <f>IF(P55="計画なし","－",IF(P55="策定済","✕",IF(N55="","？",IF(AND(N55&gt;='集計・設定'!$C$4,N55&lt;='集計・設定'!$C$5),IF(P55="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P55="計画なし","－",IF(P55="策定済","✕",IF(N55="","？",IF(AND(N55&gt;=TGT_MIN,N55&lt;=TGT_MAX),IF(P55="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -20781,11 +20888,11 @@
         <v/>
       </c>
       <c r="D56" s="13">
-        <f>IF(J56="計画なし","－",IF(J56="策定済","✕",IF(H56="","？",IF(AND(H56&gt;='集計・設定'!$C$4,H56&lt;='集計・設定'!$C$5),IF(J56="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J56="計画なし","－",IF(J56="策定済","✕",IF(H56="","？",IF(AND(H56&gt;=TGT_MIN,H56&lt;=TGT_MAX),IF(J56="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E56" s="13">
-        <f>IF(P56="計画なし","－",IF(P56="策定済","✕",IF(N56="","？",IF(AND(N56&gt;='集計・設定'!$C$4,N56&lt;='集計・設定'!$C$5),IF(P56="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P56="計画なし","－",IF(P56="策定済","✕",IF(N56="","？",IF(AND(N56&gt;=TGT_MIN,N56&lt;=TGT_MAX),IF(P56="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F56" s="11" t="inlineStr">
@@ -20864,11 +20971,11 @@
         <v/>
       </c>
       <c r="D57" s="13">
-        <f>IF(J57="計画なし","－",IF(J57="策定済","✕",IF(H57="","？",IF(AND(H57&gt;='集計・設定'!$C$4,H57&lt;='集計・設定'!$C$5),IF(J57="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J57="計画なし","－",IF(J57="策定済","✕",IF(H57="","？",IF(AND(H57&gt;=TGT_MIN,H57&lt;=TGT_MAX),IF(J57="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E57" s="13">
-        <f>IF(P57="計画なし","－",IF(P57="策定済","✕",IF(N57="","？",IF(AND(N57&gt;='集計・設定'!$C$4,N57&lt;='集計・設定'!$C$5),IF(P57="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P57="計画なし","－",IF(P57="策定済","✕",IF(N57="","？",IF(AND(N57&gt;=TGT_MIN,N57&lt;=TGT_MAX),IF(P57="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -20947,11 +21054,11 @@
         <v/>
       </c>
       <c r="D58" s="13">
-        <f>IF(J58="計画なし","－",IF(J58="策定済","✕",IF(H58="","？",IF(AND(H58&gt;='集計・設定'!$C$4,H58&lt;='集計・設定'!$C$5),IF(J58="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J58="計画なし","－",IF(J58="策定済","✕",IF(H58="","？",IF(AND(H58&gt;=TGT_MIN,H58&lt;=TGT_MAX),IF(J58="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E58" s="13">
-        <f>IF(P58="計画なし","－",IF(P58="策定済","✕",IF(N58="","？",IF(AND(N58&gt;='集計・設定'!$C$4,N58&lt;='集計・設定'!$C$5),IF(P58="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P58="計画なし","－",IF(P58="策定済","✕",IF(N58="","？",IF(AND(N58&gt;=TGT_MIN,N58&lt;=TGT_MAX),IF(P58="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F58" s="11" t="inlineStr">
@@ -21030,11 +21137,11 @@
         <v/>
       </c>
       <c r="D59" s="13">
-        <f>IF(J59="計画なし","－",IF(J59="策定済","✕",IF(H59="","？",IF(AND(H59&gt;='集計・設定'!$C$4,H59&lt;='集計・設定'!$C$5),IF(J59="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J59="計画なし","－",IF(J59="策定済","✕",IF(H59="","？",IF(AND(H59&gt;=TGT_MIN,H59&lt;=TGT_MAX),IF(J59="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E59" s="13">
-        <f>IF(P59="計画なし","－",IF(P59="策定済","✕",IF(N59="","？",IF(AND(N59&gt;='集計・設定'!$C$4,N59&lt;='集計・設定'!$C$5),IF(P59="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P59="計画なし","－",IF(P59="策定済","✕",IF(N59="","？",IF(AND(N59&gt;=TGT_MIN,N59&lt;=TGT_MAX),IF(P59="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -21113,11 +21220,11 @@
         <v/>
       </c>
       <c r="D60" s="13">
-        <f>IF(J60="計画なし","－",IF(J60="策定済","✕",IF(H60="","？",IF(AND(H60&gt;='集計・設定'!$C$4,H60&lt;='集計・設定'!$C$5),IF(J60="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J60="計画なし","－",IF(J60="策定済","✕",IF(H60="","？",IF(AND(H60&gt;=TGT_MIN,H60&lt;=TGT_MAX),IF(J60="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E60" s="13">
-        <f>IF(P60="計画なし","－",IF(P60="策定済","✕",IF(N60="","？",IF(AND(N60&gt;='集計・設定'!$C$4,N60&lt;='集計・設定'!$C$5),IF(P60="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P60="計画なし","－",IF(P60="策定済","✕",IF(N60="","？",IF(AND(N60&gt;=TGT_MIN,N60&lt;=TGT_MAX),IF(P60="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -21196,11 +21303,11 @@
         <v/>
       </c>
       <c r="D61" s="13">
-        <f>IF(J61="計画なし","－",IF(J61="策定済","✕",IF(H61="","？",IF(AND(H61&gt;='集計・設定'!$C$4,H61&lt;='集計・設定'!$C$5),IF(J61="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J61="計画なし","－",IF(J61="策定済","✕",IF(H61="","？",IF(AND(H61&gt;=TGT_MIN,H61&lt;=TGT_MAX),IF(J61="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E61" s="13">
-        <f>IF(P61="計画なし","－",IF(P61="策定済","✕",IF(N61="","？",IF(AND(N61&gt;='集計・設定'!$C$4,N61&lt;='集計・設定'!$C$5),IF(P61="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P61="計画なし","－",IF(P61="策定済","✕",IF(N61="","？",IF(AND(N61&gt;=TGT_MIN,N61&lt;=TGT_MAX),IF(P61="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -21279,11 +21386,11 @@
         <v/>
       </c>
       <c r="D62" s="13">
-        <f>IF(J62="計画なし","－",IF(J62="策定済","✕",IF(H62="","？",IF(AND(H62&gt;='集計・設定'!$C$4,H62&lt;='集計・設定'!$C$5),IF(J62="着手済","△","◎"),"✕"))))</f>
+        <f>IF(J62="計画なし","－",IF(J62="策定済","✕",IF(H62="","？",IF(AND(H62&gt;=TGT_MIN,H62&lt;=TGT_MAX),IF(J62="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="E62" s="13">
-        <f>IF(P62="計画なし","－",IF(P62="策定済","✕",IF(N62="","？",IF(AND(N62&gt;='集計・設定'!$C$4,N62&lt;='集計・設定'!$C$5),IF(P62="着手済","△","◎"),"✕"))))</f>
+        <f>IF(P62="計画なし","－",IF(P62="策定済","✕",IF(N62="","？",IF(AND(N62&gt;=TGT_MIN,N62&lt;=TGT_MAX),IF(P62="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -21351,17 +21458,33 @@
   </sheetData>
   <autoFilter ref="A3:T62"/>
   <conditionalFormatting sqref="A4:T62">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>LEFT($C4,1)="◎"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="6" dxfId="1">
       <formula>LEFT($C4,1)="△"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="7" dxfId="2">
       <formula>LEFT($C4,1)="？"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="8" dxfId="3">
       <formula>LEFT($C4,1)="✕"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H62">
+    <cfRule type="expression" priority="1" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(H4),H4&gt;=TGT_MIN,H4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND(ISNUMBER(H4),H4=TGT_MAX+1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N62">
+    <cfRule type="expression" priority="3" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(N4),N4&gt;=TGT_MIN,N4&lt;=TGT_MAX)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="5">
+      <formula>AND(ISNUMBER(N4),N4=TGT_MAX+1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
+++ b/research/東北6県_公共交通計画_環境基本計画_終期一覧_2026-09.xlsx
@@ -1592,7 +1592,7 @@
       </c>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>交通：R7.3策定、R7〜R11の5年間。R1.10策定の地域公共交通網形成計画を継承。策定支援業務委託はR6.5公告（NJSS https://www2.njss.info/offers/view/29276332）。環境：第二次計画のページは確認したが計画期間は検索結果で確認できず（要確認）。</t>
+          <t>交通：R7.3策定、R7〜R11の5年間。R1.10策定の地域公共交通網形成計画を継承。策定支援業務委託はR6.5公告（NJSS https://www2.njss.info/offers/view/29276332）。環境：第二次計画のページは確認したが計画期間は検索結果で確認できず（要確認）。 【追加調査 2026-10】環境：一般検索・市サイト限定検索（計4回）とも第二次黒石市環境基本計画のページ（http://www.city.kuroishi.aomori.jp/shisei/keikaku/kankyou-kihon-keikaku.html）は出るが計画期間の記載は検索結果に出ず。検索要約に『第3次黒石市環境基本計画』が掲載されている旨の言及が2回あったが、完全一致検索ではヒットせず未確認（同ページに第3次が追加された可能性あり、要確認）。R2.3頃のパブコメページ http://www.city.kuroishi.aomori.jp/shisei/comments/2020-0327-2054-15.html あり（内容未確認）。市サイトはWebFetchブロック。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S7" s="15" t="inlineStr">
@@ -1675,7 +1675,7 @@
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.6策定（パブコメR5.4.17〜5.16）。期間は検索結果で未確認のため5年と仮定した推定値（要確認）。R6.3に五所川原市地域公共交通推進計画（R6〜R10、確認済 https://www.city.goshogawara.lg.jp/jouhou/keikaku/files/koutuu_suisin.pdf）。H28.3網形成計画・H30.3再編実施計画あり。環境：環境基本計画は検索で見当たらず。代替として五所川原市地球温暖化対策実行計画（区域施策編）が存在する模様（https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/planR2_gaiyouban.pdf の可能性）。事務事業編相当は環境保全率先行動計画（H21〜H25）。 【ファクトチェック 2026-10-01: 誤り】確認期間: R5〜R10（令和5年6月策定、令和10年度までの取組を定める）／次期: 確認できず（次期計画の策定支援業務・パブコメは見当たらず。概要版が gaiyouR7.1/R7.6/R8.1 と更新されており、R8.1時点で計画の変更あり）／根拠: https://www.city.goshogawara.lg.jp/kurashi/machi/files/suishinnkeikaku-gaiyou.ver.pdf</t>
+          <t>交通：R5.6策定（パブコメR5.4.17〜5.16）。期間は検索結果で未確認のため5年と仮定した推定値（要確認）。R6.3に五所川原市地域公共交通推進計画（R6〜R10、確認済 https://www.city.goshogawara.lg.jp/jouhou/keikaku/files/koutuu_suisin.pdf）。H28.3網形成計画・H30.3再編実施計画あり。環境：環境基本計画は検索で見当たらず。代替として五所川原市地球温暖化対策実行計画（区域施策編）が存在する模様（https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/planR2_gaiyouban.pdf の可能性）。事務事業編相当は環境保全率先行動計画（H21〜H25）。 【ファクトチェック 2026-10-01: 誤り】確認期間: R5〜R10（令和5年6月策定、令和10年度までの取組を定める）／次期: 確認できず（次期計画の策定支援業務・パブコメは見当たらず。概要版が gaiyouR7.1/R7.6/R8.1 と更新されており、R8.1時点で計画の変更あり）／根拠: https://www.city.goshogawara.lg.jp/kurashi/machi/files/suishinnkeikaku-gaiyou.ver.pdf 【追加調査 2026-10】環境：市サイト限定検索・完全一致検索とも『五所川原市環境基本計画』『環境基本条例』は見当たらず。環境関連は一般廃棄物処理基本計画（R3〜R12, https://www.city.goshogawara.lg.jp/kurashi/kurashi/files/pianR2.pdf）、生活排水基本計画、環境保全率先行動計画、ゼロカーボンシティ宣言のみヒット。計画なしの明示的根拠はないため未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S8" s="18" t="inlineStr">
@@ -1752,18 +1752,18 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q9" s="11" t="n"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：計画期間R5〜R9（5か年、検索結果で確認）。概要版 https://www.city.towada.lg.jp/kurashi/koutsu/files/gaiyouban.pdf 。策定支援業務仕様書 https://www.city.towada.lg.jp/kurashi/koutsu/files/shiyousyo.pdf あり（日付不明、現行計画策定時のものの可能性が高い。次期計画分かは要確認）。R9終了のため次期計画はR8〜R9に着手見込み。環境：環境基本計画は検索で見当たらず。R7.3に十和田市地球温暖化対策実行計画（区域施策編）策定（https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/keikakugaiyouban.pdf）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（2023〜2027年度）／次期: 確認できず（市サイト内検索で次期計画の策定支援プロポーザル・協議会審議は見当たらず。前回はR4年度にプロポーザル https://www.city.towada.lg.jp/kurashi/koutsuu/koutsuukeikaku.ht／根拠: https://www.city.towada.lg.jp/kurashi/koutsuu/files/keikaku.pdf</t>
-        </is>
-      </c>
-      <c r="S9" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：計画期間R5〜R9（5か年、検索結果で確認）。概要版 https://www.city.towada.lg.jp/kurashi/koutsu/files/gaiyouban.pdf 。策定支援業務仕様書 https://www.city.towada.lg.jp/kurashi/koutsu/files/shiyousyo.pdf あり（日付不明、現行計画策定時のものの可能性が高い。次期計画分かは要確認）。R9終了のため次期計画はR8〜R9に着手見込み。環境：環境基本計画は検索で見当たらず。R7.3に十和田市地球温暖化対策実行計画（区域施策編）策定（https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/keikakugaiyouban.pdf）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（2023〜2027年度）／次期: 確認できず（市サイト内検索で次期計画の策定支援プロポーザル・協議会審議は見当たらず。前回はR4年度にプロポーザル https://www.city.towada.lg.jp/kurashi/koutsuu/koutsuukeikaku.ht／根拠: https://www.city.towada.lg.jp/kurashi/koutsuu/files/keikaku.pdf 【追加調査 2026-10】環境：市サイト限定検索で環境基本計画は見当たらず。十和田市地球温暖化対策実行計画（区域施策編）案（2025/1/16版、計画期間2025〜2030年度 https://www.city.towada.lg.jp/shisei/gyousei/machidukuri/files/kuikisesakuhenan.pdf）の整合・連携先として第2次総合計画・都市計画MP・森林整備計画・国土強靭化計画・地域公共交通計画等が列挙されるが環境基本計画は挙がっておらず、環境分野の総合計画は区域施策編＋事務事業編（とわだエコ・オフィスプラン）で代替とみられる。確認日2026-10-02。</t>
+        </is>
+      </c>
+      <c r="S9" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T9" s="11" t="inlineStr">
@@ -1932,7 +1932,7 @@
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>交通：下北地域公共交通総合連携協議会（むつ市・大間町・東通村・風間浦村・佐井村）がR7.3策定、2025〜2029。URLは素案PDF（パブコメR7.2.17〜3.3）。前計画はH30.3の下北地域公共交通網形成計画。市単独ではむつ市公共交通再編関連資料（2026）https://www.city.mutsu.lg.jp/kurashi/koutsu/koutsu_sisaku/files/mutsu_kokyokotsusaihen_2026.pdf あり（地域公共交通計画ではなく再編計画の可能性）。環境：環境基本計画は検索で見当たらず。第4期むつ市地球温暖化対策推進実行計画（事務事業編）R7.6策定（https://www.city.mutsu.lg.jp/kurashi/kankyo/kankyo/files/ondankakeikaku4.pdf）。</t>
+          <t>交通：下北地域公共交通総合連携協議会（むつ市・大間町・東通村・風間浦村・佐井村）がR7.3策定、2025〜2029。URLは素案PDF（パブコメR7.2.17〜3.3）。前計画はH30.3の下北地域公共交通網形成計画。市単独ではむつ市公共交通再編関連資料（2026）https://www.city.mutsu.lg.jp/kurashi/koutsu/koutsu_sisaku/files/mutsu_kokyokotsusaihen_2026.pdf あり（地域公共交通計画ではなく再編計画の可能性）。環境：環境基本計画は検索で見当たらず。第4期むつ市地球温暖化対策推進実行計画（事務事業編）R7.6策定（https://www.city.mutsu.lg.jp/kurashi/kankyo/kankyo/files/ondankakeikaku4.pdf）。 【追加調査 2026-10】環境：市サイト限定検索・完全一致検索（『むつ市環境基本計画』『むつ市環境基本条例』）とも該当なし。生活環境ページ https://www.city.mutsu.lg.jp/kurashi/kankyo/kankyo/ には地球温暖化対策推進実行計画・緑の基本計画等のみ。計画なしの明示的根拠はないため未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S11" s="18" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>交通：地域公共交通計画は検索で確認できず。つがる市地域公共交通会議（H20.9設置）https://www.city.tsugaru.aomori.jp/soshiki/somu/tiikisousei/kikakusinnkou/kokyokotu/6434.html 。環境：第2次計画のページは確認、期間不明。区域施策編は西つがる3市町（つがる市・鰺ヶ沢町・深浦町）共同で策定（R6.3パブコメ https://www.town.fukaura.lg.jp/fixed_docs/2024032100017/）。</t>
+          <t>交通：地域公共交通計画は検索で確認できず。つがる市地域公共交通会議（H20.9設置）https://www.city.tsugaru.aomori.jp/soshiki/somu/tiikisousei/kikakusinnkou/kokyokotu/6434.html 。環境：第2次計画のページは確認、期間不明。区域施策編は西つがる3市町（つがる市・鰺ヶ沢町・深浦町）共同で策定（R6.3パブコメ https://www.town.fukaura.lg.jp/fixed_docs/2024032100017/）。 【追加調査 2026-10】環境：市サイト限定検索で『つがる市環境基本計画』一覧 https://www.city.tsugaru.aomori.jp/soshiki/minsei/shimin/kankyoeisei/gomi/kankyoukihonkeikaku/index.html と第2次計画ページ（10184.html、PDF約10MB公開、つがる市環境基本条例に基づく計画）を確認。計画期間・策定年は検索結果で確認できず（計4回検索）。市サイトはWebFetchブロック。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S12" s="18" t="inlineStr">
@@ -2181,18 +2181,18 @@
       </c>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q14" s="11" t="n"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>交通：町HPに計画掲載、令和3年度策定と検索結果に記載（期間は未確認、5年計画と仮定しR4〜R8推定）。R8終了なら次期改定の動きに注意。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
-        </is>
-      </c>
-      <c r="S14" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：町HPに計画掲載、令和3年度策定と検索結果に記載（期間は未確認、5年計画と仮定しR4〜R8推定）。R8終了なら次期改定の動きに注意。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：町サイト限定検索（town.hiranai.aomori.jp）で環境基本計画は見当たらず。町民課所管の環境関連計画として出るのは平内町地球温暖化対策実行計画（事務事業編、R2.3策定、R2〜R6）https://www.town.hiranai.aomori.jp/soshiki/chomin/1/3/1/chikyuondankataisaku01.html 、一般廃棄物処理基本計画、災害廃棄物処理計画のみ。環境分野は第六次平内町長期振興計画 https://www.town.hiranai.aomori.jp/soshiki/kikaku/1/1/2/414.html の分野別計画で扱う。町の計画一覧（まちづくり・計画 https://www.town.hiranai.aomori.jp/chosei/machizukuri/index.html ）にも無く計画なしと判断（明示的な記載ではない点に留意）。確認日2026-10-02。</t>
+        </is>
+      </c>
+      <c r="S14" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr">
@@ -2270,7 +2270,7 @@
       <c r="Q15" s="11" t="n"/>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>交通：策定支援業務プロポーザル2022-10（https://www.town.imabetsu.lg.jp/news/gyousei/2022-1017-1745-1.html）、計画公表ページ2023-08-28。期間は検索結果で未確認（R5〜R9推定）。JR津軽線蟹田〜三厩は2027年4月廃止・バス/乗合タクシー転換予定（NPO今別外ヶ浜交通）で計画見直しの可能性あり。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（5年間）／次期: 確認できず（次期計画の策定業務・アンケートは見当たらず。ただしJR津軽線蟹田以北について、代行バス・わんタク・町営バス等を統合した自動車交通を令和9年4月1日から運行予定（広報今別733号 https://www.town.imabetsu／根拠: https://www.town.imabetsu.lg.jp/gyousei/koukai/2023-0828-1639-1.html</t>
+          <t>交通：策定支援業務プロポーザル2022-10（https://www.town.imabetsu.lg.jp/news/gyousei/2022-1017-1745-1.html）、計画公表ページ2023-08-28。期間は検索結果で未確認（R5〜R9推定）。JR津軽線蟹田〜三厩は2027年4月廃止・バス/乗合タクシー転換予定（NPO今別外ヶ浜交通）で計画見直しの可能性あり。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（5年間）／次期: 確認できず（次期計画の策定業務・アンケートは見当たらず。ただしJR津軽線蟹田以北について、代行バス・わんタク・町営バス等を統合した自動車交通を令和9年4月1日から運行予定（広報今別733号 https://www.town.imabetsu／根拠: https://www.town.imabetsu.lg.jp/gyousei/koukai/2023-0828-1639-1.html 【追加調査 2026-10】環境：町サイト限定検索（town.imabetsu.lg.jp）で『環境基本計画』『地球温暖化対策実行計画』とも該当なし。町の施策一覧 https://www.town.imabetsu.lg.jp/gyousei/shisaku/ には総合計画（第6次、R7〜R16 https://www.town.imabetsu.lg.jp/gyousei/shisaku/files/No.6_sougou.pdf ）・総合戦略・地域公共交通計画等のみで、脱炭素は総合計画内で言及。計画なしの可能性大だが明示根拠に乏しく未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S15" s="18" t="inlineStr">
@@ -2343,7 +2343,7 @@
       <c r="Q16" s="11" t="n"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>交通：村名検索・村HP内検索で地域公共交通計画は見当たらず（公共交通ページ https://www.vill.yomogita.lg.jp/kurashi/kotsu/ のみ）。青森市計画は市単独。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：村名検索・村HP内検索で地域公共交通計画は見当たらず（公共交通ページ https://www.vill.yomogita.lg.jp/kurashi/kotsu/ のみ）。青森市計画は市単独。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：村サイト限定検索（vill.yomogita.lg.jp）で環境基本計画は見当たらず。計画ページ https://www.vill.yomogita.lg.jp/sonsei/keikaku/ には過疎計画（R3〜R7）・青森圏域国土強靱化地域計画等。検索要約で『蓬田村地球温暖化対策推進実行計画』の存在が示唆されたがURL未確認。計画なしの確証はなく未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S16" s="18" t="inlineStr">
@@ -2420,18 +2420,18 @@
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>交通計画は2024年2月27日パブコメ実施（URLは同パブコメページ、期間は5年と推定）。JR津軽線蟹田〜三厩の代行・転換が絡む。環境基本計画は確認できず（今回検索でも見当たらず）、代替として地球温暖化対策実行計画（区域施策編）令和8年3月策定: https://www.town.sotogahama.lg.jp/gyosei/keikaku/files/01_soto_kuikisesaku_plan.pdf 環境基本計画は検索で確認できず（計画なしの確証なし）。</t>
-        </is>
-      </c>
-      <c r="S17" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通計画は2024年2月27日パブコメ実施（URLは同パブコメページ、期間は5年と推定）。JR津軽線蟹田〜三厩の代行・転換が絡む。環境基本計画は確認できず（今回検索でも見当たらず）、代替として地球温暖化対策実行計画（区域施策編）令和8年3月策定: https://www.town.sotogahama.lg.jp/gyosei/keikaku/files/01_soto_kuikisesaku_plan.pdf 環境基本計画は検索で確認できず（計画なしの確証なし）。 【追加調査 2026-10】環境：町サイト限定検索で環境基本計画は見当たらず。各種計画ページ https://www.town.sotogahama.lg.jp/gyosei/keikaku/ の環境系は外ヶ浜町地球温暖化対策実行計画（区域施策編、2026-03-24策定）https://www.town.sotogahama.lg.jp/gyosei/keikaku/files/01_soto_kuikisesaku_plan.pdf と事務事業編（2020.3）https://www.town.sotogahama.lg.jp/kurashi/kankyo/2021-1022-ontaiho.html 、一般廃棄物処理基本計画のみ。2023.9ゼロカーボンシティ宣言。区域施策編のみで環境基本計画なしと判断。確認日2026-10-02。</t>
+        </is>
+      </c>
+      <c r="S17" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T17" s="11" t="inlineStr">
@@ -2503,18 +2503,18 @@
       </c>
       <c r="P18" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>交通：旧メモ「単独計画は確認できず」は誤り。町HPで2024年3月策定を確認（パブコメ http://www.town.ajigasawa.lg.jp/gyosei_jyoho/publiccomment/kokyokotukeikaku.html）。期間は未確認で5年と仮定しR6〜R10推定。五所川原圏域定住自立圏構成町。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
-        </is>
-      </c>
-      <c r="S18" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：旧メモ「単独計画は確認できず」は誤り。町HPで2024年3月策定を確認（パブコメ http://www.town.ajigasawa.lg.jp/gyosei_jyoho/publiccomment/kokyokotukeikaku.html）。期間は未確認で5年と仮定しR6〜R10推定。五所川原圏域定住自立圏構成町。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：『鰺ヶ沢町 環境基本計画』検索・町サイト限定検索（環境基本計画/環境計画/環境基本条例）とも環境基本計画は見当たらず。環境分野は西つがる3市町（五所川原市・鰺ヶ沢町・深浦町）共同の地球温暖化対策実行計画（区域施策編） http://www.town.ajigasawa.lg.jp/gyosei_jyoho/keikaku/kikakusinkou240516.html と再生可能エネルギー導入計画 https://www.town.ajigasawa.lg.jp/gyosei_jyoho/keikaku/seisakusaiene.html のみ（区域施策編のみ）。町計画一覧 https://www.town.ajigasawa.lg.jp/gyosei_jyoho/keikaku/index.html はWebFetchブロックで目視不可。確認日2026-10-02</t>
+        </is>
+      </c>
+      <c r="S18" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr">
@@ -2586,18 +2586,18 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>交通：計画書表紙「令和6年4月」。前計画は深浦町地域公共交通網形成計画（2020年3月策定）。期間は未確認で5年と仮定しR6〜R10推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
-        </is>
-      </c>
-      <c r="S19" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：計画書表紙「令和6年4月」。前計画は深浦町地域公共交通網形成計画（2020年3月策定）。期間は未確認で5年と仮定しR6〜R10推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画は見当たらず。環境系は西つがる3市町地球温暖化対策実行計画［区域施策編］ https://www.town.fukaura.lg.jp/fixed_docs/2024032100017/ 、西つがる3市町再エネ導入計画 https://www.town.fukaura.lg.jp/fixed_docs/2024052000038/ 、循環型社会形成推進地域計画のみ（区域施策編のみ）。確認日2026-10-02</t>
+        </is>
+      </c>
+      <c r="S19" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T19" s="11" t="inlineStr">
@@ -2659,18 +2659,18 @@
       </c>
       <c r="P20" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q20" s="11" t="n"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>交通：村HP内検索で地域公共交通計画は見当たらず（コミュニティバスのみ https://www.nishimeya.jp/kurashi_tetsuzuki/kokyokotsu/300.html）。弘前市地域公共交通計画（R6.3）は市単独とみられる。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境：村HP内検索で環境基本計画は見当たらず（再生可能エネルギー振興策 https://www.nishimeya.jp/sonseijoho/seisaku_keikaku/5/7/228.html、災害廃棄物処理計画R8.1はあり）。計画なしの可能性が高いが確証なく未確認。</t>
+          <t>交通：村HP内検索で地域公共交通計画は見当たらず（コミュニティバスのみ https://www.nishimeya.jp/kurashi_tetsuzuki/kokyokotsu/300.html）。弘前市地域公共交通計画（R6.3）は市単独とみられる。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境：村HP内検索で環境基本計画は見当たらず（再生可能エネルギー振興策 https://www.nishimeya.jp/sonseijoho/seisaku_keikaku/5/7/228.html、災害廃棄物処理計画R8.1はあり）。計画なしの可能性が高いが確証なく未確認。 【追加調査 2026-10】環境：村名検索・村サイト限定検索で環境基本計画は見当たらず。西目屋村地球温暖化対策実行計画（区域施策編、2024年3月策定） https://www.nishimeya.jp/sonseijoho/gyozaisei/872.html 、バイオマス活用推進計画、再エネ振興策のみ（区域施策編のみ）。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S20" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T20" s="11" t="inlineStr">
@@ -2732,18 +2732,18 @@
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン・総合計画のみ）。弘前圏域8市町村の弘南鉄道維持活性化基本方針（2020）あり。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン・総合計画のみ）。弘前圏域8市町村の弘南鉄道維持活性化基本方針（2020）あり。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画は見当たらず。藤崎町地球温暖化対策実行計画（R7策定、計画期間R8〜R12、2030年度52%削減・検索要約による） https://www.town.fujisaki.lg.jp/index.cfm/7,23198,24,339,html のみ（区域施策編のみ）。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S21" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T21" s="11" t="inlineStr">
@@ -2821,7 +2821,7 @@
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>町HP「大鰐町地域公共交通計画策定について」ページに計画PDF（ファイル名R5.5.pdf）掲載→R5.5策定と見られ、5年計画ならR5〜R9（期間は未確認・推定）。過去に計画案策定支援業務の公募型プロポーザル実施: http://www.town.owani.lg.jp/news/index.cfm/detail.1.12187.html （日付未確認）。弘南鉄道大鰐線は運行休止/廃止方向で交通再編の動きあり。環境基本計画・温対計画は検索で見当たらず。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず（関連: 弘南鉄道大鰐線は2028年3月末で運行休止と発表され、代替交通は県主催の検討会議で調整中 https://trafficnews.jp/post/592513）／根拠: http://www.town.owani.lg.jp/aboutowani/plan/kokyo-kotsu.html</t>
+          <t>町HP「大鰐町地域公共交通計画策定について」ページに計画PDF（ファイル名R5.5.pdf）掲載→R5.5策定と見られ、5年計画ならR5〜R9（期間は未確認・推定）。過去に計画案策定支援業務の公募型プロポーザル実施: http://www.town.owani.lg.jp/news/index.cfm/detail.1.12187.html （日付未確認）。弘南鉄道大鰐線は運行休止/廃止方向で交通再編の動きあり。環境基本計画・温対計画は検索で見当たらず。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず（関連: 弘南鉄道大鰐線は2028年3月末で運行休止と発表され、代替交通は県主催の検討会議で調整中 https://trafficnews.jp/post/592513）／根拠: http://www.town.owani.lg.jp/aboutowani/plan/kokyo-kotsu.html 【追加調査 2026-10】【2026-10-02調査】検索3回（計画期間・次期計画/プロポ）で、町HP http://www.town.owani.lg.jp/aboutowani/plan/kokyo-kotsu.html のPDF（R5.5.pdf）以外に期間を示す本文は得られず、R5〜R9は推定のまま。町サイトはWebFetch不可（egress blocked）。次期計画の委託・パブコメ等は検索で見当たらず。 【追加調査 2026-10】環境：町名検索・町サイト限定検索（環境基本計画/温対実行計画/環境基本条例）とも該当なし。町計画ページ（振興計画・都市計画MP・地域防災計画等 http://www.town.owani.lg.jp/aboutowani/plan/shinko.html ）に環境計画は出ず。温対区域施策編も未確認のため根拠弱く未確認。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S22" s="18" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>交通：村HP内検索で地域公共交通計画は見当たらず。弘南鉄道弘南線・大鰐線 維持活性化支援計画（5市町村、2021年1月）に参加 http://www.vill.inakadate.lg.jp/docs/2021022200016/。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：村HP内検索で地域公共交通計画は見当たらず。弘南鉄道弘南線・大鰐線 維持活性化支援計画（5市町村、2021年1月）に参加 http://www.vill.inakadate.lg.jp/docs/2021022200016/。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：村名検索・村サイト限定検索で環境基本計画・温対実行計画・環境基本条例いずれも該当なし（公共施設等総合管理計画等のみ http://www.vill.inakadate.lg.jp/docs/2016102100010/files/sougoukannri-kaitei.pdf ）。計画なしの可能性高いが確証なく未確認。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S23" s="18" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="Q24" s="11" t="n"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン案R7.2に公共交通の記述あり https://www.town.itayanagi.aomori.jp/administration/salary/files/toshimasu.pdf）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（都市計画マスタープラン案R7.2に公共交通の記述あり https://www.town.itayanagi.aomori.jp/administration/salary/files/toshimasu.pdf）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画・温対実行計画・環境基本条例いずれもヒットなし（地域再生計画の汚水処理関連のみ）。計画なしの可能性高いが確証なく未確認。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S24" s="18" t="inlineStr">
@@ -3034,18 +3034,18 @@
       </c>
       <c r="P25" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（各種計画ページ https://www.town.tsuruta.lg.jp/syoukai/syoukai-kakusyu/index.html に該当表示なし、要目視確認）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。</t>
+          <t>交通：町名検索・町HP内検索で地域公共交通計画は見当たらず（各種計画ページ https://www.town.tsuruta.lg.jp/syoukai/syoukai-kakusyu/index.html に該当表示なし、要目視確認）。なお青森県地域公共交通計画（R5〜R9、県全域）は県計画として全市町村を対象。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画は見当たらず。各種計画ページ https://www.town.tsuruta.lg.jp/syoukai/syoukai-kakusyu/index.html には鶴田町地域脱炭素実行計画（温対法21条4項の区域施策編・気候変動適応計画兼ねる、R7〜R12、2025年4月策定） https://www.town.tsuruta.lg.jp/info/document/jikko_keikaku.pdf が掲載（区域施策編のみ）。ページはWebFetchブロックで目視未了。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T25" s="11" t="inlineStr">
@@ -3117,18 +3117,18 @@
       </c>
       <c r="P26" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q26" s="11" t="n"/>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>交通：計画書表紙「令和5年4月」、計画ページ https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 。ファイル名にr6とあり令和6年に改訂の可能性。期間は未確認で5年と仮定しR5〜R9推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（町のプロポーザル一覧に交通計画関連は見当たらず）／根拠: https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html</t>
-        </is>
-      </c>
-      <c r="S26" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：計画書表紙「令和5年4月」、計画ページ https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 。ファイル名にr6とあり令和6年に改訂の可能性。期間は未確認で5年と仮定しR5〜R9推定。環境基本計画は町/村名検索・公式サイト内検索で見当たらず（計画なしの確証はないため未確認）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（町のプロポーザル一覧に交通計画関連は見当たらず）／根拠: https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/5/1/1/4311.html 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画は見当たらず。中泊町地球温暖化対策実行計画（事務事業編・区域施策編）、再エネ導入戦略、NAKAZERO共創アクション（脱炭素行動計画、R8.4策定、脱炭素先行地域選定） https://www.town.nakadomari.lg.jp/soshikikarasagasu/sogosenryakuka/gyomuannai/tikyuuondankataisaku/5369.html のみ（区域施策編のみ）。確認日2026-10-02</t>
+        </is>
+      </c>
+      <c r="S26" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T26" s="11" t="inlineStr">
@@ -3196,7 +3196,7 @@
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>交通・環境とも町単独計画は検索で確認できず（町HP「まちの計画」 https://www.town.noheji.aomori.jp/life/chosei/machidukuri/machi-keikaku は存在するが内容未確認、町サイトは取得不可）。地域間幹線系統確保維持費補助金交付要綱あり https://www.town.noheji.aomori.jp/reiki_int/reiki_honbun/c041RG00000724.html 。改定作業の情報なし。</t>
+          <t>交通・環境とも町単独計画は検索で確認できず（町HP「まちの計画」 https://www.town.noheji.aomori.jp/life/chosei/machidukuri/machi-keikaku は存在するが内容未確認、町サイトは取得不可）。地域間幹線系統確保維持費補助金交付要綱あり https://www.town.noheji.aomori.jp/reiki_int/reiki_honbun/c041RG00000724.html 。改定作業の情報なし。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画・温対実行計画・環境基本条例いずれも見当たらず（ヒットは地域防災計画・過疎計画R3〜R7等。過疎計画内に温暖化対策の記述あり https://www.town.noheji.aomori.jp/application/files/8816/4030/5415/ebdf28da23a799a96da8885110e20596.pdf ）。町サイトWebFetch不可。確証なく未確認。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S27" s="18" t="inlineStr">
@@ -3271,18 +3271,18 @@
       </c>
       <c r="P28" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q28" s="11" t="n"/>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>網形成計画（策定支援プロポ: http://www.town.shichinohe.lg.jp/jigyo/nyuusatsu/post-65.html）。期間未確認で既に期限切れの可能性、後継の地域公共交通計画は未確認（H21に地域公共交通会議設置・総合連携計画策定の経緯あり）。環境基本計画は確認できず、関連として地域省エネルギー重点ビジョン（H22）あり（計画なしは弱い根拠）。 環境基本計画は検索で確認できず（計画なしの確証なし）。</t>
-        </is>
-      </c>
-      <c r="S28" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>網形成計画（策定支援プロポ: http://www.town.shichinohe.lg.jp/jigyo/nyuusatsu/post-65.html）。期間未確認で既に期限切れの可能性、後継の地域公共交通計画は未確認（H21に地域公共交通会議設置・総合連携計画策定の経緯あり）。環境基本計画は確認できず、関連として地域省エネルギー重点ビジョン（H22）あり（計画なしは弱い根拠）。 環境基本計画は検索で確認できず（計画なしの確証なし）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索・条例検索で環境基本計画/環境基本条例は見当たらず。七戸町地球温暖化対策実行計画（区域施策編、令和6年3月） https://www.town.shichinohe.lg.jp/gyosei/2024/d97c0d43297ff492dc72aae03439179b.pdf が町政情報に掲載（区域施策編のみ）。他に地域省エネルギー重点ビジョン（H22）。確認日2026-10-02</t>
+        </is>
+      </c>
+      <c r="S28" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T28" s="17" t="inlineStr">
@@ -3350,7 +3350,7 @@
       <c r="Q29" s="11" t="n"/>
       <c r="R29" s="11" t="inlineStr">
         <is>
-          <t>交通計画は未確認だが、2026年8月31日に「交通まちづくりワークショップ」開催告知（町バス利用者・学生・保護者・事業者対象）: https://www.town.rokunohe.aomori.jp/docs/2026083100015 。地域公共交通計画策定に向けた作業と推定（計画名・プロポは未確認）。環境基本計画・温対計画は検索で見当たらず。</t>
+          <t>交通計画は未確認だが、2026年8月31日に「交通まちづくりワークショップ」開催告知（町バス利用者・学生・保護者・事業者対象）: https://www.town.rokunohe.aomori.jp/docs/2026083100015 。地域公共交通計画策定に向けた作業と推定（計画名・プロポは未確認）。環境基本計画・温対計画は検索で見当たらず。 【追加調査 2026-10】環境：町名検索・町サイト限定検索で環境基本計画・温対実行計画・環境基本条例いずれも見当たらず（公共施設等総合管理計画H29等のみ https://www.town.rokunohe.aomori.jp/file/chousei/shisaku/kokyoshisetsusougoukanriplan/kokyoshisetsusougoukanriplan.pdf ）。確証なく未確認。確認日2026-10-02</t>
         </is>
       </c>
       <c r="S29" s="18" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="Q30" s="11" t="n"/>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>町単独の地域公共交通計画は確認できず。下北地域公共交通計画（2025年3月策定、下北地域公共交通総合連携協議会）の対象はむつ市・大間町・東通村・風間浦村・佐井村の5市町村で横浜町は含まれない（むつ市資料 https://www.city.mutsu.lg.jp/government/katsudou/kyoudou/files/04kotsu.pdf で確認）。下北半島都市圏広域立地適正化方針（R5.8）には含まれる。町HPに2026-04-10付PDFあり内容未確認 https://www.town.yokohama.lg.jp/index.cfm/6,9299,c,html/9299/20260410-143501.pdf 。環境基本計画・区域施策編も検索で見当たらず（横浜市との再エネ連携協定はあり）。</t>
+          <t>町単独の地域公共交通計画は確認できず。下北地域公共交通計画（2025年3月策定、下北地域公共交通総合連携協議会）の対象はむつ市・大間町・東通村・風間浦村・佐井村の5市町村で横浜町は含まれない（むつ市資料 https://www.city.mutsu.lg.jp/government/katsudou/kyoudou/files/04kotsu.pdf で確認）。下北半島都市圏広域立地適正化方針（R5.8）には含まれる。町HPに2026-04-10付PDFあり内容未確認 https://www.town.yokohama.lg.jp/index.cfm/6,9299,c,html/9299/20260410-143501.pdf 。環境基本計画・区域施策編も検索で見当たらず（横浜市との再エネ連携協定はあり）。 【追加調査 2026-10】環境：環境基本計画は町名検索・町サイト(town.yokohama.lg.jp)限定検索ともヒットせず。町サイトではゼロカーボンシティ宣言ページに地球温暖化対策実行計画（事務事業編、R6.3策定）と、今後区域施策編を策定予定との記載のみ https://www.town.yokohama.lg.jp/index.cfm/6,11904,18,194,html 。環境基本計画の有無は断定できず未確認のまま。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S30" s="18" t="inlineStr">
@@ -3490,18 +3490,18 @@
       </c>
       <c r="P31" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>東北町地域公共交通会議あり（会議録 https://www.town.tohoku.lg.jp/chousei/info/info_yakuba_03-54.html ）。地域公共交通計画の有無は検索で確認できず（東北運輸局の計画一覧PDF https://wwwtb.mlit.go.jp/tohoku/content/000338501.pdf がヒットしたが中身未確認）。環境基本計画も見当たらず、関連は「小川原湖環境再生」計画（地域再生計画、汚水処理）程度。第2期まち・ひと・しごと創生推進計画はR8.4〜R13.3。</t>
+          <t>東北町地域公共交通会議あり（会議録 https://www.town.tohoku.lg.jp/chousei/info/info_yakuba_03-54.html ）。地域公共交通計画の有無は検索で確認できず（東北運輸局の計画一覧PDF https://wwwtb.mlit.go.jp/tohoku/content/000338501.pdf がヒットしたが中身未確認）。環境基本計画も見当たらず、関連は「小川原湖環境再生」計画（地域再生計画、汚水処理）程度。第2期まち・ひと・しごと創生推進計画はR8.4〜R13.3。 【追加調査 2026-10】環境：町サイト限定検索で環境基本計画はヒットせず、代わりに東北町地球温暖化対策実行計画（区域施策編）（計画期間2026〜2035＝R8〜R17、2030年度50%削減・2050実質ゼロ）の策定業務プロポーザル資料・計画ページのみ（区域施策編で対応）。 https://www.town.tohoku.lg.jp/chousei/info/info_yakuba_09-42.html 、仕様書 https://www.town.tohoku.lg.jp/chousei/info/file/info_yakuba_09-29-02.pdf 。根拠は検索結果ベースでやや弱い。（確認日2026-10-02） 根拠: 計画期間は、2026（令和8）年度から2035（令和17）年度までの10年間（区域施策編・検索要約）</t>
         </is>
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T31" s="11" t="inlineStr">
@@ -3571,18 +3571,18 @@
       </c>
       <c r="P32" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q32" s="11" t="n"/>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>R7.3策定（素案住民意見聴取後）。計画ページ https://www.rokkasho.jp/index.cfm/11,19571,31,177,html 。R7.6に計画に基づく再編・見直し検討及び実証運行支援業務の公募型プロポーザル実施 https://www.rokkasho.jp/index.cfm/14,19918,31,177,html 。環境基本計画は検索で見当たらず（関連: 水環境保全計画、地域新エネルギービジョン、バイオマスタウン構想）。</t>
-        </is>
-      </c>
-      <c r="S32" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>R7.3策定（素案住民意見聴取後）。計画ページ https://www.rokkasho.jp/index.cfm/11,19571,31,177,html 。R7.6に計画に基づく再編・見直し検討及び実証運行支援業務の公募型プロポーザル実施 https://www.rokkasho.jp/index.cfm/14,19918,31,177,html 。環境基本計画は検索で見当たらず（関連: 水環境保全計画、地域新エネルギービジョン、バイオマスタウン構想）。 【追加調査 2026-10】環境：村サイト限定検索で環境基本計画はヒットせず。代わりに六ヶ所村地球温暖化対策実行計画（区域施策編）（R6.3策定、R6〜R15、ゼロカーボンシティ宣言R4.12）http://www.rokkasho.jp/index.cfm/10,17954,31,124,html 、新エネルギー推進計画、水環境保全計画あり。区域施策編等の個別計画で対応と判断（根拠は検索結果ベース）。（確認日2026-10-02） 根拠: 区域施策編の計画期間 令和6年度～令和15年度（検索要約）</t>
+        </is>
+      </c>
+      <c r="S32" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr">
@@ -3660,7 +3660,7 @@
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は町名検索・ゼロカーボン検索とも該当なし（地域再生計画等のみヒット）。区域施策編も未確認。</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は町名検索・ゼロカーボン検索とも該当なし（地域再生計画等のみヒット）。区域施策編も未確認。 【追加調査 2026-10】環境：町名検索・町サイト限定検索とも環境基本計画はヒットせず。町サイトでは第2次総合計画後期基本計画（R6〜R10）https://www.town.oirase.aomori.jp/uploaded/attachment/22191.pdf の環境保全施策、都市計画MP、地球温暖化対策実行計画（事務事業編）、自然・地域と再生可能エネルギー共生審議会 https://www.town.oirase.aomori.jp/soshiki/1232/kanykoukyousei.html のみ。区域施策編も確認できず。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S33" s="18" t="inlineStr">
@@ -3743,7 +3743,7 @@
       <c r="Q34" s="11" t="n"/>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
+          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。 【追加調査 2026-10】環境：環境基本計画は検索でヒットせず。町サイト(town.ooma.lg.jp)の公表情報一覧に第3次地球温暖化対策実行計画（2024-12-13公表、事務事業編とみられる）、第2次(2019)、第1次(2013)の記載あり https://www.town.ooma.lg.jp/allpub_index.html 。環境基本計画の有無は断定できず。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S34" s="18" t="inlineStr">
@@ -3826,7 +3826,7 @@
       <c r="Q35" s="11" t="n"/>
       <c r="R35" s="11" t="inlineStr">
         <is>
-          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画は検索でヒットせず（原発モニタリング・風力アセス関連のみ）。</t>
+          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画は検索でヒットせず（原発モニタリング・風力アセス関連のみ）。 【追加調査 2026-10】環境：環境基本計画は検索でヒットせず（原発関連の環境放射線モニタリング基本計画のみ：県 https://www.pref.aomori.lg.jp/soshiki/kikikanri/atom/higashidori-monitoring-keikaku-R0803.pdf ）。村サイト限定検索は結果なし。温暖化対策実行計画も確認できず。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S35" s="18" t="inlineStr">
@@ -3909,7 +3909,7 @@
       <c r="Q36" s="11" t="n"/>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
+          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。 【追加調査 2026-10】環境：環境基本計画は検索でヒットせず。村サイト(kazamaura.jp)では第2次風間浦村地球温暖化対策実行計画（事務事業編）の2024年度実施状況 https://www.kazamaura.jp/2026/01/27/%E7%AC%AC%EF%BC%92%E6%AC%A1%E9%A2%A8%E9%96%93%E6%B5%A6%E6%9D%91%E5%9C%B0%E7%90%83%E6%B8%A9%E6%9A%96%E5%8C%96%E5%AF%BE%E7%AD%96%E5%AE%9F%E8%A1%8C%E8%A8%88%E7%94%BB%EF%BC%88%E4%BA%8B%E5%8B%99%E4%BA%8B-4/ 、ゼロカーボンシティ宣言（R5.3.1）、ブルーカーボン調査のみ。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S36" s="18" t="inlineStr">
@@ -3992,7 +3992,7 @@
       <c r="Q37" s="11" t="n"/>
       <c r="R37" s="11" t="inlineStr">
         <is>
-          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
+          <t>交通計画は下北5市町村の圏域共同計画（2025〜2029＝R7〜R11、R7.3策定）。t_urlはむつ市サイト掲載の素案PDF（確定版URLは検索で見つからず）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。 【追加調査 2026-10】環境：環境基本計画は検索でヒットせず。村サイト(vill.sai.lg.jp)では脱炭素先行地域（2023.4選定）関連補助金 https://www.vill.sai.lg.jp/status-initiatives/decarbonization/ 、ゼロカーボンシティさい表明、ブルーカーボン推進事業のみ。温暖化対策実行計画の有無も未確認。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S37" s="18" t="inlineStr">
@@ -4069,18 +4069,18 @@
       </c>
       <c r="P38" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q38" s="11" t="n"/>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・地球温暖化対策実行計画とも検索でヒットせず（地域再生計画・風力アセスのみ）。</t>
-        </is>
-      </c>
-      <c r="S38" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・地球温暖化対策実行計画とも検索でヒットせず（地域再生計画・風力アセスのみ）。 【追加調査 2026-10】環境：町名検索・町サイト限定検索とも環境基本計画はヒットせず。代わりに三戸町地球温暖化対策実行計画（事務事業編＋町全体の区域の削減施策を含む、R6〜R12、2030年度58.7%削減）https://www.town.sannohe.aomori.jp/soshiki/soumu/gyouseijouhou/1/4712.html と2050ゼロカーボン宣言。温暖化実行計画で対応と判断（根拠は検索結果ベース）。（確認日2026-10-02） 根拠: 計画期間 令和6年度～令和12年度（温暖化実行計画・検索要約）</t>
+        </is>
+      </c>
+      <c r="S38" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T38" s="11" t="inlineStr">
@@ -4152,18 +4152,18 @@
       </c>
       <c r="P39" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q39" s="11" t="n"/>
       <c r="R39" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は検索でヒットせず。代替として五戸町地球温暖化対策実行計画（区域施策編・地域気候変動適応計画兼ねる、R7.3策定、環境省地域脱炭素実現支援事業で作成）あり：https://www.town.gonohe.aomori.jp/chosei/tikyuondankahonpen.pdf （概要版 https://www.town.gonohe.aomori.jp/chosei/tikyuondankagaiyouban.pdf ）。期間は検索結果で確認できず。環境省策定状況 https://www.env.go.jp/policy/local_keikaku/sakutei2/02/02442.html</t>
-        </is>
-      </c>
-      <c r="S39" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画は検索でヒットせず。代替として五戸町地球温暖化対策実行計画（区域施策編・地域気候変動適応計画兼ねる、R7.3策定、環境省地域脱炭素実現支援事業で作成）あり：https://www.town.gonohe.aomori.jp/chosei/tikyuondankahonpen.pdf （概要版 https://www.town.gonohe.aomori.jp/chosei/tikyuondankagaiyouban.pdf ）。期間は検索結果で確認できず。環境省策定状況 https://www.env.go.jp/policy/local_keikaku/sakutei2/02/02442.html 【追加調査 2026-10】環境：町名検索で環境基本計画はヒットせず、町サイトPDFは五戸町地球温暖化対策実行計画（区域施策編・適応計画兼、R7.3策定、計画期間R7〜R12）https://www.town.gonohe.aomori.jp/chosei/tikyuondankahonpen.pdf 、概要版 https://www.town.gonohe.aomori.jp/chosei/tikyuondankagaiyouban.pdf 、ごみ処理基本計画（R8〜R17）のみ。区域施策編のみと判断。（確認日2026-10-02） 根拠: 令和7（2025）年度から令和12（2030）年度までの6年間（区域施策編概要版・検索要約）</t>
+        </is>
+      </c>
+      <c r="S39" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T39" s="11" t="inlineStr">
@@ -4241,7 +4241,7 @@
       <c r="Q40" s="11" t="n"/>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。 【追加調査 2026-10】環境：環境基本計画は町名検索・町サイト限定検索ともヒットせず。町サイト計画ページには田子町総合計画、地球温暖化対策実行計画（事務事業編、H24〜H28と古い）https://www.town.takko.lg.jp/index.cfm/13,234,50,202,html 、森林整備計画等。計画一覧 http://www.town.takko.lg.jp/index.cfm/13,0,50,202,html の全体は未確認のため未確認のまま。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S40" s="18" t="inlineStr">
@@ -4324,7 +4324,7 @@
       <c r="Q41" s="11" t="n"/>
       <c r="R41" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。青森県三戸郡南部町。環境基本計画・温暖化対策実行計画とも検索でヒットせず（地域再生計画のみ）。</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。青森県三戸郡南部町。環境基本計画・温暖化対策実行計画とも検索でヒットせず（地域再生計画のみ）。 【追加調査 2026-10】環境：青森県三戸郡南部町（山梨・鳥取の南部町と別）。町サイト(town.aomori-nanbu.lg.jp)限定検索で環境基本計画・区域施策編はヒットせず（議会会議録、公共施設等総合管理計画の脱炭素記載、第2次総合振興計画進捗報告のみ）。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S41" s="18" t="inlineStr">
@@ -4407,7 +4407,7 @@
       <c r="Q42" s="11" t="n"/>
       <c r="R42" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画・ゼロカーボン関連とも検索でヒットせず。</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画・ゼロカーボン関連とも検索でヒットせず。 【追加調査 2026-10】環境：環境基本計画は町名検索・町サイト限定検索ともヒットせず。町サイトでは第2次階上町環境保全率先行動計画（階上町地球温暖化対策推進実行計画、H26.12）https://www.town.hashikami.lg.jp/index.cfm/9,2212,c,html/2212/20200316-154455.pdf と自家消費型太陽光補助のみ。（確認日2026-10-02）</t>
         </is>
       </c>
       <c r="S42" s="18" t="inlineStr">
@@ -4484,18 +4484,18 @@
       </c>
       <c r="P43" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q43" s="11" t="n"/>
       <c r="R43" s="11" t="inlineStr">
         <is>
-          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。</t>
-        </is>
-      </c>
-      <c r="S43" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通計画は八戸圏域8市町村の圏域共同計画（R5〜R10）。環境基本計画・温暖化対策実行計画とも検索でヒットせず。 【追加調査 2026-10】環境：村サイトの「ゴミ・リサイクル・環境」ページ https://www.vill.shingo.aomori.jp/public/anzeneisei/ に掲載の計画はごみ減量・分別収集・一般廃棄物処理基本計画・地球温暖化対策実行計画（事務事業編）・災害廃棄物処理計画で、環境基本計画は無し（検索要約ベース）。村名検索でもヒットせず。（確認日2026-10-02）</t>
+        </is>
+      </c>
+      <c r="S43" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T43" s="11" t="inlineStr">
@@ -5250,13 +5250,15 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>10年計画（R3頃〜、終期未確認）</t>
-        </is>
-      </c>
-      <c r="N9" s="13" t="n"/>
+          <t>H30〜R9</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -5271,7 +5273,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：網形成計画（H30〜）をR6.3に地域公共交通計画として策定、計画期間は2018〜2027年度（R9終期）、2028年度以降に見直し予定。計画ページ https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html 。次期計画の委託等は未確認。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：10年計画（R10以降に見直しとの記載あり）、正確な期間未確認。区域施策編改訂支援業務プロポーザルあり https://www.city.kuji.iwate.jp/assets/fukushi/siyousyo_ondankapropo.pdf 。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず／根拠: https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html</t>
+          <t>交通：網形成計画（H30〜）をR6.3に地域公共交通計画として策定、計画期間は2018〜2027年度（R9終期）、2028年度以降に見直し予定。計画ページ https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html 。次期計画の委託等は未確認。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：10年計画（R10以降に見直しとの記載あり）、正確な期間未確認。区域施策編改訂支援業務プロポーザルあり https://www.city.kuji.iwate.jp/assets/fukushi/siyousyo_ondankapropo.pdf 。 【ファクトチェック 2026-10-01: 確認できず】確認期間: None／次期: 確認できず／根拠: https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html 【追加調査 2026-10】【2026-10-02調査】検索3回で計画ページ https://www.city.kuji.lg.jp/soshiki/chiikizukurishinko/1/6/1/1835.html は確認できたが、計画期間（H30〜R9=2018〜2027年度）を示す本文抜粋は得られず推定のまま。市サイトはWebFetch不可（egress blocked）。次期計画の委託等も検索で見当たらず。 【追加調査 2026-10】環境：市サイト限定検索2回で『第1章 計画の基本的事項』(2021_kuji_kankyou_1.pdf)の本文として「2018年度から2027年度までの10年間」を確認（PDF直接取得は不可）。前回メモの『R10以降に見直し』と整合。R9終期のため次期（第3次）計画の策定委託・審議会・パブコメを検索したが見当たらず（着手未確認）。確認日2026-10-02。 根拠: 計画の期間は…2018年度から2027年度までの10年間とします</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -5341,18 +5343,20 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>R8〜R12</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P10" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>策定済</t>
         </is>
       </c>
       <c r="Q10" s="14" t="inlineStr">
@@ -5362,7 +5366,7 @@
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>交通：R7〜R12（R7年度開始の新計画）。環境：第5次計画を公開、期間は検索結果で未確認。</t>
+          <t>交通：R7〜R12（R7年度開始の新計画）。環境：第5次計画を公開、期間は検索結果で未確認。 【追加調査 2026-10】環境：市サイト限定検索2回（別クエリ）で環境基本計画ページの本文として「第５次遠野市環境基本計画の期間は令和8年から令和12年度まで」を確認。R8開始の新計画（第3次遠野市総合計画R8〜R17と同時期）のため策定済と判断（策定月・パブコメは未確認）。市サイトはWebFetchブロック。確認日2026-10-02。URL https://www.city.tono.iwate.jp/index.cfm/45,34797,247,html 根拠: 第５次遠野市環境基本計画…令和8年から令和12年度まで</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -6061,13 +6065,15 @@
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>R3〜（終期不明）</t>
-        </is>
-      </c>
-      <c r="N18" s="13" t="n"/>
+          <t>R3〜R10</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P18" s="13" t="inlineStr">
@@ -6082,7 +6088,7 @@
       </c>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>交通：第1次R3.5〜R6.3、第2次（R7〜R11）はパブコメR7.3.17締切で策定 https://www.town.shizukuishi.iwate.jp/docs/2025021300036/ 。環境：R3.5策定、終期は検索で未確認（10年ならR12）。</t>
+          <t>交通：第1次R3.5〜R6.3、第2次（R7〜R11）はパブコメR7.3.17締切で策定 https://www.town.shizukuishi.iwate.jp/docs/2025021300036/ 。環境：R3.5策定、終期は検索で未確認（10年ならR12）。 【追加調査 2026-10】環境：第二期雫石町環境基本計画（R3.5策定）、計画期間R3〜R10（2021〜2028年度、8年間）。町サイト限定検索2回の取得本文で一致して確認。中間見直し規定あり。終期R10のため次期計画の着手状況は未調査。確認日2026-10-02。URL: https://www.town.shizukuishi.iwate.jp/docs/2016050600013/file_contents/kankyoukihonkeikaku.pdf 根拠: 計画期間は2021年度（令和3年度）から2028年度（令和10年度）までの8年間（検索取得本文の要約）</t>
         </is>
       </c>
       <c r="S18" s="15" t="inlineStr">
@@ -6303,29 +6309,35 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>紫波町環境・循環基本計画</t>
+          <t>紫波2100 2026環境・循環基本計画（2021環境・循環基本計画の中間見直し版）</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N21" s="13" t="n"/>
+          <t>R8〜R12</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="Q21" s="11" t="n"/>
+          <t>策定済</t>
+        </is>
+      </c>
+      <c r="Q21" s="14" t="inlineStr">
+        <is>
+          <t>https://www.town.shiwa.iwate.jp/shiwatown/cms/soshiki/2_1/2_3/2026%E7%92%B0%E5%A2%83%E3%83%BB%E5%BE%AA%E7%92%B0%E5%9F%BA%E6%9C%AC%E8%A8%88%E7%94%BB%EF%BC%88%E6%9C%80%E7%B5%82%E8%AA%BF%E6%95%B4%EF%BC%89_20260316_%E7%A2%BA%E5%AE%9A.pdf</t>
+        </is>
+      </c>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>交通：R6.3策定、R6〜R10。環境：環境・循環基本計画（2021年関連）の存在は示唆されるが期間・URLは確認できず。</t>
+          <t>交通：R6.3策定、R6〜R10。環境：環境・循環基本計画（2021年関連）の存在は示唆されるが期間・URLは確認できず。 【追加調査 2026-10】環境：2021環境・循環基本計画（R3.3策定、R3〜R12）の中間見直しとして2026版を策定。意見公募R7.11.14〜R7.12.3（https://www.town.shiwa.iwate.jp/soshiki/2_1/2_3/173492829222563-2/ ）、確定版PDF（20260316確定）。計画期間R8〜R12（5年間）。計画一覧 https://www.town.shiwa.iwate.jp/soshiki/2_1/2_3/452.html/ に2011版(H23〜R2)・2016版・2021版(R3〜R12)・2026版(R8〜R12)。確認日2026-10-02。 根拠: 計画期間は5年間とし、令和8（2026）年度を初年度、令和12（2030）年度を目標年度とします（意見公募ページ取得本文の要約）</t>
         </is>
       </c>
       <c r="S21" s="15" t="inlineStr">
@@ -6725,13 +6737,15 @@
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>R5〜（終期不明）</t>
-        </is>
-      </c>
-      <c r="N26" s="13" t="n"/>
+          <t>R4〜R8</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="n">
+        <v>8</v>
+      </c>
       <c r="O26" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P26" s="13" t="inlineStr">
@@ -6746,7 +6760,7 @@
       </c>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>交通：2025〜2029年度。環境：R5.6策定、期間は未確認。区域施策編策定支援業務（R7.5）あり https://www.town.sumita.iwate.jp/docs/2025052000011/files/shinsakijun.pdf 。</t>
+          <t>交通：2025〜2029年度。環境：R5.6策定、期間は未確認。区域施策編策定支援業務（R7.5）あり https://www.town.sumita.iwate.jp/docs/2025052000011/files/shinsakijun.pdf 。 【追加調査 2026-10】環境：第5次住田町環境基本計画、町の計画・方針一覧（https://www.town.sumita.iwate.jp/docs/2016050600013/ ）の検索要約で『R5.3策定、計画期間R4〜R8』と3回一致して出たが原文スニペットは未取得。計画書公開はR5.6（docs/2023061500010）で、策定時期と始期の整合に疑問が残るため推定（R5〜R9の可能性も残る）。5年計画。次期（第6次）計画の策定業務委託・審議会・パブコメは町サイト検索で見当たらず（未着手か未公表）。関連：地球温暖化対策実行計画（区域施策編）作成支援業務プロポーザルR7.5 https://www.town.sumita.iwate.jp/docs/2025052000011/ 。町HPへの直接取得はプロキシでブロック。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S26" s="15" t="inlineStr">
@@ -7056,7 +7070,7 @@
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>田野畑村環境基本計画（H16.11策定）</t>
+          <t>田野畑村環境基本計画</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -7082,7 +7096,7 @@
       </c>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.9.15公開、期間は検索で確認できず（5年ならR5〜R9の可能性）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：H16策定の計画ページあり、期間・改定状況不明。</t>
+          <t>交通：R5.9.15公開、期間は検索で確認できず（5年ならR5〜R9の可能性）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：H16策定の計画ページあり、期間・改定状況不明。 【追加調査 2026-10】環境：村サイト限定検索で『田野畑村環境基本計画』ページ（https://www.vill.tanohata.iwate.jp/docs/2015081800027/ 、ページ更新2017-02-08）を確認。『環境の保全と創造に関する基本条例』に基づきH16.11策定と記載。計画期間・改定（第2次等）の記載は検索結果で確認できず、改定・次期策定の動きも見当たらない（H16策定のまま期間不明）。各種計画一覧 https://www.vill.tanohata.iwate.jp/bunya/keikaku/tanohata/ 。村HP直接取得はブロック。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S30" s="15" t="inlineStr">
@@ -7117,24 +7131,34 @@
         <f>IF(P31="計画なし","－",IF(P31="策定済","✕",IF(N31="","？",IF(AND(N31&gt;=TGT_MIN,N31&lt;=TGT_MAX),IF(P31="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
-      <c r="F31" s="11" t="n"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>三陸鉄道沿線地域等公共交通計画（岩手県・沿線市町村の広域計画）</t>
+        </is>
+      </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="n"/>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>計画なし</t>
-        </is>
-      </c>
-      <c r="K31" s="11" t="n"/>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>https://www.city.miyako.iwate.jp/material/files/group/8/sanntetsukoutuukeikaku2024.pdf</t>
+        </is>
+      </c>
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="11" t="inlineStr">
         <is>
@@ -7155,17 +7179,17 @@
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>交通：村独自の地域公共交通計画は確認できず（村営バス無料運行 https://www.vill.fudai.iwate.jp/lifescene/koutsu.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。</t>
-        </is>
-      </c>
-      <c r="S31" s="18" t="inlineStr">
-        <is>
-          <t>環境のみ調査</t>
-        </is>
-      </c>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>掲載（広域：三陸鉄道沿線地域等）【当方未把握】</t>
+          <t>交通：村独自の地域公共交通計画は確認できず（村営バス無料運行 https://www.vill.fudai.iwate.jp/lifescene/koutsu.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。 【追加調査 2026-10】交通(2026-10調査)：国交省一覧(R8.5末)の広域計画「三陸鉄道沿線地域等」＝三陸鉄道沿線地域等公共交通計画。検索結果本文で計画期間「令和６年度（2024年度）から令和10年度（2028年度）」を確認（前身の三陸鉄道沿線地域等公共交通網形成計画をR6.3中間評価を踏まえ改定、岩手県地域公共交通計画R6〜R10と整合）。PDF https://www.city.miyako.iwate.jp/material/files/group/8/sanntetsukoutuukeikaku2024.pdf 。終期R10のため次期計画の着手情報なし。普代村独自の地域公共交通計画は引き続き見当たらず。 根拠: 三陸鉄道沿線地域等公共交通計画の計画期間は令和６年度（2024年度）から令和10年度（2028年度）</t>
+        </is>
+      </c>
+      <c r="S31" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
         </is>
       </c>
     </row>
@@ -7263,24 +7287,34 @@
         <f>IF(P33="計画なし","－",IF(P33="策定済","✕",IF(N33="","？",IF(AND(N33&gt;=TGT_MIN,N33&lt;=TGT_MAX),IF(P33="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
-      <c r="F33" s="11" t="n"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>三陸鉄道沿線地域等公共交通計画（岩手県・沿線市町村の広域計画）</t>
+        </is>
+      </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="n"/>
+          <t>R6〜R10</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>計画なし</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="n"/>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr">
+        <is>
+          <t>https://www.city.miyako.iwate.jp/material/files/group/8/sanntetsukoutuukeikaku2024.pdf</t>
+        </is>
+      </c>
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="11" t="inlineStr">
         <is>
@@ -7301,17 +7335,17 @@
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>交通：村独自の計画は確認できず（村営バス https://www.vill.noda.iwate.jp/soshiki/miraizukurisuishinka/miraizukurisuishinhan/doro_kotsu/642.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。</t>
-        </is>
-      </c>
-      <c r="S33" s="18" t="inlineStr">
-        <is>
-          <t>環境のみ調査</t>
-        </is>
-      </c>
-      <c r="T33" s="17" t="inlineStr">
-        <is>
-          <t>掲載（広域：三陸鉄道沿線地域等）【当方未把握】</t>
+          <t>交通：村独自の計画は確認できず（村営バス https://www.vill.noda.iwate.jp/soshiki/miraizukurisuishinka/miraizukurisuishinhan/doro_kotsu/642.html ）。三陸鉄道沿線地域等公共交通計画（岩手県・沿線12市町村の広域計画、2024策定） https://www.city.miyako.iwate.jp/gyosei/soshiki/kokyokotsuusuishin/2/1/605.html もカバー。環境：確認できず。 【追加調査 2026-10】交通(2026-10調査)：国交省一覧(R8.5末)の広域計画「三陸鉄道沿線地域等」＝三陸鉄道沿線地域等公共交通計画。検索結果本文で計画期間「令和６年度（2024年度）から令和10年度（2028年度）」を確認（前身の三陸鉄道沿線地域等公共交通網形成計画をR6.3中間評価を踏まえ改定、岩手県地域公共交通計画R6〜R10と整合）。PDF https://www.city.miyako.iwate.jp/material/files/group/8/sanntetsukoutuukeikaku2024.pdf 。終期R10のため次期計画の着手情報なし。野田村独自の地域公共交通計画は引き続き見当たらず。 根拠: 三陸鉄道沿線地域等公共交通計画の計画期間は令和６年度（2024年度）から令和10年度（2028年度）</t>
+        </is>
+      </c>
+      <c r="S33" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：三陸鉄道沿線地域等）</t>
         </is>
       </c>
     </row>
@@ -7620,19 +7654,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8122,7 +8159,7 @@
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>交通：第2次はH30.2策定・R3.6.28二次改定、目標年次R8（県の市町村計画一覧 https://www.pref.miyagi.jp/documents/7752/02_r8_sityousonkeikaku.pdf の検索要約より）。同資料で第3次気仙沼市総合交通計画を策定中と記載あり→着手済と判断（要確認）。法定地域公共交通計画としての位置付けは未確認。R8.7にAIデマンド交通導入業務プロポーザル https://www.kesennuma.miyagi.jp/sec/s023/020/010/010/20260706170359.html 。環境：市公式サイト内検索で環境基本計画ヒットせず（計画なしの可能性、要確認）。WebFetchは市サイトblocked。 地球温暖化対策実行計画（区域施策編）のパブコメ実績・気仙沼市持続可能なまち推進計画（R7.7）あり https://www.kesennuma.miyagi.jp/li/life/020/080/070/index.html 。</t>
+          <t>交通：第2次はH30.2策定・R3.6.28二次改定、目標年次R8（県の市町村計画一覧 https://www.pref.miyagi.jp/documents/7752/02_r8_sityousonkeikaku.pdf の検索要約より）。同資料で第3次気仙沼市総合交通計画を策定中と記載あり→着手済と判断（要確認）。法定地域公共交通計画としての位置付けは未確認。R8.7にAIデマンド交通導入業務プロポーザル https://www.kesennuma.miyagi.jp/sec/s023/020/010/010/20260706170359.html 。環境：市公式サイト内検索で環境基本計画ヒットせず（計画なしの可能性、要確認）。WebFetchは市サイトblocked。 地球温暖化対策実行計画（区域施策編）のパブコメ実績・気仙沼市持続可能なまち推進計画（R7.7）あり https://www.kesennuma.miyagi.jp/li/life/020/080/070/index.html 。 【追加調査 2026-10】環境：『気仙沼市環境基本計画』の名称での計画ページ・PDFは検索（一般・市ドメイン限定・完全一致、計5回）でヒットせず。一方、市ドメイン検索の要約で、気仙沼市地球温暖化対策実行計画（区域施策編、2025〜2030年度）は『市環境基本計画における地球温暖化対策を推進するための個別計画』と記載との情報あり（要約のみ・URL特定できず、一般論の混入の可能性）。存在有無は判断保留（計画なしとは断定できず）。計画・施策一覧 https://www.kesennuma.miyagi.jp/li/shisei/060/index.html の確認を推奨。</t>
         </is>
       </c>
       <c r="S7" s="18" t="inlineStr">
@@ -8192,13 +8229,15 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>不明（H31.4公表）</t>
-        </is>
-      </c>
-      <c r="N8" s="13" t="n"/>
+          <t>H31(R1)〜R10（10年間）</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P8" s="13" t="inlineStr">
@@ -8213,7 +8252,7 @@
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3策定（前身の網形成計画はH29.6）、計画ページ https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html 。期間は検索で確認できず5年と仮定しR9終期を推定→R9終期なら次期策定はR8〜R9着手見込み（有望・要確認）。環境：第3次計画と第3次温暖化対策実行計画をH31.4.23掲載、期間不明（10年ならR10頃終期）。広域：宮城県地域公共交通計画R8〜R14あり（県計画、検索要約より）。佐賀県白石町・千葉県白井市とは別。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度〜令和9年度の5年間、R5.3策定）／次期: 着手済の可能性高：「白石市地域公共交通計画策定調査に係る公募型プロポーザル」（2026-07-14更新、募集終了）が市サイト まちづくり推進課/入札・契約情報に掲載（https://www.city.shiroishi.miyagi.jp/／根拠: https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html</t>
+          <t>交通：R5.3策定（前身の網形成計画はH29.6）、計画ページ https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html 。期間は検索で確認できず5年と仮定しR9終期を推定→R9終期なら次期策定はR8〜R9着手見込み（有望・要確認）。環境：第3次計画と第3次温暖化対策実行計画をH31.4.23掲載、期間不明（10年ならR10頃終期）。広域：宮城県地域公共交通計画R8〜R14あり（県計画、検索要約より）。佐賀県白石町・千葉県白井市とは別。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度〜令和9年度の5年間、R5.3策定）／次期: 着手済の可能性高：「白石市地域公共交通計画策定調査に係る公募型プロポーザル」（2026-07-14更新、募集終了）が市サイト まちづくり推進課/入札・契約情報に掲載（https://www.city.shiroishi.miyagi.jp/／根拠: https://www.city.shiroishi.miyagi.jp/soshiki/17/27078.html 【追加調査 2026-10】環境：第3次白石市環境基本計画は平成31年度（令和元年度）から10年間＝R10終期。市サイト内検索（環境課ページ https://www.city.shiroishi.miyagi.jp/soshiki/18/ 、令和2年度施政方針 https://www.city.shiroishi.miyagi.jp/site/mayor/16031.html ）の結果本文で2回一致。次期はR9〜R10着手見込み（現時点未確認）。 根拠: 第３次白石市環境基本計画は令和元年度から10年間を計画期間</t>
         </is>
       </c>
       <c r="S8" s="15" t="inlineStr">
@@ -8283,13 +8322,15 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>不明（H30〜R1の2か年で策定）</t>
-        </is>
-      </c>
-      <c r="N9" s="13" t="n"/>
+          <t>R2〜R12（11年間）</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -8299,12 +8340,12 @@
       </c>
       <c r="Q9" s="14" t="inlineStr">
         <is>
-          <t>https://www.city.natori.miyagi.jp/uploaded/attachment/10172.pdf</t>
+          <t>https://www.city.natori.miyagi.jp/page/4721.html</t>
         </is>
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：R5.3.28策定、R9終期。次期計画の策定業務・プロポーザルは検索で未確認。R8.8.25にR8年度名取市地域公共交通活性化推進協議会開催 https://www.city.natori.miyagi.jp/page/45227.html （次期計画の議題か要確認・有望）。計画ページ https://www.city.natori.miyagi.jp/page/4327.html 。環境：第二次計画の期間は検索で確認できず（R2開始10年ならR11終期と推定）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度の5ヶ年、R5.3.28策定）／次期: 確認できず（令和8年度協議会 R8.8.25開催の議題は『計画の取組状況について』のみ／https://www.city.natori.miyagi.jp/page/45227.html）／根拠: https://www.city.natori.miyagi.jp/page/4327.html</t>
+          <t>交通：R5.3.28策定、R9終期。次期計画の策定業務・プロポーザルは検索で未確認。R8.8.25にR8年度名取市地域公共交通活性化推進協議会開催 https://www.city.natori.miyagi.jp/page/45227.html （次期計画の議題か要確認・有望）。計画ページ https://www.city.natori.miyagi.jp/page/4327.html 。環境：第二次計画の期間は検索で確認できず（R2開始10年ならR11終期と推定）。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（令和5年度～令和9年度の5ヶ年、R5.3.28策定）／次期: 確認できず（令和8年度協議会 R8.8.25開催の議題は『計画の取組状況について』のみ／https://www.city.natori.miyagi.jp/page/45227.html）／根拠: https://www.city.natori.miyagi.jp/page/4327.html 【追加調査 2026-10】環境：第二次名取市環境基本計画の計画期間は令和2（2020）年度〜令和12（2030）年度の11年間。計画ページ https://www.city.natori.miyagi.jp/page/4721.html 、本編PDF https://www.city.natori.miyagi.jp/uploaded/attachment/10172.pdf 。R7.?に環境に関する市民・事業者意識調査実施 https://www.city.natori.miyagi.jp/page/39371.html （中間見直し等の可能性）。 根拠: 計画期間は令和2（2020）年度から令和12（2030）年度までの11年間</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -8372,13 +8413,15 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>不明（R5策定）</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>R5〜R14（10年間）</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="n">
+        <v>14</v>
+      </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P10" s="13" t="inlineStr">
@@ -8389,7 +8432,7 @@
       <c r="Q10" s="11" t="n"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>交通：市単独の地域公共交通計画（初策定）を策定中、案のパブコメ実施 https://www.city.kakuda.lg.jp/soshiki/4/25038.html 、R8.1.23に第3回活性化協議会 https://www.city.kakuda.lg.jp/uploaded/life/24126_87553_misc.pdf 。R8.3頃策定の可能性（策定完了・期間は未確認）。広域：阿武隈急行線地域公共交通計画（案）パブコメ https://www.city.kakuda.lg.jp/soshiki/4/24148.html 。環境：第3次環境基本計画R5策定（期間不明）、角田市地球温暖化対策総合計画 R6.3策定・R8.3修正 https://www.city.kakuda.lg.jp/uploaded/life/17642_48417_misc.pdf 。</t>
+          <t>交通：市単独の地域公共交通計画（初策定）を策定中、案のパブコメ実施 https://www.city.kakuda.lg.jp/soshiki/4/25038.html 、R8.1.23に第3回活性化協議会 https://www.city.kakuda.lg.jp/uploaded/life/24126_87553_misc.pdf 。R8.3頃策定の可能性（策定完了・期間は未確認）。広域：阿武隈急行線地域公共交通計画（案）パブコメ https://www.city.kakuda.lg.jp/soshiki/4/24148.html 。環境：第3次環境基本計画R5策定（期間不明）、角田市地球温暖化対策総合計画 R6.3策定・R8.3修正 https://www.city.kakuda.lg.jp/uploaded/life/17642_48417_misc.pdf 。 【追加調査 2026-10】環境：角田市第3次環境基本計画（2023年策定、環境像『「緑・水・人」調和のとれた環境都市』）。市サイト内検索の要約で『計画期間は2023年度から2032年度までの10年間』（出典は角田市地球温暖化対策総合計画 https://www.city.kakuda.lg.jp/uploaded/life/17642_48417_misc.pdf と思われる）。別検索では同PDF中の表から2020〜2030年度との要約もあり不一致のため推定扱い。計画単独ページURLは未発見。 根拠: 計画期間は2023年度から2032年度までの10年間</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -8730,28 +8773,30 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N14" s="13" t="n"/>
+          <t>H30〜R9（10年間）</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>着手済</t>
         </is>
       </c>
       <c r="Q14" s="14" t="inlineStr">
         <is>
-          <t>https://www.kuriharacity.jp/li/010/020/080/index.html</t>
+          <t>https://www.kuriharacity.jp/w012/010/010/020/120/51193.html</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>交通：市企画部所管の地域公共交通計画の存在は市サイトで確認、期間は検索で確認できず。広報くりはら2024『特集 生まれ変わる地域公共交通』 https://www.kuriharacity.jp/w009/030/010/2024/379/kurihara379_02.pdf 。環境：第2次計画の存在のみ確認、期間不明（第2次総合計画がH29〜R8のため連動していればR8終期の可能性、要確認）。</t>
+          <t>交通：市企画部所管の地域公共交通計画の存在は市サイトで確認、期間は検索で確認できず。広報くりはら2024『特集 生まれ変わる地域公共交通』 https://www.kuriharacity.jp/w009/030/010/2024/379/kurihara379_02.pdf 。環境：第2次計画の存在のみ確認、期間不明（第2次総合計画がH29〜R8のため連動していればR8終期の可能性、要確認）。 【追加調査 2026-10】環境：第2次栗原市環境基本計画はH30（2018）〜R9（2027）年度の10年間（計画ページ https://www.kuriharacity.jp/w012/010/010/020/120/51193.html の検索結果）。次期：『第3次栗原市環境基本計画策定支援業務』が市の2026年6月入札結果に掲載（R8.6.3執行）https://www.kuriharacity.jp/w004/030/010/030/20260114/202606/PAGE000000000000015506.html →着手済。第3次総合計画（R9〜）も並行策定中。 根拠: 第2次栗原市環境基本計画…2018年度から2027年度までの10年間</t>
         </is>
       </c>
       <c r="S14" s="15" t="inlineStr">
@@ -9020,7 +9065,7 @@
       <c r="Q17" s="11" t="n"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>交通：R7.3策定（R6年度）、t_urlはR7.3協議会資料の計画（案）。都市・地域総合交通戦略 https://www.tomiya-city.miyagi.jp/shisei/keikaku/keikaku/nek5ga2.html 。環境：単独の環境基本計画は検索で確認できず（計画なしの可能性、市HP計画一覧 https://www.tomiya-city.miyagi.jp/shisei/keikaku/ 要確認）。温暖化対策実行計画は存在。第2次富谷市総合計画をR8年度開始で策定。</t>
+          <t>交通：R7.3策定（R6年度）、t_urlはR7.3協議会資料の計画（案）。都市・地域総合交通戦略 https://www.tomiya-city.miyagi.jp/shisei/keikaku/keikaku/nek5ga2.html 。環境：単独の環境基本計画は検索で確認できず（計画なしの可能性、市HP計画一覧 https://www.tomiya-city.miyagi.jp/shisei/keikaku/ 要確認）。温暖化対策実行計画は存在。第2次富谷市総合計画をR8年度開始で策定。 【追加調査 2026-10】環境：市ドメイン検索・計画一覧系検索（計2回）で環境基本計画はヒットせず。総合計画の関連計画として地球温暖化対策実行計画・2050年ゼロカーボン戦略 https://www.tomiya-city.miyagi.jp/kurashi/kankyou/zerocarbon/zero2050.html は挙がるが環境基本計画の記載は見当たらない（要約ベース）。計画なしの可能性が高いが公式一覧での確認ができず未断定。</t>
         </is>
       </c>
       <c r="S17" s="18" t="inlineStr">
@@ -9690,7 +9735,7 @@
       </c>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>交通：パブコメR6.2.2〜2.16（https://www.town.watari.miyagi.jp/town/detail.php?content=1686 ）、R6.3策定、R6〜R10（5年）。本編PDF https://www.town.watari.miyagi.jp/common/img/content/content_20240405_084913.pdf 。環境：第2次計画の存在は検索で確認、期間は未確認（e_urlは環境基本計画関連と思われるPDF、町サイトはWebFetch遮断で未検証）。地球温暖化対策実行計画（区域施策編）も策定済 https://www.town.watari.miyagi.jp/town/detail.php?content=1811 。亘理・山元の共同交通計画は見当たらず（各町単独）。</t>
+          <t>交通：パブコメR6.2.2〜2.16（https://www.town.watari.miyagi.jp/town/detail.php?content=1686 ）、R6.3策定、R6〜R10（5年）。本編PDF https://www.town.watari.miyagi.jp/common/img/content/content_20240405_084913.pdf 。環境：第2次計画の存在は検索で確認、期間は未確認（e_urlは環境基本計画関連と思われるPDF、町サイトはWebFetch遮断で未検証）。地球温暖化対策実行計画（区域施策編）も策定済 https://www.town.watari.miyagi.jp/town/detail.php?content=1811 。亘理・山元の共同交通計画は見当たらず（各町単独）。 【追加調査 2026-10】環境：第2次亘理町環境基本計画の存在は再確認（e_urlのPDF content_20220126_163920 が上位ヒット、R4.1頃公表）が、期間は検索3回とも本文に出ず不明のまま（R4開始10年ならR13終期の可能性）。町の環境・ごみカテゴリ https://www.town.watari.miyagi.jp/life/category/?category=124 。</t>
         </is>
       </c>
       <c r="S25" s="15" t="inlineStr">
@@ -9808,7 +9853,11 @@
         <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
-      <c r="F27" s="11" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>松島町の交通関係計画（H29年度策定、正式名称未確認・期間満了）</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
           <t>不明</t>
@@ -9822,7 +9871,7 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>計画なし</t>
+          <t>未確認</t>
         </is>
       </c>
       <c r="K27" s="11" t="n"/>
@@ -9846,17 +9895,17 @@
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>交通・環境とも町独自計画は検索で確認できず（町サイトの検索インデックスが薄く、存在しない確証はない＝要確認）。宮城県地域公共交通計画（R8〜R14）が町域を含む https://www.pref.miyagi.jp/soshiki/soukou/20240520.html 。</t>
-        </is>
-      </c>
-      <c r="S27" s="18" t="inlineStr">
-        <is>
-          <t>環境のみ調査</t>
+          <t>交通・環境とも町独自計画は検索で確認できず（町サイトの検索インデックスが薄く、存在しない確証はない＝要確認）。宮城県地域公共交通計画（R8〜R14）が町域を含む https://www.pref.miyagi.jp/soshiki/soukou/20240520.html 。 【追加調査 2026-10】交通(2026-10調査)：国交省一覧(R8.5末)では町単独計画あり・期間満了（灰色）。R7.3.4第1回定例会会議録（https://www.town.miyagi-matsushima.lg.jp/uploaded/attachment/2895.pdf ）の検索要約で、町当局が「交通関係の計画はH29年度に策定、現時点で見直しの具体的予定なし」と答弁（北部地区デマンド交通実証H30〜R1は利用低迷で導入見送り）。計画名・期間は検索で特定できず（町サイトに計画書の掲載見当たらず）。次期計画の着手（委託・パブコメ等）も確認できず。宮城県地域公共交通計画（R8〜R14）が町域をカバー。 根拠: （検索要約）a transportation-related plan was formulated in fiscal year 2017 ... no specific plans for revision</t>
+        </is>
+      </c>
+      <c r="S27" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t>掲載／期間満了【当方未把握】</t>
+          <t>掲載／期間満了</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10215,7 @@
       <c r="Q31" s="11" t="n"/>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独・黒川地域共同の地域公共交通計画は検索で確認できず（町民バス運行のみの可能性）。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：町独自の環境基本計画は検索で確認できず。</t>
+          <t>交通：町単独・黒川地域共同の地域公共交通計画は検索で確認できず（町民バス運行のみの可能性）。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：町独自の環境基本計画は検索で確認できず。 【追加調査 2026-10】環境：一般検索・町ドメイン限定検索（town.miyagi-osato.lg.jp）とも環境基本計画はヒットせず。総合計画 https://www.town.miyagi-osato.lg.jp/soshiki/machidukuri/sougoukeikaku2025.html の環境分野で対応している模様。計画なしの可能性が高いが、計画一覧での明確な根拠はなく未断定。</t>
         </is>
       </c>
       <c r="S31" s="18" t="inlineStr">
@@ -10312,7 +10361,7 @@
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は確認できず。大崎定住自立圏（大崎市・色麻・加美・涌谷・美里）で大崎圏域公共交通検討研究会を開催し圏域交通を検討 https://www.pref.miyagi.jp/site/tiikisinnkou/teizyu.html 。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：環境基本計画は検索で確認できず。</t>
+          <t>交通：町単独計画は確認できず。大崎定住自立圏（大崎市・色麻・加美・涌谷・美里）で大崎圏域公共交通検討研究会を開催し圏域交通を検討 https://www.pref.miyagi.jp/site/tiikisinnkou/teizyu.html 。宮城県地域公共交通計画（次期R8〜R14、7年間）が県全域を対象 https://www.pref.miyagi.jp/documents/59495/07thedraftplanoflptp.pdf。環境：環境基本計画は検索で確認できず。 【追加調査 2026-10】環境：一般検索・町ドメイン限定検索とも環境基本計画はヒットせず。町議会会議録で地球温暖化対策実行計画・ゼロカーボン関連の言及のみ。町の政策・施策一覧 https://www.town.shikama.miyagi.jp/chosei/seisaku_shisaku/index.html で要確認。計画なしの可能性が高いが未断定。</t>
         </is>
       </c>
       <c r="S33" s="18" t="inlineStr">
@@ -11585,7 +11634,7 @@
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>交通：R7.6改訂版（秋北バス一部路線廃止・八幡平地区再編 R7.10.1対応）。計画期間は検索結果で未確認だが、R4年度協議会で策定審議（資料 https://www.city.kazuno.lg.jp/material/files/group/8/shiryou3_R4_3.pdf ）→R5年度始期の5年計画（R5〜R9）と推定、要確認。協議会 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html 。環境：エネルギービジョン（R4.2）が第3次環境基本計画と終期を整合、R13年3月まで（=R12年度末）https://www.city.kazuno.lg.jp/material/files/group/14/energyvision.pdf 。e_urlは市の環境ページ（計画直リンク未取得）。 【ファクトチェック 2026-10-01: 確認できず】確認期間: R5〜R9（要約のみ）／次期: 確認できず／根拠: https://realtime-nippon.com/archives/052094230123001/</t>
+          <t>交通：R7.6改訂版（秋北バス一部路線廃止・八幡平地区再編 R7.10.1対応）。計画期間は検索結果で未確認だが、R4年度協議会で策定審議（資料 https://www.city.kazuno.lg.jp/material/files/group/8/shiryou3_R4_3.pdf ）→R5年度始期の5年計画（R5〜R9）と推定、要確認。協議会 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html 。環境：エネルギービジョン（R4.2）が第3次環境基本計画と終期を整合、R13年3月まで（=R12年度末）https://www.city.kazuno.lg.jp/material/files/group/14/energyvision.pdf 。e_urlは市の環境ページ（計画直リンク未取得）。 【ファクトチェック 2026-10-01: 確認できず】確認期間: R5〜R9（要約のみ）／次期: 確認できず／根拠: https://realtime-nippon.com/archives/052094230123001/ 【追加調査 2026-10】【2026-10-02調査】検索3回の要約がいずれも「計画期間は令和5年度から令和9年度まで」と回答（出典候補: 計画ページ https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/10092.html 、協議会 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/9297.html ）が、本文抜粋は表示されず要約のみのため推定のまま（R5〜R9の確度は高い）。市サイト・realtime-nipponはWebFetch不可。関連: R7.10.1八幡平地区公共交通再編 https://www.city.kazuno.lg.jp/soshiki/shiminkyodo/kankyoseikatsu/gyomu/2/3/13627.html 。次期計画の委託・審議は検索で見当たらず。</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -12287,7 +12336,7 @@
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>交通：村単独の地域公共交通計画は確認できず。以前は北秋田市・上小阿仁村の地域公共交通網形成計画（H29〜H34）が検索要約に出たが未確証。現行の北秋田市地域公共交通計画（R5〜R9、R5.3策定 https://www.city.kitaakita.akita.jp/uploads/public/news_0000015700_00/koukyoukoutsukeikaku.pdf ）の計画区域に上小阿仁村が含まれるかは未確認（要確認、含まれればt_end=9）。環境：環境基本計画・温対計画とも村HP検索で確認できず（計画なしの可能性大）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。</t>
+          <t>交通：村単独の地域公共交通計画は確認できず。以前は北秋田市・上小阿仁村の地域公共交通網形成計画（H29〜H34）が検索要約に出たが未確証。現行の北秋田市地域公共交通計画（R5〜R9、R5.3策定 https://www.city.kitaakita.akita.jp/uploads/public/news_0000015700_00/koukyoukoutsukeikaku.pdf ）の計画区域に上小阿仁村が含まれるかは未確認（要確認、含まれればt_end=9）。環境：環境基本計画・温対計画とも村HP検索で確認できず（計画なしの可能性大）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。 【追加調査 2026-10】環境：村サイト限定検索で、村議会会議録（R6第6回12月 https://www.vill.kamikoani.akita.jp/div/gikai/pdf/R6-6-3.pdf 、R7第2回3月 https://www.vill.kamikoani.akita.jp/div/gikai/pdf/R7-2-1.pdf 等）に『上小阿仁村環境基本計画』を自然エネルギーによる脱炭素戦略の村全体の総合行動計画として策定する旨の言及が要約で出た（どの会議録かは原文未確認）。小水力発電可能性調査（2023）を踏まえ再エネ設備基本設計を進行中との記載。策定済の計画書・期間・URLは検索で見当たらず（策定中または未公表の可能性）。未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S18" s="18" t="inlineStr">
@@ -12378,7 +12427,7 @@
       </c>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>交通：R6.6.18作成、前計画は藤里町地域公共交通網形成計画（H27〜H31）。計画PDF http://www.town.fujisato.akita.jp/up/files/town/soshiki/c52/c74/%E8%97%A4%E9%87%8C%E7%94%BA%E5%9C%B0%E5%9F%9F%E5%85%AC%E5%85%B1%E4%BA%A4%E9%80%9A%E8%A8%88%E7%94%BB.pdf 。能代山本地域の広域計画は確認できず（R6.10秋北バス路線再編で町内デマンド拡充）。環境：環境省資料でH12.3策定の記載のみ、現行版・改定状況は町HPで確認できず（実質計画なしの可能性）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。</t>
+          <t>交通：R6.6.18作成、前計画は藤里町地域公共交通網形成計画（H27〜H31）。計画PDF http://www.town.fujisato.akita.jp/up/files/town/soshiki/c52/c74/%E8%97%A4%E9%87%8C%E7%94%BA%E5%9C%B0%E5%9F%9F%E5%85%AC%E5%85%B1%E4%BA%A4%E9%80%9A%E8%A8%88%E7%94%BB.pdf 。能代山本地域の広域計画は確認できず（R6.10秋北バス路線再編で町内デマンド拡充）。環境：環境省資料でH12.3策定の記載のみ、現行版・改定状況は町HPで確認できず（実質計画なしの可能性）。参考：秋田県地域公共交通計画（R4.3策定、R4〜R8）が県全域を対象、R8終期のため次期計画はR8年度に策定作業中と見込まれる（R8第1回県活性化協議会 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf ）。 【追加調査 2026-10】環境：町サイト限定（town.fujisato.akita.jp）で『環境基本計画』検索→過疎計画・国土強靱化・総合戦略・まちづくり計画（H26.3）・公共施設等総合管理計画のみヒットし、環境基本計画（H12.3策定、環境省資料 https://www.env.go.jp/press/files/jp/3487.pdf ）の現行版・改定版は町HP上に見当たらず。計画が実質失効の可能性大だが計画なしの明示根拠はないため未確認のまま。確認日2026-10-02。</t>
         </is>
       </c>
       <c r="S19" s="15" t="inlineStr">
@@ -13067,30 +13116,30 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>秋田県地域公共交通計画（県計画、村独自計画は見当たらず）</t>
+          <t>東成瀬村地域公共交通計画</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>R4〜R8</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>8</v>
+          <t>R8〜R12</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>確認済</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>策定済</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.akita.lg.jp/uploads/public/archive_0000062825_00/観スポ_所管事項関連　別冊２（秋田県地域公共交通計画（案）について）.pdf</t>
+          <t>https://vill.higashinaruse.lg.jp/villager/lifework/post-36197/</t>
         </is>
       </c>
       <c r="L28" s="11" t="n"/>
@@ -13113,7 +13162,7 @@
       <c r="Q28" s="11" t="n"/>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>交通：村独自の地域公共交通計画・湯沢雄勝広域共同計画とも検索で確認できず。環境：環境基本計画見当たらず（まち・ひと・しごと創生推進計画のみ確認）。【県計画】秋田県地域公共交通計画はR4〜R8（R4.3策定、R8＝今年度終期）。R8.6.23の令和8年度第1回秋田県地域公共交通活性化協議会で県計画の策定（次期計画）を議論 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf</t>
+          <t>交通：村独自の地域公共交通計画・湯沢雄勝広域共同計画とも検索で確認できず。環境：環境基本計画見当たらず（まち・ひと・しごと創生推進計画のみ確認）。【県計画】秋田県地域公共交通計画はR4〜R8（R4.3策定、R8＝今年度終期）。R8.6.23の令和8年度第1回秋田県地域公共交通活性化協議会で県計画の策定（次期計画）を議論 https://www.pref.akita.lg.jp/uploads/public/archive_0000098833_00/R8活性化協議会①/令和８年度第１回秋田県地域公共交通活性化協議会_会議概要.pdf 【追加調査 2026-10】交通(2026-10調査)：村単独の東成瀬村地域公共交通計画をR8.3策定（村HP「東成瀬村地域公共交通計画を策定しました」 https://vill.higashinaruse.lg.jp/villager/lifework/post-36197/ ）。計画期間 令和8年度〜令和12年度（2026〜2030年度）、検索結果本文で2回確認。東成瀬村地域公共交通活性化協議会を設置（R6年度第1回協議会R7.1.30 https://vill.higashinaruse.lg.jp/wp-content/uploads/2025/03/a47c589c-621f-42c3-b67e-b4f7bba572f4.pdf ）、「交通空白」解消に向けた調査・検討業務を公募（https://vill.higashinaruse.lg.jp/villager/news/post-33178/ ）。R8.10.1から公共ライドシェア実証開始（https://vill.higashinaruse.lg.jp/villager/post-38003/ ）。従来記載の秋田県計画は参考扱いに。 ※期間は英語の検索要約でのみ確認（本文未確認）のため推定に留める。 根拠: formulated in March 2026 (Reiwa 8). The plan covers the period from fiscal year 2026 to fiscal year 2030 (Reiwa 8 to Reiwa 12)</t>
         </is>
       </c>
       <c r="S28" s="15" t="inlineStr">
@@ -13741,18 +13790,20 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定）</t>
+          <t>山形県地域公共交通計画（県・市町村共同、R8.3.27策定）</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>R8〜不明</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="n"/>
+          <t>R8〜R12</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -13762,7 +13813,7 @@
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.yamagata.jp/020057/kurashi/kendo/kotsuseisaku/ykotsu_kasseikakyougikai.html</t>
+          <t>https://www.pref.yamagata.jp/documents/50579/keikaku_honpen.pdf</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -13795,7 +13846,7 @@
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>交通：市単独の地域公共交通計画は検索で見当たらず。県計画の最上地域部会で最上管内8市町村の公共交通再編を検討中（R7.11資料 https://www.pref.yamagata.jp/documents/47862/20251125shiryou2-2.pdf ）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。</t>
+          <t>交通：市単独の地域公共交通計画は検索で見当たらず。県計画の最上地域部会で最上管内8市町村の公共交通再編を検討中（R7.11資料 https://www.pref.yamagata.jp/documents/47862/20251125shiryou2-2.pdf ）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 【追加調査 2026-10】交通(2026-10調査)：市単独の「新庄市地域公共交通計画」は検索で見当たらず。新庄市の地域内フィーダー系統（まちなか循環線）は山形県地域公共交通計画に位置付け（https://www.pref.yamagata.jp/documents/22689/05_shinjo.pdf ）。国交省一覧の「単独・期間満了」は前県計画（R3〜R7、市町村共同作成）を指す可能性が高い。次期県計画は計画期間 令和8〜12年度（本編 https://www.pref.yamagata.jp/documents/50579/keikaku_honpen.pdf 、概要 https://www.pref.yamagata.jp/documents/50579/keikaku_gaiyou.pdf 、策定業務仕様書 https://www300.pref.yamagata.jp/documents/45835/02_shiyousyo.pdf ）。県全域＋全市町村が対象、4地域ブロック（最上ブロック）構成。 根拠: 山形県地域公共交通計画（本編）… 計画期間 令和8～12年度（検索結果本文）</t>
         </is>
       </c>
       <c r="S8" s="15" t="inlineStr">
@@ -13863,13 +13914,15 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N9" s="13" t="n"/>
+          <t>R5〜R14（10年間）</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>14</v>
+      </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -13884,7 +13937,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：法定の地域公共交通計画は見当たらず、市の生活交通ネットワーク計画と県計画（山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定））で対応。環境：R5.3改定、期間は検索で確認できず。</t>
+          <t>交通：法定の地域公共交通計画は見当たらず、市の生活交通ネットワーク計画と県計画（山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定））で対応。環境：R5.3改定、期間は検索で確認できず。 【追加調査 2026-10】環境：R5.3改定版の計画期間は2023（R5）〜2032（R14）年度の10年間。旧計画（H26〜R5）を1年前倒しで改定（R4ゼロカーボンシティ宣言を受け）。計画ページ https://www.city.sagae.yamagata.jp/shisei/keikaku/toshikankyokeikaku/kankyokeikaku.html 。 根拠: 計画期間は令和5年度から令和14年度までの10年間（前計画 平成26年度〜令和5年度を1年前倒しで改定）</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -14316,13 +14369,15 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>R5〜不明</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="n"/>
+          <t>R5〜R14（10年間）</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>14</v>
+      </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="P14" s="13" t="inlineStr">
@@ -14337,7 +14392,7 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>交通：市単独の地域公共交通計画は見当たらず（市民バス運行、県計画を踏まえる）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：前計画H25〜R4の後継としてR4年度に第3次策定（期間は未確認、R5開始と推定）。</t>
+          <t>交通：市単独の地域公共交通計画は見当たらず（市民バス運行、県計画を踏まえる）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：前計画H25〜R4の後継としてR4年度に第3次策定（期間は未確認、R5開始と推定）。 【追加調査 2026-10】環境：第3次東根市大けやき環境基本計画はR4年度策定、計画期間R5〜R14（2023〜2032年度）の10年間。前計画（改訂版）はH25〜R4。計画ページ https://www.city.higashine.yamagata.jp/section_list/section008/seikatsukankyo-keikaku/169 （本編・概要版PDF掲載）。 根拠: The third version covers the period from R5 to R14 (fiscal year 2023 to fiscal year 2032)</t>
         </is>
       </c>
       <c r="S14" s="15" t="inlineStr">
@@ -15708,7 +15763,7 @@
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定）</t>
+          <t>高畠町地域公共交通計画</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -15729,7 +15784,7 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.yamagata.jp/020057/kurashi/kendo/kotsuseisaku/ykotsu_kasseikakyougikai.html</t>
+          <t>https://www.town.takahata.yamagata.jp/soshikiichiran/kikaku/3/kokyokotsu/4511.html</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
@@ -15739,10 +15794,12 @@
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>R5〜不明</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="n"/>
+          <t>R5〜（10年ならR14）</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>14</v>
+      </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
           <t>推定</t>
@@ -15760,7 +15817,7 @@
       </c>
       <c r="R31" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独の地域公共交通計画は見当たらず（デマンド交通運行）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第2次がR4年度で終了→第3次策定（R5開始と推定、終期未確認）。</t>
+          <t>交通：町単独の地域公共交通計画は見当たらず（デマンド交通運行）。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第2次がR4年度で終了→第3次策定（R5開始と推定、終期未確認）。 【追加調査 2026-10】交通(2026-10調査)：町単独の「高畠町地域公共交通計画」を新規策定。計画案のパブリックコメントを令和7年12月17日〜令和8年1月7日に実施（https://www.town.takahata.yamagata.jp/soshikiichiran/kikaku/3/kokyokotsu/4511.html ）、協議の場は高畠町公共交通会議（H22設置 https://www.town.takahata.yamagata.jp/soshikiichiran/kikaku/3/machizukuri/4298.html ）。国交省一覧(R8.5末)に単独計画あり（期間満了でない）ことから、R7年度末頃策定・R8開始と推定。計画期間は検索結果本文で確認できず（計画案PDF・町サイトはWebFetch不可）。参考：山形県地域公共交通計画（次期）はR8〜R12（https://www.pref.yamagata.jp/documents/50579/keikaku_honpen.pdf ）。 根拠: 高畠町地域公共交通計画…意見募集期間は令和7年12月17日（水曜日）～令和8年1月7日（水曜日） 【追加調査 2026-10】環境：第2次（H25.3策定）がR4年度で期間終了→第3次高畠町環境基本計画をR5年度から実施（計画ページ https://www.town.takahata.yamagata.jp/kurashi/gyoseijoho/kakushukeikaku/1/2728.html ）。終期は検索3回で本文に出ず、10年間と仮定しR14と推定。 根拠: 第2次計画の計画期間が令和4年度で終了…令和5年度から第3次計画</t>
         </is>
       </c>
       <c r="S31" s="15" t="inlineStr">
@@ -15797,18 +15854,20 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定）</t>
+          <t>川西町地域公共交通計画</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>R8〜不明</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="n"/>
+          <t>R8〜R12</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>12</v>
+      </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr">
@@ -15818,7 +15877,7 @@
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.yamagata.jp/020057/kurashi/kendo/kotsuseisaku/ykotsu_kasseikakyougikai.html</t>
+          <t>https://www.town.kawanishi.yamagata.jp/kurashi/doro/02keikaku.pdf</t>
         </is>
       </c>
       <c r="L32" s="11" t="n"/>
@@ -15841,7 +15900,7 @@
       <c r="Q32" s="11" t="n"/>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：環境基本計画は検索で見当たらず（政策・計画 https://www.town.kawanishi.yamagata.jp/machinojoho/seisaku/ ）。</t>
+          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：環境基本計画は検索で見当たらず（政策・計画 https://www.town.kawanishi.yamagata.jp/machinojoho/seisaku/ ）。 【追加調査 2026-10】町単独の『川西町地域公共交通計画』を確認（区域：町全域、計画期間R8〜R12の5年間、デマンド型乗合交通等）。町サイト掲載 本編 https://www.town.kawanishi.yamagata.jp/kurashi/doro/02keikaku.pdf 、概要 https://www.town.kawanishi.yamagata.jp/kurashi/doro/01keikakugaiyou.pdf （2026-10-02検索。WebFetchはブロックのため本文直接閲覧不可、検索結果本文で期間確認）。R8開始の新計画のため策定済。広域：フラワー長井線（2市2町）は鉄道事業再構築実施計画R6.4.1〜R16.3.31（https://www.mlit.go.jp/report/press/tetsudo05_hh_000146.html ）。県計画の記載は参考に格下げ。 根拠: 計画期間は令和８年度（2026年度）から令和１２年度（2030年度）までの５年間</t>
         </is>
       </c>
       <c r="S32" s="15" t="inlineStr">
@@ -16003,7 +16062,7 @@
       <c r="Q34" s="11" t="n"/>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：環境基本計画は検索で見当たらず。</t>
+          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：環境基本計画は検索で見当たらず。 【追加調査 2026-10】国交省一覧の広域計画『フラワー長井線沿線』は、長井市・南陽市・川西町・白鷹町が平成28年2月に作成した『フラワー長井線沿線地域公共交通網形成計画』（H28.4〜R3.3＝H28〜R2、期間満了）と判断（本文PDF：https://www.town.kawanishi.yamagata.jp/machinojoho/seisaku/2017-1017-1735.pdf ）。後継の沿線広域交通計画は検索で確認できず。鉄道部分は鉄道事業再構築実施計画（R6.4.1〜R16.3.31、https://www.mlit.go.jp/report/press/tetsudo05_hh_000146.html ）が継続。町単独の地域公共交通計画は確認できず、白鷹町地域公共交通会議は山形県地域公共交通計画の町部分（デマンドタクシー全町線等、https://www.pref.yamagata.jp/documents/34797/20230628_6-10_31.pdf ）を協議。現行データ（県計画）を維持。2026-10-02検索。 根拠: フラワー長井線沿線地域公共交通網形成計画（平成28年2月、長井市・南陽市・川西町・白鷹町）／計画期間 平成28年4月〜平成33年3月</t>
         </is>
       </c>
       <c r="S34" s="15" t="inlineStr">
@@ -16202,7 +16261,7 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>山形県地域公共交通計画（県・市町村共同、次期計画R8.3.27策定）</t>
+          <t>庄内町地域公共交通計画</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -16223,7 +16282,7 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.yamagata.jp/020057/kurashi/kendo/kotsuseisaku/ykotsu_kasseikakyougikai.html</t>
+          <t>https://www.town.shonai.lg.jp/kurashi/koutsu/chiikikoukyou/tiikikoukyokotsukaigi.html</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
@@ -16254,7 +16313,7 @@
       </c>
       <c r="R37" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独の地域公共交通計画は検索で確認できず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第2次（H29.3策定）の後継として第3次案のパブコメを経てR8.3策定とみられる（期間未確認）。計画一覧 https://www.town.shonai.lg.jp/gyousei/shisaku/index.files/R6_keikaku.pdf 。</t>
+          <t>交通：町単独の地域公共交通計画は検索で確認できず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第2次（H29.3策定）の後継として第3次案のパブコメを経てR8.3策定とみられる（期間未確認）。計画一覧 https://www.town.shonai.lg.jp/gyousei/shisaku/index.files/R6_keikaku.pdf 。 【追加調査 2026-10】町単独の『庄内町地域公共交通計画』をR8.3策定（基本方針「住み続けたいまちの基盤となる交通体系の構築」）。計画（案）のパブコメ R8.2.2〜R8.2.24（https://www.town.shonai.lg.jp/gyousei/public/iken/koutuukeikaku.html ）。計画に基づき既存循環線4路線・デマンド2路線を区域運行型デマンドタクシー「しょうないデマンド」へ転換、AI予約配車システム導入委託をプロポで実施（https://www.town.shonai.lg.jp/kurashi/koutsu/choueibasu/demandtaxi_reservation_system.html ）。計画期間の終期は検索結果本文で確認できず（R8開始、5年ならR8〜R12）。町サイトはWebFetchブロック。2026-10-02検索。 根拠: 令和8年度からの「庄内町地域公共交通計画（案）」…令和8年2月2日から令和8年2月24日までパブリックコメント募集</t>
         </is>
       </c>
       <c r="S37" s="15" t="inlineStr">
@@ -16322,13 +16381,15 @@
       </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N38" s="13" t="n"/>
+          <t>R4〜R13</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>13</v>
+      </c>
       <c r="O38" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">
@@ -16343,7 +16404,7 @@
       </c>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第3次遊佐町環境基本計画の存在を確認（期間未確認）。R8.1策定の第9次振興計画で環境基本計画に言及。</t>
+          <t>交通：町単独計画は見当たらず。山形県地域公共交通計画（前計画R3〜R7）は市町村の利便増進実施計画等を内包する県全域計画。次期計画はR8.2パブコメ（https://www200.pref.yamagata.jp/020057/keikakupabukomepress2.html ）を経てR8.3.27策定（期間は未確認、R8開始）。 環境：第3次遊佐町環境基本計画の存在を確認（期間未確認）。R8.1策定の第9次振興計画で環境基本計画に言及。 【追加調査 2026-10】環境：町ドメイン検索の要約で第3次遊佐町環境基本計画の計画期間は令和4（2022）〜令和13（2031）年度。裏付け検索1回では再現せず、計画PDFのURLも未特定のため推定。 根拠: 第３次遊佐町環境基本計画 計画期間 令和4年度〜令和13年度（検索要約）</t>
         </is>
       </c>
       <c r="S38" s="15" t="inlineStr">
@@ -17117,13 +17178,15 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N9" s="13" t="n"/>
+          <t>H30〜R9</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>9</v>
+      </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr">
@@ -17138,7 +17201,7 @@
       </c>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>交通：計画ページあり、R7.1.29一部改定。計画期間は検索で確認できず。環境：第3次計画（中間改定版）を公表（計画・条例ページ）、期間は検索で確認できず。区域施策編はR4〜R12。参考：須賀川市の環境（R7.5）https://www.city.sukagawa.fukushima.jp/material/files/group/47/r05shinokankyo.pdf</t>
+          <t>交通：計画ページあり、R7.1.29一部改定。計画期間は検索で確認できず。環境：第3次計画（中間改定版）を公表（計画・条例ページ）、期間は検索で確認できず。区域施策編はR4〜R12。参考：須賀川市の環境（R7.5）https://www.city.sukagawa.fukushima.jp/material/files/group/47/r05shinokankyo.pdf 【追加調査 2026-10】市サイト内検索の要約で第3次計画はH30(2018)〜R9(2027)、R4.3中間見直し（出典は『須賀川市の環境』R7.5 https://www.city.sukagawa.fukushima.jp/material/files/group/47/r05shinokankyo.pdf と思われるが本文未確認）。R9終期だが次期（第4次）計画の策定業務・審議会等は市サイト検索で見当たらず。 根拠: Third Environmental Basic Plan covers the period from fiscal year 2018 (Heisei 30) to fiscal year 2027 (Reiwa 9)（検索要約）</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -17203,18 +17266,20 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>喜多方市環境基本計画（中間見直し版）</t>
+          <t>喜多方市環境基本計画（R4.3中間見直し）</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N10" s="13" t="n"/>
+          <t>H28〜R8</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="n">
+        <v>8</v>
+      </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P10" s="13" t="inlineStr">
@@ -17222,10 +17287,14 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="n"/>
+      <c r="Q10" s="14" t="inlineStr">
+        <is>
+          <t>https://www.city.kitakata.fukushima.jp/life/4/25/125/</t>
+        </is>
+      </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>交通：会津圏域6市町村共同計画、パブコメR7.12.15〜R8.1.5、R8〜R13。環境：環境基本計画ありR4.3.29中間見直し（地球温暖化対策総合ビジョン2023-2050を個別方針に位置付け https://www.city.kitakata.fukushima.jp/soshiki/kankyo/49610.html ）、計画期間は検索で確認できず（中間見直しR4から逆算するとR8前後終期の可能性、要確認）。</t>
+          <t>交通：会津圏域6市町村共同計画、パブコメR7.12.15〜R8.1.5、R8〜R13。環境：環境基本計画ありR4.3.29中間見直し（地球温暖化対策総合ビジョン2023-2050を個別方針に位置付け https://www.city.kitakata.fukushima.jp/soshiki/kankyo/49610.html ）、計画期間は検索で確認できず（中間見直しR4から逆算するとR8前後終期の可能性、要確認）。 【追加調査 2026-10】市サイト内検索の要約2件でH28(2016)〜R8(2026)、R4.3中間見直し（パブコメ結果R4.3.2公表）。本文未確認のため推定（e_urlは市の計画一覧ページ）。R8終期だが次期計画の策定業務・審議会・パブコメ等は市サイト検索（R7〜R8）で見当たらず＝未確認。 根拠: planning period spanning fiscal year 2016 (平成28年度) through fiscal year 2026 (令和8年度)（検索要約）</t>
         </is>
       </c>
       <c r="S10" s="15" t="inlineStr">
@@ -17278,16 +17347,22 @@
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>第2次相馬市環境基本計画</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N11" s="13" t="n"/>
+          <t>H30〜R9</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="n">
+        <v>9</v>
+      </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr">
@@ -17295,15 +17370,19 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="n"/>
+      <c r="Q11" s="14" t="inlineStr">
+        <is>
+          <t>https://www.city.soma.fukushima.jp/shinososhiki/seikatsukankyoka/keikaku_shisaku/1622.html</t>
+        </is>
+      </c>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>交通・環境とも検索で確認できず（市サイト内検索でも該当ページ出ず、南相馬市の結果に埋もれる）。公共交通情報 https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/seikatsu/1/1679.html 。参考：福島県地域公共交通計画（R6.3策定）https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf</t>
+          <t>交通・環境とも検索で確認できず（市サイト内検索でも該当ページ出ず、南相馬市の結果に埋もれる）。公共交通情報 https://www.city.soma.fukushima.jp/shinososhiki/kikakuseisakuka/seikatsu/1/1679.html 。参考：福島県地域公共交通計画（R6.3策定）https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf 【追加調査 2026-10】市HP「環境・廃棄物」計画ページ（1622.html）に相馬市環境基本条例に基づく相馬市環境基本計画を掲載。検索要約で第2次計画はH30.3策定・10年間（H30〜R9）、策定5年経過で見直し実施。R9終期だが第3次計画の策定作業は市サイト検索で見当たらず（R8.8に長期総合計画の審議会・市民アンケートは開始）。 根拠: 第2次相馬市環境基本計画は平成30年3月に策定され、10年間を計画期間（検索要約）</t>
         </is>
       </c>
       <c r="S11" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T11" s="11" t="inlineStr">
@@ -17466,18 +17545,18 @@
       </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q13" s="11" t="n"/>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>交通：R4〜R8、R6.6一部改訂。R8.3協議会で「第2次田村市地域公共交通計画策定業務」の審査委員会設置を協議→次期計画策定着手（資料 https://www.city.tamura.lg.jp/soshiki/1/assets/%E8%B3%87%E6%96%99%E4%B8%80%E5%BC%8F%EF%BC%88R7%E7%AC%AC1%E5%9B%9E%EF%BC%89.pdf ほか）。環境：環境基本計画は検索で確認できず（一般廃棄物処理計画等のみヒット）。</t>
-        </is>
-      </c>
-      <c r="S13" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：R4〜R8、R6.6一部改訂。R8.3協議会で「第2次田村市地域公共交通計画策定業務」の審査委員会設置を協議→次期計画策定着手（資料 https://www.city.tamura.lg.jp/soshiki/1/assets/%E8%B3%87%E6%96%99%E4%B8%80%E5%BC%8F%EF%BC%88R7%E7%AC%AC1%E5%9B%9E%EF%BC%89.pdf ほか）。環境：環境基本計画は検索で確認できず（一般廃棄物処理計画等のみヒット）。 【追加調査 2026-10】市サイト内検索で環境基本計画は見当たらず、環境分野は第4期田村市地球温暖化対策実行計画【区域施策編・事務事業編】(R4〜R12, https://www.city.tamura.lg.jp/soshiki/8/entry_5.html)・地域新エネルギービジョン・一般廃棄物処理基本計画のみ。第2次総合計画が上位計画。根拠は検索ベースで中程度。 根拠: 第４期田村市地球温暖化対策実行計画【区域施策編・事務事業編】</t>
+        </is>
+      </c>
+      <c r="S13" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T13" s="11" t="inlineStr">
@@ -17542,13 +17621,15 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="N14" s="13" t="n"/>
+          <t>R5〜R12（推定）</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="n">
+        <v>12</v>
+      </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="P14" s="13" t="inlineStr">
@@ -17563,7 +17644,7 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>交通：新計画R8〜R12（R8.1資料）。旧計画概要 https://www.city.minamisoma.lg.jp/material/files/group/13/koutuukeikakugaiyou.pdf 。環境：第三次計画R5.10策定（第二次はH36=R6まで）、期間は検索で確認できず（R6開始と推定）。ゼロカーボン推進計画2023〜2030。</t>
+          <t>交通：新計画R8〜R12（R8.1資料）。旧計画概要 https://www.city.minamisoma.lg.jp/material/files/group/13/koutuukeikakugaiyou.pdf 。環境：第三次計画R5.10策定（第二次はH36=R6まで）、期間は検索で確認できず（R6開始と推定）。ゼロカーボン推進計画2023〜2030。 【追加調査 2026-10】市サイト内検索の要約で第三次計画は2023〜2030年度（8年間）・4年後中間評価とされる（R5.10策定、第三次総合計画R5〜R12と整合）。ただし別の要約ではR6〜R13とも出ており本文未確認のため推定。終期R12で次期作業は対象外。 根拠: The plan period spans from fiscal year 2023 to fiscal year 2030 (8 years)（検索要約）</t>
         </is>
       </c>
       <c r="S14" s="15" t="inlineStr">
@@ -17724,7 +17805,7 @@
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>不明（R1〜R10と推定）</t>
         </is>
       </c>
       <c r="N16" s="13" t="n"/>
@@ -17741,7 +17822,7 @@
       <c r="Q16" s="11" t="n"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>2026-07-06 「本宮市第2期地域公共交通計画策定支援業務委託」公募型プロポーザル実施を市が公表（生活環境課、https://www.city.motomiya.lg.jp/soshiki/10/tiikikoukyoukoutsuukeikaku.html）。現行計画期間は未確認（第2期がR9開始と推定）。環境基本計画は「本宮市第2次環境基本計画」（市HP掲載、2019-05-13更新と検索結果に表示、計画・事業ページ https://www.city.motomiya.lg.jp/life/6/25/ ）だが計画期間は再検索でも確認できず。ゼロカーボンシティ宣言2021年3月（https://www.city.motomiya.lg.jp/soshiki/10/2050zerocarboncity.html）。</t>
+          <t>2026-07-06 「本宮市第2期地域公共交通計画策定支援業務委託」公募型プロポーザル実施を市が公表（生活環境課、https://www.city.motomiya.lg.jp/soshiki/10/tiikikoukyoukoutsuukeikaku.html）。現行計画期間は未確認（第2期がR9開始と推定）。環境基本計画は「本宮市第2次環境基本計画」（市HP掲載、2019-05-13更新と検索結果に表示、計画・事業ページ https://www.city.motomiya.lg.jp/life/6/25/ ）だが計画期間は再検索でも確認できず。ゼロカーボンシティ宣言2021年3月（https://www.city.motomiya.lg.jp/soshiki/10/2050zerocarboncity.html）。 【追加調査 2026-10】市サイト内検索の要約で第1次本宮市環境基本計画はH21〜H30の10年間→第2次（2019.5掲載）はR1〜R10の可能性が高いが本文で確認できず。計画・事業ページ https://www.city.motomiya.lg.jp/life/6/25/ 。 根拠: 本宮市環境基本計画の計画期間は平成21年度から平成30年度までの10年間（検索要約、第1次）</t>
         </is>
       </c>
       <c r="S16" s="15" t="inlineStr">
@@ -17881,18 +17962,18 @@
       </c>
       <c r="P18" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画は町HP内検索でも確認できず。「地域公共交通あり方協議会」設置、国見まちなかタクシー・ももたんパス（タクシー助成実証、https://www.town.kunimi.fukushima.jp/soshiki/4/16576.html）等を実施。広報くにみR3.4号特集、町資料「これからの公共交通のカタチ」（https://www.town.kunimi.fukushima.jp/uploaded/attachment/6659.pdf）。環境基本計画は検索で確認できず。代替として地球温暖化対策実行計画をR6.1.9公表（住民防災課所管）。第6次総合計画（KuniMirai2030）あり。</t>
+          <t>地域公共交通計画は町HP内検索でも確認できず。「地域公共交通あり方協議会」設置、国見まちなかタクシー・ももたんパス（タクシー助成実証、https://www.town.kunimi.fukushima.jp/soshiki/4/16576.html）等を実施。広報くにみR3.4号特集、町資料「これからの公共交通のカタチ」（https://www.town.kunimi.fukushima.jp/uploaded/attachment/6659.pdf）。環境基本計画は検索で確認できず。代替として地球温暖化対策実行計画をR6.1.9公表（住民防災課所管）。第6次総合計画（KuniMirai2030）あり。 【追加調査 2026-10】町サイト内検索で環境基本計画は見当たらず。環境分野は地球温暖化対策実行計画（R6.1公表）、自然環境等と再エネ発電事業との調和条例（https://www.town.kunimi.fukushima.jp/soshiki/4/18511.html）、第6次総合計画（R3〜R12）のみ。根拠は検索ベース。</t>
         </is>
       </c>
       <c r="S18" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr">
@@ -17922,16 +18003,22 @@
         <f>IF(P19="計画なし","－",IF(P19="策定済","✕",IF(N19="","？",IF(AND(N19&gt;=TGT_MIN,N19&lt;=TGT_MAX),IF(P19="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
-      <c r="F19" s="11" t="n"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>福島県避難地域広域公共交通計画（県・避難12市町村の広域計画）</t>
+        </is>
+      </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="n"/>
+          <t>R5〜R9</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr">
@@ -17939,7 +18026,11 @@
           <t>未確認</t>
         </is>
       </c>
-      <c r="K19" s="11" t="n"/>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/sec/16005d/hinankeikaku.html</t>
+        </is>
+      </c>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
@@ -17954,23 +18045,23 @@
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q19" s="11" t="n"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画は検索で確認できず。川俣町地域公共交通会議（H20.3設置、https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/kawamatakoukyokotsu.html）がH21.3に地域公共交通総合連携計画を策定（デマンド型乗合タクシー導入、国交省資料）—旧法計画で現行計画は未確認。環境基本計画も検索で確認できず（各種計画一覧 https://www.town.kawamata.lg.jp/site/chosei-shisetsu/list74.html 要確認）。循環型社会形成推進地域計画（R3〜R7）あり。</t>
-        </is>
-      </c>
-      <c r="S19" s="18" t="inlineStr">
-        <is>
-          <t>未調査</t>
-        </is>
-      </c>
-      <c r="T19" s="17" t="inlineStr">
-        <is>
-          <t>掲載（広域：福島県避難地域）【当方未把握】</t>
+          <t>地域公共交通計画は検索で確認できず。川俣町地域公共交通会議（H20.3設置、https://www.town.kawamata.lg.jp/site/kurashi-tetsuzuki/kawamatakoukyokotsu.html）がH21.3に地域公共交通総合連携計画を策定（デマンド型乗合タクシー導入、国交省資料）—旧法計画で現行計画は未確認。環境基本計画も検索で確認できず（各種計画一覧 https://www.town.kawamata.lg.jp/site/chosei-shisetsu/list74.html 要確認）。循環型社会形成推進地域計画（R3〜R7）あり。 【追加調査 2026-10】国交省一覧の広域計画『福島県避難地域』＝福島県避難地域広域公共交通計画（前身はH30.3.28策定の避難地域広域公共交通網形成計画）。対象は田村市・南相馬市・川俣町・広野町・楢葉町・富岡町・川内村・大熊町・双葉町・浪江町・葛尾村・飯舘村の12市町村。計画期間R5.4〜R10.3。次期計画：R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画策定（R10.4開始）予定。R8.6.25福島県地域公共交通活性化協議会で避難地域広域公共交通検討協議会の今年度スケジュールを報告（資料 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf 、協議会 https://www.pref.fukushima.lg.jp/sec/16005d/chiikikoukyoukasseikakyougikai.html ）。策定委託・パブコメは未確認のため着手済とはせず。町単独計画は確認できず（H21.3旧法連携計画のみ）。2026-10-02検索。 根拠: 避難地域広域公共交通計画は令和5年4月から令和10年3月までの計画期間…令和８年度に最終評価 【追加調査 2026-10】町サイト内検索で環境基本計画は見当たらず、環境分野は「川俣町地域まるごと脱炭素計画（地球温暖化対策実行計画 区域施策編）」（https://www.town.kawamata.lg.jp/site/chosei-shisetsu/chiikimarugotodathutansokeikaku.html）と循環型社会形成推進地域計画のみ。 根拠: 川俣町地域まるごと脱炭素計画～川俣町地球温暖化対策実行計画（区域施策編）</t>
+        </is>
+      </c>
+      <c r="S19" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>掲載（広域：福島県避難地域）</t>
         </is>
       </c>
     </row>
@@ -18043,7 +18134,7 @@
       <c r="Q20" s="11" t="n"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画は素案パブコメR4.1.28〜2.25実施（結果 https://www.vill.otama.fukushima.jp/file/contents/527/25641/koukyoukoutuu_kekka.pdf）→R3年度末策定、期間は5年と推定（R8度末終了なら次期計画作業の可能性、ただし検索で確認できず）。デマンド型乗合タクシー（AI配車）・通勤通学バス運行。環境基本計画は検索で確認できず（各種計画一覧に見当たらず、第5次総合振興計画・立地適正化計画R6.8等のみ）。</t>
+          <t>地域公共交通計画は素案パブコメR4.1.28〜2.25実施（結果 https://www.vill.otama.fukushima.jp/file/contents/527/25641/koukyoukoutuu_kekka.pdf）→R3年度末策定、期間は5年と推定（R8度末終了なら次期計画作業の可能性、ただし検索で確認できず）。デマンド型乗合タクシー（AI配車）・通勤通学バス運行。環境基本計画は検索で確認できず（各種計画一覧に見当たらず、第5次総合振興計画・立地適正化計画R6.8等のみ）。 【追加調査 2026-10】大玉村環境基本条例（https://www.vill.otama.fukushima.jp/reiki_int/reiki_honbun/c522RG00000647.html）で村長に環境基本計画策定を規定しているが、計画本体は村サイト検索・一般検索とも見当たらず（総合振興計画・都市マス等のみ）。条例があるため計画なしとは断定せず未確認のまま。</t>
         </is>
       </c>
       <c r="S20" s="18" t="inlineStr">
@@ -18110,18 +18201,18 @@
       </c>
       <c r="P21" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q21" s="11" t="n"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画は町HP内検索でも確認できず（都市計画マスタープラン、鏡石駅周辺将来まちづくりビジョンR7.3のみ）。環境基本計画も検索で確認できず。各種まちづくり計画一覧: https://www.town.kagamiishi.fukushima.jp/kurashi/chousei/008285.html</t>
+          <t>地域公共交通計画は町HP内検索でも確認できず（都市計画マスタープラン、鏡石駅周辺将来まちづくりビジョンR7.3のみ）。環境基本計画も検索で確認できず。各種まちづくり計画一覧: https://www.town.kagamiishi.fukushima.jp/kurashi/chousei/008285.html 【追加調査 2026-10】町サイト内検索で環境基本計画は見当たらず、環境分野は第3次鏡石町地球温暖化対策実行計画（区域施策編・事務事業編）（https://www.town.kagamiishi.fukushima.jp/kurashi/kurashi_tetuzuki/kankyo/011647.html）のみ。 根拠: 第３次鏡石町地球温暖化対策実行計画（区域施策編、事務事業編）</t>
         </is>
       </c>
       <c r="S21" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T21" s="11" t="inlineStr">
@@ -18183,18 +18274,18 @@
       </c>
       <c r="P22" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q22" s="11" t="n"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画・環境基本計画とも検索で確認できず（村HPはほぼ検索インデックスなし）。小規模村で計画なしの可能性。</t>
+          <t>地域公共交通計画・環境基本計画とも検索で確認できず（村HPはほぼ検索インデックスなし）。小規模村で計画なしの可能性。 【追加調査 2026-10】村HP計画一覧（https://www.vill.tenei.fukushima.jp/life/4/16/120/）・サイト内検索で環境基本計画は見当たらず、第1次天栄村地球温暖化対策実行計画（区域施策編）・ゼロカーボンシティ宣言（https://www.vill.tenei.fukushima.jp/soshiki/3/zero-co2.html）・第五次総合計画のみ。</t>
         </is>
       </c>
       <c r="S22" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T22" s="11" t="inlineStr">
@@ -18256,18 +18347,18 @@
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q23" s="11" t="n"/>
       <c r="R23" s="11" t="inlineStr">
         <is>
-          <t>町単独の地域公共交通計画・環境基本計画は検索で確認できず。会津線沿線（会津若松市・下郷町・南会津町）で会津線活性化連携協議会が地域公共交通総合連携計画を策定（旧法）、会津鉄道の鉄道事業再構築実施計画はR7.4〜R17.3。会津地域の広域公共交通計画（2026〜2031、6市町村）の記載が検索要約にあるが対象市町村・名称は要確認。過疎地域持続的発展計画（R3〜R7）あり。</t>
+          <t>町単独の地域公共交通計画・環境基本計画は検索で確認できず。会津線沿線（会津若松市・下郷町・南会津町）で会津線活性化連携協議会が地域公共交通総合連携計画を策定（旧法）、会津鉄道の鉄道事業再構築実施計画はR7.4〜R17.3。会津地域の広域公共交通計画（2026〜2031、6市町村）の記載が検索要約にあるが対象市町村・名称は要確認。過疎地域持続的発展計画（R3〜R7）あり。 【追加調査 2026-10】町サイト内検索で環境基本計画・温暖化対策実行計画とも見当たらず。総合計画等ページ（https://www.town.shimogo.fukushima.jp/organization/sougouseisaku/kikakuseisaku/1/820.html）は第7次総合計画中心で、環境は総合計画の基本目標「住み続けたいまち（生活環境）」で扱う。根拠は検索ベースで弱め。</t>
         </is>
       </c>
       <c r="S23" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T23" s="11" t="inlineStr">
@@ -18335,7 +18426,7 @@
       <c r="Q24" s="11" t="n"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画・環境基本計画とも検索で確認できず。小規模村で計画なしの可能性（南会津地域4町村の共同交通計画も確認できず）。</t>
+          <t>地域公共交通計画・環境基本計画とも検索で確認できず。小規模村で計画なしの可能性（南会津地域4町村の共同交通計画も確認できず）。 【追加調査 2026-10】環境基本計画・地球温暖化対策実行計画とも検索で確認できず（ヒットは循環型社会形成推進地域計画 H29〜R3 https://www.env.go.jp/recycle/waste/3r_network/5_region/project_list/07_fukushima/06_hinoemata_h29.pdf のみ）。人口約500人の小規模村で計画なしの可能性高いが、村HPの計画一覧で否定確認できず未確認のまま。</t>
         </is>
       </c>
       <c r="S24" s="18" t="inlineStr">
@@ -18402,18 +18493,18 @@
       </c>
       <c r="P25" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>地域公共交通計画は町HP内検索でも確認できず（只見駅周回バス、雪んこタクシー等運行）。環境基本計画も検索で確認できず（ユネスコエコパーク関連の取組はあり）。</t>
+          <t>地域公共交通計画は町HP内検索でも確認できず（只見駅周回バス、雪んこタクシー等運行）。環境基本計画も検索で確認できず（ユネスコエコパーク関連の取組はあり）。 【追加調査 2026-10】町HP「環境関連の計画」ページ https://www.town.tadami.lg.jp/lifeguide/cat01/cat5/000082.html に掲載されるのは生活排水処理基本計画・一般廃棄物処理実施計画・地球温暖化対策実行計画等で、環境基本計画は無し（検索結果要約ベース）。環境施策は第七次只見町振興計画・野生動植物を保護する条例(H28.6)・ユネスコエコパークで対応。 根拠: 只見町は生活排水処理基本計画、一般廃棄物処理実施計画、地球温暖化対策実行計画などを策定（『環境関連の計画』ページ）</t>
         </is>
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T25" s="11" t="inlineStr">
@@ -18499,7 +18590,7 @@
       </c>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>交通計画はR6.3策定（R6.6改訂、本編 https://www.town.minamiaizu.lg.jp/material/files/group/3/6gatukaiteibann.pdf ）。会津線沿線3市町の連携計画・会津鉄道再構築（R7.4〜R17.3）にも関係。環境基本条例H19.12、第1次計画H21.3、第2次計画の期間は確認できず。地球温暖化対策実行計画（区域施策編）をR7.3策定（https://www.town.minamiaizu.lg.jp/official/soshikikarasagasu/kankyosuidoka/kakushukeikaku/1/3540.html）、ゼロカーボン宣言済、エスプールとゼロカーボンタウン連携協定。</t>
+          <t>交通計画はR6.3策定（R6.6改訂、本編 https://www.town.minamiaizu.lg.jp/material/files/group/3/6gatukaiteibann.pdf ）。会津線沿線3市町の連携計画・会津鉄道再構築（R7.4〜R17.3）にも関係。環境基本条例H19.12、第1次計画H21.3、第2次計画の期間は確認できず。地球温暖化対策実行計画（区域施策編）をR7.3策定（https://www.town.minamiaizu.lg.jp/official/soshikikarasagasu/kankyosuidoka/kakushukeikaku/1/3540.html）、ゼロカーボン宣言済、エスプールとゼロカーボンタウン連携協定。 【追加調査 2026-10】第2次計画の期間は検索で確認できず（町HP 450.htmlの要約：『2009年3月に南会津町環境基本計画を策定…前計画の策定から10年が経過したため第2次を策定』）。H31(2019)頃策定・10年計画ならR1〜R10頃と推測されるが未確認のため不明のまま。町は令和元〜6年度の環境年次報告書を公表。WebFetchは町HPブロック。 根拠: 前計画の策定から10年が経過したため、「第2次南会津町環境基本計画」を策定</t>
         </is>
       </c>
       <c r="S26" s="15" t="inlineStr">
@@ -18534,24 +18625,34 @@
         <f>IF(P27="計画なし","－",IF(P27="策定済","✕",IF(N27="","？",IF(AND(N27&gt;=TGT_MIN,N27&lt;=TGT_MAX),IF(P27="着手済","△","◎"),"✕"))))</f>
         <v/>
       </c>
-      <c r="F27" s="11" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>北塩原村地域公共交通計画</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="n"/>
+          <t>R7〜R11</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>11</v>
+      </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="n"/>
+          <t>策定済</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>https://www.vill.kitashiobara.fukushima.jp/soshiki/somukikaku/6805.html</t>
+        </is>
+      </c>
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
@@ -18572,17 +18673,17 @@
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>村単独の地域公共交通計画は検索で確認できず（会津圏域計画の対象外）。再検索でも確認できず（国交省事例:喜多方～裏磐梯バス・桧原湖周遊バス https://www.mlit.go.jp/sogoseisaku/transport/pdf/021_kitashiobara.pdf ）。 【環境】環境基本計画は検索で確認できず。代替として『北塩原村地域まるごと脱炭素計画』（区域施策編＋地域気候変動適応計画を兼ねる） https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3387.pdf 、事務事業編あり。ゼロカーボンシティ宣言済。</t>
-        </is>
-      </c>
-      <c r="S27" s="18" t="inlineStr">
-        <is>
-          <t>環境のみ調査</t>
-        </is>
-      </c>
-      <c r="T27" s="17" t="inlineStr">
-        <is>
-          <t>掲載【当方未把握】</t>
+          <t>村単独の地域公共交通計画は検索で確認できず（会津圏域計画の対象外）。再検索でも確認できず（国交省事例:喜多方～裏磐梯バス・桧原湖周遊バス https://www.mlit.go.jp/sogoseisaku/transport/pdf/021_kitashiobara.pdf ）。 【環境】環境基本計画は検索で確認できず。代替として『北塩原村地域まるごと脱炭素計画』（区域施策編＋地域気候変動適応計画を兼ねる） https://www.vill.kitashiobara.fukushima.jp/uploaded/attachment/3387.pdf 、事務事業編あり。ゼロカーボンシティ宣言済。 【追加調査 2026-10】村ページ『北塩原村地域公共交通計画を策定しました』（総務企画課、https://www.vill.kitashiobara.fukushima.jp/soshiki/somukikaku/6805.html ）で確認。従前の公共交通網形成計画を踏まえリ・デザインを目的に策定、計画期間R7〜R11の5年間。基本方針5本（村民の移動利便性向上、周辺都市へのアクセス性向上、安定的な提供体制、情報発信、利用機会創出）。R7開始の新計画のため策定済。前回の『会津圏域対象外・確認できず』の記載を訂正。2026-10-02検索。 根拠: 本計画の実施期間は令和７年度から令和１１年度までの５年間</t>
+        </is>
+      </c>
+      <c r="S27" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>掲載</t>
         </is>
       </c>
     </row>
@@ -18957,7 +19058,7 @@
       <c r="Q32" s="11" t="n"/>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.yugawa.fukushima.jp/site/gyousei-top/various-plans.html ）。</t>
+          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.yugawa.fukushima.jp/site/gyousei-top/various-plans.html ）。 【追加調査 2026-10】村HPドメイン限定検索でも環境基本計画はヒットせず（国土利用計画・過疎計画・公共施設等総合管理計画のみ）。各種計画ページ https://www.vill.yugawa.fukushima.jp/site/gyousei-top/various-plans.html で否定確認できておらず未確認のまま（計画なしの可能性高）。</t>
         </is>
       </c>
       <c r="S32" s="18" t="inlineStr">
@@ -19034,18 +19135,18 @@
       </c>
       <c r="P33" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず。役場地球温暖化対策実行計画(R4.1改訂) https://www.town.yanaizu.fukushima.jp/docs/2022120500022/file_contents/ondankakeikaku.pdf 、R4.12ゼロカーボンシティ宣言。</t>
-        </is>
-      </c>
-      <c r="S33" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 【環境】環境基本計画は検索で確認できず。役場地球温暖化対策実行計画(R4.1改訂) https://www.town.yanaizu.fukushima.jp/docs/2022120500022/file_contents/ondankakeikaku.pdf 、R4.12ゼロカーボンシティ宣言。 【追加調査 2026-10】町HPドメイン限定検索で環境基本計画ヒットせず。各種計画ページ https://www.town.yanaizu.fukushima.jp/docs/2021080600018/ 、環境関連は役場地球温暖化対策実行計画(事務事業編,R4.1改訂)とゼロカーボンシティ宣言(R4.12) https://www.town.yanaizu.fukushima.jp/docs/2022120500022 のみ。総合計画（第6次柳津町振興計画）で環境を包含。 根拠: 検索結果では環境基本計画は見当たらず、ゼロカーボンシティ宣言・実行計画のみ</t>
+        </is>
+      </c>
+      <c r="S33" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T33" s="11" t="inlineStr">
@@ -19107,18 +19208,18 @@
       </c>
       <c r="P34" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q34" s="11" t="n"/>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。三島町ゼロカーボンビジョン(2022.5) https://www.town.mishima.fukushima.jp/uploaded/attachment/1087.pdf 、第2次実行計画（事務事業編）R6.3策定・2024〜2030 http://www.town.mishima.fukushima.jp/soshiki/chiiki-seisaku/4267.html 。</t>
+          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。三島町ゼロカーボンビジョン(2022.5) https://www.town.mishima.fukushima.jp/uploaded/attachment/1087.pdf 、第2次実行計画（事務事業編）R6.3策定・2024〜2030 http://www.town.mishima.fukushima.jp/soshiki/chiiki-seisaku/4267.html 。 【追加調査 2026-10】町HPドメイン限定検索で環境基本計画ヒットせず。環境関連は三島町ゼロカーボンビジョン(R4.5) https://www.town.mishima.fukushima.jp/soshiki/chiiki-seisaku/47.html と第2次地球温暖化対策実行計画(事務事業編,R6.3.1策定) http://www.town.mishima.fukushima.jp/soshiki/chiiki-seisaku/4267.html のみ。第5次三島町振興計画（後期基本計画案）が環境分野を包含。 根拠: 第２次三島町 地球温暖化対策実行計画(事務事業編） 令和6 年３月１日 策定</t>
         </is>
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr">
@@ -19180,18 +19281,18 @@
       </c>
       <c r="P35" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q35" s="11" t="n"/>
       <c r="R35" s="11" t="inlineStr">
         <is>
-          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。自然環境等と再エネ発電事業等との調和に関する条例制定(パブコメ) https://www.town.kaneyama.fukushima.jp/soshiki/54/pabukomesizennkannkyou.html 。R7.9議会でゼロカーボン表明検討の質疑。</t>
+          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず。自然環境等と再エネ発電事業等との調和に関する条例制定(パブコメ) https://www.town.kaneyama.fukushima.jp/soshiki/54/pabukomesizennkannkyou.html 。R7.9議会でゼロカーボン表明検討の質疑。 【追加調査 2026-10】町HPドメイン限定検索で環境基本計画ヒットせず（第五次総合計画 https://www.town.kaneyama.fukushima.jp/soshiki/54/daigojisougoukeikaku.html 、国土強靱化計画等のみ）。環境施策は総合計画と自然環境・再エネ調和条例で対応。ゼロカーボン表明も検討段階。</t>
         </is>
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>未調査</t>
+          <t>環境のみ調査</t>
         </is>
       </c>
       <c r="T35" s="11" t="inlineStr">
@@ -19259,7 +19360,7 @@
       <c r="Q36" s="11" t="n"/>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.showa.fukushima.jp/procedure/1096/ ）。</t>
+          <t>単独/奥会津広域の地域公共交通計画は再検索でも確認できず（只見線利活用計画のみ）（会津圏域計画の対象外）。 【環境】環境基本計画は検索で確認できず（村HP各種計画 https://www.vill.showa.fukushima.jp/procedure/1096/ ）。 【追加調査 2026-10】村HPドメイン限定検索で環境基本計画・温暖化対策実行計画ともヒットせず（各種計画 https://www.vill.showa.fukushima.jp/procedure/1096/ 、第6次昭和村振興計画のみ）。計画なしの可能性高いが一覧内容を直接確認できず未確認のまま。</t>
         </is>
       </c>
       <c r="S36" s="18" t="inlineStr">
@@ -19336,18 +19437,18 @@
       </c>
       <c r="P37" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q37" s="11" t="n"/>
       <c r="R37" s="11" t="inlineStr">
         <is>
-          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 別途、町単独の『会津美里町地域公共交通計画（案）』(令和8年、町地域公共交通会議資料) https://www.town.aizumisato.fukushima.jp/material/files/group/3/keikakuann.pdf が作成中＝着手済（期間未確認）。 【環境】環境基本計画は検索で確認できず。地球温暖化対策実行計画（事務事業編R4〜R6） https://www.town.aizumisato.fukushima.jp/gyosei/gyoseijoho/8/7/2/3496.html 、再エネ導入目標等策定支援業務プロポーザル https://www.town.aizumisato.fukushima.jp/soshiki/1009/3/10/5800.html 、ゼロカーボン宣言済。</t>
-        </is>
-      </c>
-      <c r="S37" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>前計画 会津圏域地域公共交通網形成計画(R2.3策定,R8.3終了)の後継として令和8年3月策定、R8〜R13の6年間（対象:会津若松市・喜多方市・会津坂下町・湯川村・柳津町・会津美里町）。パブコメ結果 https://www.pref.fukushima.lg.jp/sec/16005d/aizukenikimoukeikaku.html 。 別途、町単独の『会津美里町地域公共交通計画（案）』(令和8年、町地域公共交通会議資料) https://www.town.aizumisato.fukushima.jp/material/files/group/3/keikakuann.pdf が作成中＝着手済（期間未確認）。 【環境】環境基本計画は検索で確認できず。地球温暖化対策実行計画（事務事業編R4〜R6） https://www.town.aizumisato.fukushima.jp/gyosei/gyoseijoho/8/7/2/3496.html 、再エネ導入目標等策定支援業務プロポーザル https://www.town.aizumisato.fukushima.jp/soshiki/1009/3/10/5800.html 、ゼロカーボン宣言済。 【追加調査 2026-10】町HPドメイン限定・一般検索とも環境基本計画/環境基本条例ヒットせず。環境関連は地球温暖化対策実行計画(事務事業編R4〜R6) https://www.town.aizumisato.fukushima.jp/gyosei/gyoseijoho/8/7/2/3496.html 、ゼロカーボン宣言、再エネ導入目標策定支援業務のみ。第4次総合計画(2026〜2035,素案) https://www.town.aizumisato.fukushima.jp/material/files/group/3/03dai4jisougoukeikakusoan.pdf が環境分野を包含。 根拠: 地球温暖化対策の推進（令和4年度から令和6年度）について</t>
+        </is>
+      </c>
+      <c r="S37" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T37" s="11" t="inlineStr">
@@ -19407,7 +19508,7 @@
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>西郷村環境基本計画</t>
+          <t>西郷村環境基本計画（改定）</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr">
@@ -19423,7 +19524,7 @@
       </c>
       <c r="P38" s="13" t="inlineStr">
         <is>
-          <t>着手済</t>
+          <t>策定済</t>
         </is>
       </c>
       <c r="Q38" s="14" t="inlineStr">
@@ -19433,7 +19534,7 @@
       </c>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>旧 西郷村地域公共交通網形成計画 https://www.vill.nishigo.fukushima.jp/soshiki/kikakuseisakuka/shisaku_keikaku/2/2322.html の後継。策定調査業務をプロポーザル発注 https://www.vill.nishigo.fukushima.jp/soshiki/kikakuseisakuka/shisaku_keikaku/2/5707.html 、素案R8.3、R8.3策定、計画期間R8〜R13の6年間（URLは素案）。AIデマンド交通実証導入も進行。 【環境】『西郷村環境基本計画』あり https://www.vill.nishigo.fukushima.jp/soshiki/kankyohozenka/kankyo_gomi/2/4547.html （期間は検索で確認できず）。R8.9.3ゼロ・カーボンシティ宣言ページで環境基本計画の改定・地球温暖化対策実行計画（区域施策編）策定に言及 https://www.vill.nishigo.fukushima.jp/soshiki/juminseikatsuka/kankyo_gomi/2/6556.html （改定版の策定済/作業中かは要確認）。</t>
+          <t>旧 西郷村地域公共交通網形成計画 https://www.vill.nishigo.fukushima.jp/soshiki/kikakuseisakuka/shisaku_keikaku/2/2322.html の後継。策定調査業務をプロポーザル発注 https://www.vill.nishigo.fukushima.jp/soshiki/kikakuseisakuka/shisaku_keikaku/2/5707.html 、素案R8.3、R8.3策定、計画期間R8〜R13の6年間（URLは素案）。AIデマンド交通実証導入も進行。 【環境】『西郷村環境基本計画』あり https://www.vill.nishigo.fukushima.jp/soshiki/kankyohozenka/kankyo_gomi/2/4547.html （期間は検索で確認できず）。R8.9.3ゼロ・カーボンシティ宣言ページで環境基本計画の改定・地球温暖化対策実行計画（区域施策編）策定に言及 https://www.vill.nishigo.fukushima.jp/soshiki/juminseikatsuka/kankyo_gomi/2/6556.html （改定版の策定済/作業中かは要確認）。 【追加調査 2026-10】R8.9.3ゼロ・カーボンシティ宣言ページ https://www.vill.nishigo.fukushima.jp/soshiki/juminseikatsuka/kankyo_gomi/2/6556.html に関連資料として『環境基本計画（改定）』『地球温暖化対策実行計画【区域施策編】』が掲載（複数検索要約で『策定している』）→改定版はR8頃策定済と判断（着手済から変更、ただし本文未確認で策定月・期間は不明）。旧計画ページ https://www.vill.nishigo.fukushima.jp/soshiki/kankyohozenka/kankyo_gomi/2/4547.html は2023.5.19更新。WebFetchは村HPブロック。 根拠: 2050年脱炭素…ゼロ・カーボンシティ宣言（2026年9月3日）関連：環境基本計画（改定）・地球温暖化対策実行計画【区域施策編】</t>
         </is>
       </c>
       <c r="S38" s="15" t="inlineStr">
@@ -19516,7 +19617,7 @@
       <c r="Q39" s="11" t="n"/>
       <c r="R39" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。コミュニティバス「ふれあい号」3路線運行。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。村HP「各種計画の一覧」https://www.vill.izumizaki.fukushima.jp/page/page001839.html で要確認。</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。コミュニティバス「ふれあい号」3路線運行。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。村HP「各種計画の一覧」https://www.vill.izumizaki.fukushima.jp/page/page001839.html で要確認。 【追加調査 2026-10】村HPドメイン限定検索で環境基本計画ヒットせず（各種計画 https://www.vill.izumizaki.fukushima.jp/page/dir000364.html 、各種計画の一覧 https://www.vill.izumizaki.fukushima.jp/page/page001839.html に掲載有無は要約で確認できず）。計画なしの可能性高いが未確認のまま。</t>
         </is>
       </c>
       <c r="S39" s="18" t="inlineStr">
@@ -19599,7 +19700,7 @@
       <c r="Q40" s="11" t="n"/>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。しらかわ地域定住自立圏構成村。環境基本計画・温暖化対策実行計画とも検索で確認できず。</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。しらかわ地域定住自立圏構成村。環境基本計画・温暖化対策実行計画とも検索で確認できず。 【追加調査 2026-10】環境基本計画・温暖化対策実行計画とも検索（村HPドメイン指定含む）でヒットなし。小規模村で計画なしの可能性高いが根拠資料なく未確認のまま。</t>
         </is>
       </c>
       <c r="S40" s="18" t="inlineStr">
@@ -19750,7 +19851,7 @@
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>不明（R3.3策定。要約1件に「令和32年（2050年）まで」とあるが長期目標年の誤認の可能性）</t>
         </is>
       </c>
       <c r="N42" s="13" t="n"/>
@@ -19766,12 +19867,12 @@
       </c>
       <c r="Q42" s="14" t="inlineStr">
         <is>
-          <t>https://www.town.tanagura.fukushima.jp/page/page001917.html</t>
+          <t>https://www.town.tanagura.fukushima.jp/data/doc/1617153691_doc_15_0.pdf</t>
         </is>
       </c>
       <c r="R42" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。環境基本計画はR3.3策定（本編PDF https://www.town.tanagura.fukushima.jp/data/doc/1617153691_doc_15_0.pdf）。計画期間は検索結果で確認できず（10年ならR3〜R12、5年ならR3〜R7→改定期の可能性）。要PDF確認。</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。環境基本計画はR3.3策定（本編PDF https://www.town.tanagura.fukushima.jp/data/doc/1617153691_doc_15_0.pdf）。計画期間は検索結果で確認できず（10年ならR3〜R12、5年ならR3〜R7→改定期の可能性）。要PDF確認。 【追加調査 2026-10】国交省一覧では町単独計画あり・期間満了（灰色）だが、町単独の地域公共交通計画（網形成計画・旧連携計画含む）は4回の検索（『棚倉町地域公共交通計画』『地域公共交通網形成計画』『地域公共交通会議』等）で確認できず。町サイトで見つかったのはタクシー・バス利用料金助成事業（https://www.town.tanagura.fukushima.jp/jumin/sumai-kankyo-eisei/page001281.html ）のみ。期間満了の旧計画が残存、次期計画の着手も未確認。現行データ（福島県地域公共交通計画R6〜R12）を維持。要：町総務課/企画担当へ照会。2026-10-02検索。 【追加調査 2026-10】町HPドメイン検索で本編PDF（R3.3策定）がヒット。検索要約では「計画期間は令和32年（2050年）まで」、2030年度45%・2050年80%削減（H25比）目標。要約1件のみで、長期目標年を計画期間と誤認している可能性あり（本文で中間見直し年の有無は未確認）。PDF・町HPは取得不可（egressブロック）。期間がR3〜R12ならR12満了。次期計画着手の情報なし。 追加検索：計画書に温室効果ガス排出量・国県動向・社会情勢の変化に応じ適宜見直す旨の記載（固定の中間見直し年は確認できず）。検索要約に「2026年3月30日」とあったがPDFのファイル名タイムスタンプ(1617153691=2021/3/31)からR3.3策定と判断（R8新規策定ではない）。 【統合時判断】期間の根拠が要約1件のみで長期目標年との混同が疑われるため、e_end は空欄・不明とした（R3〜R12の10年計画の可能性もあり要本文確認）。 根拠: 計画期間は令和32年（2050年）までとされ、令和12年（2030年）までの温室効果ガス削減目標は平成25年の排出量を基準とし45％</t>
         </is>
       </c>
       <c r="S42" s="15" t="inlineStr">
@@ -19848,18 +19949,18 @@
       </c>
       <c r="P43" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q43" s="11" t="n"/>
       <c r="R43" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。町は「地域の公共交通網整備に向けた基本調査研究」を公表（https://www.town.yamatsuri.fukushima.jp/sp/page/page000235.html）。環境基本計画は町HPドメイン検索でも確認できず（総合計画・太陽光条例等のみ）。第7次総合計画R8〜R12策定。</t>
-        </is>
-      </c>
-      <c r="S43" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。町は「地域の公共交通網整備に向けた基本調査研究」を公表（https://www.town.yamatsuri.fukushima.jp/sp/page/page000235.html）。環境基本計画は町HPドメイン検索でも確認できず（総合計画・太陽光条例等のみ）。第7次総合計画R8〜R12策定。 【追加調査 2026-10】町HPドメイン指定検索で環境基本計画ヒットせず（第6次総合計画2021〜2026、第7次総合計画R8〜R12、過疎計画、公共施設計画、太陽光調和条例のみ）。地球温暖化対策実行計画も検索で確認できず。環境施策は総合計画で対応と判断（計画なし、根拠は検索での不在）。</t>
+        </is>
+      </c>
+      <c r="S43" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T43" s="17" t="inlineStr">
@@ -19891,12 +19992,12 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>福島県地域公共交通計画（県全域の広域計画）</t>
+          <t>塙町地域公共交通網形成計画（H30.3策定、国交省一覧の単独計画はこれと推定）</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>R6〜R12</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="H44" s="13" t="n">
@@ -19904,7 +20005,7 @@
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>確認済</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
@@ -19914,7 +20015,7 @@
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf</t>
+          <t>https://www.town.hanawa.fukushima.jp/page/page000688.html</t>
         </is>
       </c>
       <c r="L44" s="11" t="n"/>
@@ -19937,7 +20038,7 @@
       <c r="Q44" s="11" t="n"/>
       <c r="R44" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。町は地域公共交通網形成計画をH30.3策定（https://www.town.hanawa.fukushima.jp/page/page000688.html、期間未確認・満了の可能性）、旧「塙町地域公共交通総合連携計画」（H23.3, https://www.town.hanawa.fukushima.jp/data/doc/1503288674_doc_30_0.pdf）。環境基本計画は町HP「各種計画」ページ等で見当たらず、温暖化対策実行計画（事務事業編）（page000922）と「地域まるごと省エネ計画」（page001462、区域施策編相当）が代替。</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。町は地域公共交通網形成計画をH30.3策定（https://www.town.hanawa.fukushima.jp/page/page000688.html、期間未確認・満了の可能性）、旧「塙町地域公共交通総合連携計画」（H23.3, https://www.town.hanawa.fukushima.jp/data/doc/1503288674_doc_30_0.pdf）。環境基本計画は町HP「各種計画」ページ等で見当たらず、温暖化対策実行計画（事務事業編）（page000922）と「地域まるごと省エネ計画」（page001462、区域施策編相当）が代替。 【追加調査 2026-10】2026-10-02再調査（検索5回）：国交省一覧(R8.5末)の単独計画は、町HPでH30.3策定とされる塙町地域公共交通網形成計画と推定（網形成計画は地域公共交通計画とみなし扱い）。計画期間・後継の地域公共交通計画は検索本文で確認できず。町HPはWebFetchブロック。協議会議事録はH30年度第2回(H31.3.27, https://www.town.hanawa.fukushima.jp/data/doc/1554963460_doc_11_0.pdf)まで検索でヒット、次期計画の策定委託・パブコメ等の着手情報は見つからず。旧総合連携計画はH23〜R2年度相当。県計画(R6〜R12)は参考として既存noteどおり。要町への直接確認。</t>
         </is>
       </c>
       <c r="S44" s="15" t="inlineStr">
@@ -20014,18 +20115,18 @@
       </c>
       <c r="P45" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q45" s="11" t="n"/>
       <c r="R45" s="11" t="inlineStr">
         <is>
-          <t>交通計画はR5.2.21協議会で策定、デマンド交通導入を位置付け。R9年度末で満了→R8〜R9に次期計画検討が見込まれる。R7年度協議会会議録が村HP（上記協議会ページ）に公開、次期計画への言及は未確認。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。（バイオマスヴィレッジ構想・公害対策条例のみ確認） 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（R7年度第1回協議会資料は公開されているが次期計画の記載は確認できず）／根拠: https://www.vill.samegawa.fukushima.jp/sp/page/page002592.html</t>
-        </is>
-      </c>
-      <c r="S45" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通計画はR5.2.21協議会で策定、デマンド交通導入を位置付け。R9年度末で満了→R8〜R9に次期計画検討が見込まれる。R7年度協議会会議録が村HP（上記協議会ページ）に公開、次期計画への言及は未確認。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。（バイオマスヴィレッジ構想・公害対策条例のみ確認） 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9／次期: 確認できず（R7年度第1回協議会資料は公開されているが次期計画の記載は確認できず）／根拠: https://www.vill.samegawa.fukushima.jp/sp/page/page002592.html 【追加調査 2026-10】村HPドメイン指定検索で環境基本計画ヒットせず。「事業・計画」ページ（https://www.vill.samegawa.fukushima.jp/page/dir000046.html）周辺では第4次鮫川村振興計画（環境保全・景観施策を内包）、バイオマスヴィレッジ構想、公共施設等総合管理計画、総合戦略のみ。環境施策は振興計画で対応と判断。</t>
+        </is>
+      </c>
+      <c r="S45" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T45" s="11" t="inlineStr">
@@ -20097,18 +20198,18 @@
       </c>
       <c r="P46" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q46" s="11" t="n"/>
       <c r="R46" s="11" t="inlineStr">
         <is>
-          <t>H29.3策定の石川町地域公共交通網形成計画の後継計画（2023〜2028年度）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。第2次石川町地球温暖化防止実行計画（事務事業編、2023〜2028年度）https://www.town.ishikawa.fukushima.jp/admin/ishikawa/info/005930.html のみ確認。</t>
-        </is>
-      </c>
-      <c r="S46" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>H29.3策定の石川町地域公共交通網形成計画の後継計画（2023〜2028年度）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。第2次石川町地球温暖化防止実行計画（事務事業編、2023〜2028年度）https://www.town.ishikawa.fukushima.jp/admin/ishikawa/info/005930.html のみ確認。 【追加調査 2026-10】町HPドメイン指定検索で環境基本計画ヒットせず。環境系は第2次石川町地球温暖化防止実行計画（事務事業編、2023〜2028年度）・環境にやさしい庁内行動計画【第3期】のみ（https://www.town.ishikawa.fukushima.jp/admin/ishikawa/info/005930.html）。総合計画は第6次（2019〜10年間）。計画なしと判断。 根拠: 「第2次石川町地球温暖化防止計画（事務事業編）」が改訂され、計画期間は2023年度から2028年度</t>
+        </is>
+      </c>
+      <c r="S46" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T46" s="11" t="inlineStr">
@@ -20140,16 +20241,16 @@
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>福島県地域公共交通計画（県全域の広域計画）</t>
+          <t>玉川村地域公共交通網形成計画（R1.6策定、期間満了）</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>R6〜R12</t>
+          <t>R1〜R6</t>
         </is>
       </c>
       <c r="H47" s="13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -20163,7 +20264,7 @@
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/uploaded/attachment/622613.pdf</t>
+          <t>https://www.vill.tamakawa.fukushima.jp/guide/plan/000055.html</t>
         </is>
       </c>
       <c r="L47" s="11" t="n"/>
@@ -20180,18 +20281,18 @@
       </c>
       <c r="P47" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q47" s="11" t="n"/>
       <c r="R47" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。住宅用太陽光補助等のみ確認。</t>
-        </is>
-      </c>
-      <c r="S47" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。住宅用太陽光補助等のみ確認。 【追加調査 2026-10】2026-10-02再調査：村単独計画は「玉川村地域公共交通網形成計画」（企画政策課、玉川村地域公共交通活性化協議会で審議し令和元年6月策定、対象区域は村全域、期間2019〜2024年度の6年間）で、国交省一覧の「期間満了」と整合。後継の地域公共交通計画・策定委託・パブコメ等は村HPドメイン指定検索でも確認できず（村HPはWebFetchブロック）。現状は県計画(R6〜R12)と県中・県南圏域地域公共交通利便増進実施計画(R7.10〜R13.3, https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf)の対象。第7次総合計画を策定中（https://www.vill.tamakawa.fukushima.jp/guide/plan/005944.html）で、次期交通計画の検討が連動する可能性あり、要直接確認。 根拠: 計画の期間は2019年度から2024年度までの6年間 【追加調査 2026-10】村HPドメイン指定検索（環境基本計画・地球温暖化対策実行計画）でヒットせず。総合開発計画、第7次玉川村総合計画（策定中ニュースレター）等のみ。環境施策は総合計画で対応と判断。</t>
+        </is>
+      </c>
+      <c r="S47" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T47" s="17" t="inlineStr">
@@ -20263,18 +20364,18 @@
       </c>
       <c r="P48" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q48" s="11" t="n"/>
       <c r="R48" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。平田村地球温暖化対策実施計画が情報公開ページ（https://www.vill.hirata.fukushima.jp/soshiki/2/174.html）に掲載、一般廃棄物処理基本計画（R4.4, R7.4変更）あり。</t>
-        </is>
-      </c>
-      <c r="S48" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。平田村地球温暖化対策実施計画が情報公開ページ（https://www.vill.hirata.fukushima.jp/soshiki/2/174.html）に掲載、一般廃棄物処理基本計画（R4.4, R7.4変更）あり。 【追加調査 2026-10】村HPドメイン指定検索で環境基本計画ヒットせず。環境系は平田村地球温暖化対策実行計画（事務事業編・区域施策編、情報公開ページ https://www.vill.hirata.fukushima.jp/soshiki/2/174.html）、一般廃棄物処理基本計画（R4.4、R7.4変更）、第5次総合計画後期基本計画（R3.3）のみ。実行計画＋総合計画で対応と判断。 根拠: 「平田村地球温暖化対策実行計画」（事務事業編・区域施策編）</t>
+        </is>
+      </c>
+      <c r="S48" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T48" s="17" t="inlineStr">
@@ -20429,18 +20530,18 @@
       </c>
       <c r="P50" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q50" s="11" t="n"/>
       <c r="R50" s="11" t="inlineStr">
         <is>
-          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。町HP「各種計画」ページ（https://www.town.furudono.fukushima.jp/chouseijyouhou/torikumikeikaku/keikaku/760）に記載ある可能性は低いが未確認。</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>町村単独の地域公共交通計画は検索で確認できず、県計画（R6.3策定、R7.2等に一部改定）が対象範囲。こおりやま広域連携中枢都市圏構成団体（圏域の交通計画は確認できず）。環境基本計画は検索（村/町HPドメイン指定含む）で確認できず。町HP「各種計画」ページ（https://www.town.furudono.fukushima.jp/chouseijyouhou/torikumikeikaku/keikaku/760）に記載ある可能性は低いが未確認。 【追加調査 2026-10】町HP「各種計画」ページ（https://www.town.furudono.fukushima.jp/chouseijyouhou/torikumikeikaku/keikaku/760）は水質検査計画・橋梁長寿命化・耐震改修促進・生活排水処理等を掲載、環境基本計画は検索で確認できず。第7次振興計画、過疎・辺地計画、デジ田総合戦略のみ。計画なしと判断。</t>
+        </is>
+      </c>
+      <c r="S50" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T50" s="17" t="inlineStr">
@@ -20472,16 +20573,16 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>福島県地域公共交通計画（県全域）</t>
+          <t>三春町地域公共交通計画</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>R6〜R12</t>
+          <t>R5〜R9</t>
         </is>
       </c>
       <c r="H51" s="13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -20495,7 +20596,7 @@
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/sec/16005d/chiikikoukyoukasseikakyougikai.html</t>
+          <t>https://www.town.miharu.fukushima.jp/soshiki/4/kokyoukotsu.html</t>
         </is>
       </c>
       <c r="L51" s="11" t="n"/>
@@ -20518,7 +20619,7 @@
       <c r="Q51" s="11" t="n"/>
       <c r="R51" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は再検索でも確認できず(R8.3にユニ・トランドと交通データ活用の包括連携協定締結 https://www.logi-today.com/930374)、県全域の福島県地域公共交通計画(R6〜R12)が該当。県中・県南圏域地域公共交通利便増進実施計画(R7.10〜R13.3)にも含まれる(https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf)。環境：三春町環境条例(H12)はあるが環境基本計画は検索で確認できず。</t>
+          <t>交通：町単独計画は再検索でも確認できず(R8.3にユニ・トランドと交通データ活用の包括連携協定締結 https://www.logi-today.com/930374)、県全域の福島県地域公共交通計画(R6〜R12)が該当。県中・県南圏域地域公共交通利便増進実施計画(R7.10〜R13.3)にも含まれる(https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf)。環境：三春町環境条例(H12)はあるが環境基本計画は検索で確認できず。 【追加調査 2026-10】2026-10-02再調査：町単独の「三春町地域公共交通計画」（住民課所管、三春町地域公共交通活性化協議会）を町HPで確認。計画期間は令和5年度〜令和9年度の5年間。R6.6の協議会で一部改定、R7.8の協議会で再改定（町HPドメイン検索の本文より）。町営バスはR8.4から運行見直し（https://www.town.miharu.fukushima.jp/soshiki/4/tyoueibasu.html）、福島交通路線バスもR7.10から再編（https://www.town.miharu.fukushima.jp/soshiki/4/fukushimakotsubus.html）。次期計画（R10〜）の策定委託・パブコメ等は検索で確認できず（町HPはWebFetchブロック）。終期R9のためR8〜R9に次期策定が見込まれる。前回noteの「町単独計画確認できず」は訂正。 根拠: 計画期間は令和5年度から令和9年度までの5年間（三春町地域公共交通計画を策定しました・町HP）</t>
         </is>
       </c>
       <c r="S51" s="15" t="inlineStr">
@@ -20555,16 +20656,16 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>福島県地域公共交通計画（県全域）</t>
+          <t>小野町地域公共交通計画</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>R6〜R12</t>
+          <t>R6〜R10</t>
         </is>
       </c>
       <c r="H52" s="13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -20578,7 +20679,7 @@
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>https://www.pref.fukushima.lg.jp/sec/16005d/chiikikoukyoukasseikakyougikai.html</t>
+          <t>https://www.town.ono.fukushima.jp/soshiki/3/entry_9.html</t>
         </is>
       </c>
       <c r="L52" s="11" t="n"/>
@@ -20601,7 +20702,7 @@
       <c r="Q52" s="11" t="n"/>
       <c r="R52" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独計画は再検索でも確認できず、県全域の福島県地域公共交通計画(R6〜R12)が該当。県中・県南圏域地域公共交通利便増進実施計画(R7.10〜R13.3)にも含まれる(https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf)。環境：環境基本計画は検索で確認できず。</t>
+          <t>交通：町単独計画は再検索でも確認できず、県全域の福島県地域公共交通計画(R6〜R12)が該当。県中・県南圏域地域公共交通利便増進実施計画(R7.10〜R13.3)にも含まれる(https://www.mlit.go.jp/sogoseisaku/transport/content/001895410.pdf)。環境：環境基本計画は検索で確認できず。 【追加調査 2026-10】2026-10-02再調査：町単独の「小野町地域公共交通計画」（企画政策課まちづくり推進室）を町HPで確認。小野町総合計画(2023〜2027)・福島県地域公共交通計画(2024〜2030)を踏まえ策定、計画期間は令和6年度〜令和10年度の5年間。路線バス（郡山・石川・いわき方面）とタクシー利用料金助成が柱。終期R10のため次期計画の着手情報は未調査（現時点で該当なしと想定）。前回noteの「町単独計画確認できず」は訂正。 根拠: 計画期間：令和６年度から令和10年度（５年間）</t>
         </is>
       </c>
       <c r="S52" s="15" t="inlineStr">
@@ -20937,18 +21038,18 @@
       </c>
       <c r="P56" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q56" s="11" t="n"/>
       <c r="R56" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。村HPで脱炭素ビジョン策定業務および「地球温暖化対策実行計画(区域施策編)策定業務委託」の公募型プロポーザル実施の記載あり(時期未確認、https://www.kawauchimura.jp/)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
-        </is>
-      </c>
-      <c r="S56" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。村HPで脱炭素ビジョン策定業務および「地球温暖化対策実行計画(区域施策編)策定業務委託」の公募型プロポーザル実施の記載あり(時期未確認、https://www.kawauchimura.jp/)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf 【追加調査 2026-10】村HPドメイン指定検索で環境基本計画ヒットせず。村HP「計画、予算」ページ（https://www.kawauchimura.jp/gyosei/keikaku-yosan/）に川内村地球温暖化対策実行計画(区域施策編)が掲載、同策定業務委託は公募型プロポーザルで実施（入札情報 https://www.kawauchimura.jp/bid/）。環境基本計画ではなく区域施策編で対応と判断。 根拠: 川内村地球温暖化対策実行計画(区域施策編)は、計画、予算に関するページにも掲載</t>
+        </is>
+      </c>
+      <c r="S56" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T56" s="11" t="inlineStr">
@@ -21103,18 +21204,18 @@
       </c>
       <c r="P58" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q58" s="11" t="n"/>
       <c r="R58" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。双葉町再生可能エネルギー活用・推進計画(H28.3)あり(https://www.town.fukushima-futaba.lg.jp/secure/7318/201603_renewable-energy-promotion-plan.pdf)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
-        </is>
-      </c>
-      <c r="S58" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず。双葉町再生可能エネルギー活用・推進計画(H28.3)あり(https://www.town.fukushima-futaba.lg.jp/secure/7318/201603_renewable-energy-promotion-plan.pdf)。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf 【追加調査 2026-10】町HPドメイン指定検索で環境基本計画ヒットせず。復興まちづくり計画（第二次〜第四次 https://www.town.fukushima-futaba.lg.jp/12602.htm）、復興まちづくり長期ビジョン、森林整備計画、再生可能エネルギー活用・推進計画(H28.3)のみ。避難指示解除後の復興計画で対応と判断。</t>
+        </is>
+      </c>
+      <c r="S58" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T58" s="11" t="inlineStr">
@@ -21269,18 +21370,18 @@
       </c>
       <c r="P60" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q60" s="11" t="n"/>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず(村HP計画一覧 https://www.katsurao.org/life/3/17/52/ 参照)。第五次葛尾村振興計画(2023)、スマートコミュニティ事業あり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf</t>
-        </is>
-      </c>
-      <c r="S60" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：県の避難地域広域公共交通計画(R5.4〜R10.3、R7.3一部改定)が対象。R8年度に最終評価・次期計画の方向性決定、R9年度に次期計画(R10.4〜)策定予定との県資料あり(https://www.pref.fukushima.lg.jp/sec/16005d/hinan-koutsuu-keikaku.html、関連 https://www.pref.fukushima.lg.jp/uploaded/attachment/756357.pdf)。町村単独の交通計画は未確認。環境：環境基本計画は検索で確認できず(村HP計画一覧 https://www.katsurao.org/life/3/17/52/ 参照)。第五次葛尾村振興計画(2023)、スマートコミュニティ事業あり。 【ファクトチェック 2026-10-01: 正しい】確認期間: R5〜R9（R5.4〜R10.3）／次期: 予定のみ：協議会資料でR8年度に最終評価、R9年度に次期計画（R10.4〜）策定と記載 https://www.pref.fukushima.lg.jp/uploaded/attachment/756354.pdf（策定支援業務の公募等は確／根拠: https://www.pref.fukushima.lg.jp/uploaded/attachment/738677.pdf 【追加調査 2026-10】村HP「計画」一覧（https://www.katsurao.org/life/3/17/52/）・ドメイン指定検索で環境基本計画ヒットせず。第五次葛尾村振興計画、復興計画・かつらお再生戦略プラン、特定復興再生拠点計画、スマートコミュニティ事業のみ。計画なしと判断。</t>
+        </is>
+      </c>
+      <c r="S60" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T60" s="11" t="inlineStr">
@@ -21352,18 +21453,18 @@
       </c>
       <c r="P61" s="13" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>計画なし</t>
         </is>
       </c>
       <c r="Q61" s="11" t="n"/>
       <c r="R61" s="11" t="inlineStr">
         <is>
-          <t>交通：町単独の地域公共交通計画は検索で確認できず、県全域の福島県地域公共交通計画(R6〜R12)が該当。環境：環境基本計画は検索で確認できず。新地町環境未来都市計画(H24.5策定、R7.1・R7.7・R8.7改定、https://future-city.go.jp/pdf/torikumi_city/shinchi_plan.pdf)、地球温暖化対策実行計画(事務事業編)(https://www.shinchi-town.jp/uploaded/attachment/7983.pdf)あり。</t>
-        </is>
-      </c>
-      <c r="S61" s="18" t="inlineStr">
-        <is>
-          <t>交通のみ調査</t>
+          <t>交通：町単独の地域公共交通計画は検索で確認できず、県全域の福島県地域公共交通計画(R6〜R12)が該当。環境：環境基本計画は検索で確認できず。新地町環境未来都市計画(H24.5策定、R7.1・R7.7・R8.7改定、https://future-city.go.jp/pdf/torikumi_city/shinchi_plan.pdf)、地球温暖化対策実行計画(事務事業編)(https://www.shinchi-town.jp/uploaded/attachment/7983.pdf)あり。 【追加調査 2026-10】町HPドメイン指定検索・名称完全一致検索とも環境基本計画ヒットせず。環境施策は新地町環境未来都市計画（H24.5策定、以降改定、https://future-city.go.jp/pdf/torikumi_city/shinchi_plan.pdf）と復興計画・第6次総合計画（〜2030年度）、国環研との連携協定で対応。事務事業編実行計画あり。計画なしと判断。</t>
+        </is>
+      </c>
+      <c r="S61" s="15" t="inlineStr">
+        <is>
+          <t>調査済</t>
         </is>
       </c>
       <c r="T61" s="17" t="inlineStr">
@@ -21506,49 +21607,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
